--- a/data/test.xlsx
+++ b/data/test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I512"/>
+  <dimension ref="A1:I590"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11481,6 +11481,1868 @@
       <c r="H512" t="inlineStr"/>
       <c r="I512" t="inlineStr"/>
     </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr"/>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_container</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr"/>
+      <c r="F513" t="inlineStr"/>
+      <c r="G513" t="inlineStr"/>
+      <c r="H513" t="inlineStr"/>
+      <c r="I513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr"/>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr"/>
+      <c r="F514" t="inlineStr"/>
+      <c r="G514" t="inlineStr"/>
+      <c r="H514" t="inlineStr"/>
+      <c r="I514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr"/>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_contents</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr"/>
+      <c r="F515" t="inlineStr"/>
+      <c r="G515" t="inlineStr"/>
+      <c r="H515" t="inlineStr"/>
+      <c r="I515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr"/>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_left_side</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>[69,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr"/>
+      <c r="F516" t="inlineStr"/>
+      <c r="G516" t="inlineStr"/>
+      <c r="H516" t="inlineStr"/>
+      <c r="I516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr"/>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/clock</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>[69,0][181,96]</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr"/>
+      <c r="H517" t="inlineStr"/>
+      <c r="I517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr"/>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr"/>
+      <c r="F518" t="inlineStr"/>
+      <c r="G518" t="inlineStr"/>
+      <c r="H518" t="inlineStr"/>
+      <c r="I518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr"/>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area_inner</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr"/>
+      <c r="F519" t="inlineStr"/>
+      <c r="G519" t="inlineStr"/>
+      <c r="H519" t="inlineStr"/>
+      <c r="I519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr"/>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notificationIcons</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr"/>
+      <c r="H520" t="inlineStr"/>
+      <c r="I520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr"/>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/cutout_space_view</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>[444,0][636,76]</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr"/>
+      <c r="F521" t="inlineStr"/>
+      <c r="G521" t="inlineStr"/>
+      <c r="H521" t="inlineStr"/>
+      <c r="I521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr"/>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icon_area</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>[636,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr"/>
+      <c r="F522" t="inlineStr"/>
+      <c r="G522" t="inlineStr"/>
+      <c r="H522" t="inlineStr"/>
+      <c r="I522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr"/>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icons</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>[798,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr"/>
+      <c r="F523" t="inlineStr"/>
+      <c r="G523" t="inlineStr"/>
+      <c r="H523" t="inlineStr"/>
+      <c r="I523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr"/>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/statusIcons</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>[798,0][838,96]</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr"/>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="inlineStr"/>
+      <c r="H524" t="inlineStr"/>
+      <c r="I524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr"/>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/signal_cluster</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>[838,0][944,96]</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr"/>
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="inlineStr"/>
+      <c r="H525" t="inlineStr"/>
+      <c r="I525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr"/>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_combo</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>[838,30][896,66]</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr"/>
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="inlineStr"/>
+      <c r="H526" t="inlineStr"/>
+      <c r="I526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr"/>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_inout</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>[838,30][896,66]</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr"/>
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="inlineStr"/>
+      <c r="H527" t="inlineStr"/>
+      <c r="I527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr"/>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_signal</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>[840,30][896,66]</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr"/>
+      <c r="F528" t="inlineStr"/>
+      <c r="G528" t="inlineStr"/>
+      <c r="H528" t="inlineStr"/>
+      <c r="I528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr"/>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/no_sims</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>[896,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr"/>
+      <c r="F529" t="inlineStr"/>
+      <c r="G529" t="inlineStr"/>
+      <c r="H529" t="inlineStr"/>
+      <c r="I529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr"/>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>[944,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr"/>
+      <c r="F530" t="inlineStr"/>
+      <c r="G530" t="inlineStr"/>
+      <c r="H530" t="inlineStr"/>
+      <c r="I530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr"/>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery_content</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr"/>
+      <c r="F531" t="inlineStr"/>
+      <c r="G531" t="inlineStr"/>
+      <c r="H531" t="inlineStr"/>
+      <c r="I531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr"/>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/stat_battery_view</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr"/>
+      <c r="F532" t="inlineStr"/>
+      <c r="G532" t="inlineStr"/>
+      <c r="H532" t="inlineStr"/>
+      <c r="I532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr"/>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>com.coloros.smartsidebar:id/roundRectView</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>[1062,600][1080,822]</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr"/>
+      <c r="F533" t="inlineStr"/>
+      <c r="G533" t="inlineStr"/>
+      <c r="H533" t="inlineStr"/>
+      <c r="I533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr"/>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>android:id/content</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr"/>
+      <c r="F534" t="inlineStr"/>
+      <c r="G534" t="inlineStr"/>
+      <c r="H534" t="inlineStr"/>
+      <c r="I534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr"/>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/base_layout</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr"/>
+      <c r="F535" t="inlineStr"/>
+      <c r="G535" t="inlineStr"/>
+      <c r="H535" t="inlineStr"/>
+      <c r="I535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr"/>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>[0,96][1080,240]</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr"/>
+      <c r="F536" t="inlineStr"/>
+      <c r="G536" t="inlineStr"/>
+      <c r="H536" t="inlineStr"/>
+      <c r="I536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr"/>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title_layout</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>[0,96][1080,240]</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr"/>
+      <c r="F537" t="inlineStr"/>
+      <c r="G537" t="inlineStr"/>
+      <c r="H537" t="inlineStr"/>
+      <c r="I537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr"/>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title_left_layout</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>[0,96][129,240]</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr"/>
+      <c r="G538" t="inlineStr"/>
+      <c r="H538" t="inlineStr"/>
+      <c r="I538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr"/>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title_left_image</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>[48,139][81,196]</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr"/>
+      <c r="F539" t="inlineStr"/>
+      <c r="G539" t="inlineStr"/>
+      <c r="H539" t="inlineStr"/>
+      <c r="I539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr"/>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title_content</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>[492,96][588,240]</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="F540" t="inlineStr"/>
+      <c r="G540" t="inlineStr"/>
+      <c r="H540" t="inlineStr"/>
+      <c r="I540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr"/>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/base_content</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>[0,240][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr"/>
+      <c r="F541" t="inlineStr"/>
+      <c r="G541" t="inlineStr"/>
+      <c r="H541" t="inlineStr"/>
+      <c r="I541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr"/>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_title</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>[330,360][750,441]</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>欢迎使用睿博士</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr"/>
+      <c r="G542" t="inlineStr"/>
+      <c r="H542" t="inlineStr"/>
+      <c r="I542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr"/>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_area</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>[0,630][1080,687]</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr"/>
+      <c r="F543" t="inlineStr"/>
+      <c r="G543" t="inlineStr"/>
+      <c r="H543" t="inlineStr"/>
+      <c r="I543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr"/>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tvArea</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>[96,630][864,687]</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr">
+        <is>
+          <t>中国</t>
+        </is>
+      </c>
+      <c r="F544" t="inlineStr"/>
+      <c r="G544" t="inlineStr"/>
+      <c r="H544" t="inlineStr"/>
+      <c r="I544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr"/>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tvAreaCode</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>[864,630][936,687]</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr">
+        <is>
+          <t>+86</t>
+        </is>
+      </c>
+      <c r="F545" t="inlineStr"/>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr"/>
+      <c r="I545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr"/>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/imageView</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>[96,820][138,874]</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr"/>
+      <c r="F546" t="inlineStr"/>
+      <c r="G546" t="inlineStr"/>
+      <c r="H546" t="inlineStr"/>
+      <c r="I546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr"/>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/register1_user</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>[183,819][1080,876]</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>请输入手机号或邮箱</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr"/>
+      <c r="G547" t="inlineStr"/>
+      <c r="H547" t="inlineStr"/>
+      <c r="I547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr"/>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_tips</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>[60,954][723,1003]</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr">
+        <is>
+          <t>成功注册账号后，国家/地区将不能被修改</t>
+        </is>
+      </c>
+      <c r="F548" t="inlineStr"/>
+      <c r="G548" t="inlineStr"/>
+      <c r="H548" t="inlineStr"/>
+      <c r="I548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr"/>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_user_agreement</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>[0,1812][1080,1926]</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr"/>
+      <c r="F549" t="inlineStr"/>
+      <c r="G549" t="inlineStr"/>
+      <c r="H549" t="inlineStr"/>
+      <c r="I549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr"/>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_cb</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>[123,1812][273,1926]</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr"/>
+      <c r="F550" t="inlineStr"/>
+      <c r="G550" t="inlineStr"/>
+      <c r="H550" t="inlineStr"/>
+      <c r="I550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr"/>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/checkbox</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>[213,1848][255,1890]</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr"/>
+      <c r="F551" t="inlineStr"/>
+      <c r="G551" t="inlineStr"/>
+      <c r="H551" t="inlineStr"/>
+      <c r="I551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr"/>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_user_agreement</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>[273,1844][957,1893]</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr">
+        <is>
+          <t>已阅读并同意《用户协议》与《隐私政策》</t>
+        </is>
+      </c>
+      <c r="F552" t="inlineStr"/>
+      <c r="G552" t="inlineStr"/>
+      <c r="H552" t="inlineStr"/>
+      <c r="I552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr"/>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>[0,1926][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr"/>
+      <c r="F553" t="inlineStr"/>
+      <c r="G553" t="inlineStr"/>
+      <c r="H553" t="inlineStr"/>
+      <c r="I553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr"/>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/register1_next</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>[60,1926][1020,2058]</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr">
+        <is>
+          <t>下一步</t>
+        </is>
+      </c>
+      <c r="F554" t="inlineStr"/>
+      <c r="G554" t="inlineStr"/>
+      <c r="H554" t="inlineStr"/>
+      <c r="I554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr"/>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_one_click_register</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>[0,2118][1080,2250]</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr"/>
+      <c r="F555" t="inlineStr"/>
+      <c r="G555" t="inlineStr"/>
+      <c r="H555" t="inlineStr"/>
+      <c r="I555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>注册</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr"/>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/register_one_click</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>[60,2118][1020,2250]</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t>一键注册</t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr"/>
+      <c r="G556" t="inlineStr"/>
+      <c r="H556" t="inlineStr"/>
+      <c r="I556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr"/>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_container</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr"/>
+      <c r="F557" t="inlineStr"/>
+      <c r="G557" t="inlineStr"/>
+      <c r="H557" t="inlineStr"/>
+      <c r="I557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr"/>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr"/>
+      <c r="F558" t="inlineStr"/>
+      <c r="G558" t="inlineStr"/>
+      <c r="H558" t="inlineStr"/>
+      <c r="I558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr"/>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_contents</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr"/>
+      <c r="F559" t="inlineStr"/>
+      <c r="G559" t="inlineStr"/>
+      <c r="H559" t="inlineStr"/>
+      <c r="I559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr"/>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_left_side</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>[69,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr"/>
+      <c r="F560" t="inlineStr"/>
+      <c r="G560" t="inlineStr"/>
+      <c r="H560" t="inlineStr"/>
+      <c r="I560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr"/>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/clock</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>[69,0][181,96]</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr">
+        <is>
+          <t>11:51</t>
+        </is>
+      </c>
+      <c r="F561" t="inlineStr"/>
+      <c r="G561" t="inlineStr"/>
+      <c r="H561" t="inlineStr"/>
+      <c r="I561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr"/>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr"/>
+      <c r="F562" t="inlineStr"/>
+      <c r="G562" t="inlineStr"/>
+      <c r="H562" t="inlineStr"/>
+      <c r="I562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr"/>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area_inner</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr"/>
+      <c r="F563" t="inlineStr"/>
+      <c r="G563" t="inlineStr"/>
+      <c r="H563" t="inlineStr"/>
+      <c r="I563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr"/>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notificationIcons</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr"/>
+      <c r="F564" t="inlineStr"/>
+      <c r="G564" t="inlineStr"/>
+      <c r="H564" t="inlineStr"/>
+      <c r="I564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr"/>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/cutout_space_view</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>[444,0][636,76]</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr"/>
+      <c r="F565" t="inlineStr"/>
+      <c r="G565" t="inlineStr"/>
+      <c r="H565" t="inlineStr"/>
+      <c r="I565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr"/>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icon_area</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>[636,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr"/>
+      <c r="F566" t="inlineStr"/>
+      <c r="G566" t="inlineStr"/>
+      <c r="H566" t="inlineStr"/>
+      <c r="I566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr"/>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icons</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>[798,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr"/>
+      <c r="F567" t="inlineStr"/>
+      <c r="G567" t="inlineStr"/>
+      <c r="H567" t="inlineStr"/>
+      <c r="I567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr"/>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/statusIcons</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>[798,0][838,96]</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr"/>
+      <c r="F568" t="inlineStr"/>
+      <c r="G568" t="inlineStr"/>
+      <c r="H568" t="inlineStr"/>
+      <c r="I568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr"/>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/signal_cluster</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>[838,0][944,96]</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr"/>
+      <c r="F569" t="inlineStr"/>
+      <c r="G569" t="inlineStr"/>
+      <c r="H569" t="inlineStr"/>
+      <c r="I569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr"/>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_combo</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>[838,30][896,66]</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr"/>
+      <c r="F570" t="inlineStr"/>
+      <c r="G570" t="inlineStr"/>
+      <c r="H570" t="inlineStr"/>
+      <c r="I570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr"/>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_inout</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>[838,30][896,66]</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr"/>
+      <c r="F571" t="inlineStr"/>
+      <c r="G571" t="inlineStr"/>
+      <c r="H571" t="inlineStr"/>
+      <c r="I571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr"/>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_signal</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>[840,30][896,66]</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr"/>
+      <c r="F572" t="inlineStr"/>
+      <c r="G572" t="inlineStr"/>
+      <c r="H572" t="inlineStr"/>
+      <c r="I572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr"/>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/no_sims</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>[896,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr"/>
+      <c r="F573" t="inlineStr"/>
+      <c r="G573" t="inlineStr"/>
+      <c r="H573" t="inlineStr"/>
+      <c r="I573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr"/>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>[944,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr"/>
+      <c r="F574" t="inlineStr"/>
+      <c r="G574" t="inlineStr"/>
+      <c r="H574" t="inlineStr"/>
+      <c r="I574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr"/>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery_content</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr"/>
+      <c r="F575" t="inlineStr"/>
+      <c r="G575" t="inlineStr"/>
+      <c r="H575" t="inlineStr"/>
+      <c r="I575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr"/>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/stat_battery_view</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr"/>
+      <c r="F576" t="inlineStr"/>
+      <c r="G576" t="inlineStr"/>
+      <c r="H576" t="inlineStr"/>
+      <c r="I576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr"/>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>android:id/content</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr"/>
+      <c r="F577" t="inlineStr"/>
+      <c r="G577" t="inlineStr"/>
+      <c r="H577" t="inlineStr"/>
+      <c r="I577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr"/>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/base_layout</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr"/>
+      <c r="F578" t="inlineStr"/>
+      <c r="G578" t="inlineStr"/>
+      <c r="H578" t="inlineStr"/>
+      <c r="I578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr"/>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>[0,96][1080,240]</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr"/>
+      <c r="F579" t="inlineStr"/>
+      <c r="G579" t="inlineStr"/>
+      <c r="H579" t="inlineStr"/>
+      <c r="I579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr"/>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title_layout</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>[0,96][1080,240]</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr"/>
+      <c r="F580" t="inlineStr"/>
+      <c r="G580" t="inlineStr"/>
+      <c r="H580" t="inlineStr"/>
+      <c r="I580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr"/>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title_left_layout</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>[0,96][129,240]</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr"/>
+      <c r="F581" t="inlineStr"/>
+      <c r="G581" t="inlineStr"/>
+      <c r="H581" t="inlineStr"/>
+      <c r="I581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr"/>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title_left_image</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>[48,139][81,196]</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr"/>
+      <c r="F582" t="inlineStr"/>
+      <c r="G582" t="inlineStr"/>
+      <c r="H582" t="inlineStr"/>
+      <c r="I582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr"/>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title_content</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>[432,96][648,240]</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="F583" t="inlineStr"/>
+      <c r="G583" t="inlineStr"/>
+      <c r="H583" t="inlineStr"/>
+      <c r="I583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr"/>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/base_content</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>[0,240][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr"/>
+      <c r="F584" t="inlineStr"/>
+      <c r="G584" t="inlineStr"/>
+      <c r="H584" t="inlineStr"/>
+      <c r="I584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr"/>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/check_phone_first</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>[378,765][702,838]</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr">
+        <is>
+          <t>请先验证邮箱</t>
+        </is>
+      </c>
+      <c r="F585" t="inlineStr"/>
+      <c r="G585" t="inlineStr"/>
+      <c r="H585" t="inlineStr"/>
+      <c r="I585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr"/>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/verify_code_send</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>[96,868][984,983]</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr">
+        <is>
+          <t>验证码发送至登录邮箱chenxi00110011@163.com</t>
+        </is>
+      </c>
+      <c r="F586" t="inlineStr"/>
+      <c r="G586" t="inlineStr"/>
+      <c r="H586" t="inlineStr"/>
+      <c r="I586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr"/>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/et_input_verify_code</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>[132,1108][675,1169]</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr">
+        <is>
+          <t>请输入验证码</t>
+        </is>
+      </c>
+      <c r="F587" t="inlineStr"/>
+      <c r="G587" t="inlineStr"/>
+      <c r="H587" t="inlineStr"/>
+      <c r="I587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr"/>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/logoff_get_verify_code</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>[711,1108][936,1169]</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>获取验证码</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr"/>
+      <c r="G588" t="inlineStr"/>
+      <c r="H588" t="inlineStr"/>
+      <c r="I588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr"/>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/btn_logoff_complete</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>[60,2058][1020,2190]</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr">
+        <is>
+          <t>完成</t>
+        </is>
+      </c>
+      <c r="F589" t="inlineStr"/>
+      <c r="G589" t="inlineStr"/>
+      <c r="H589" t="inlineStr"/>
+      <c r="I589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>注销账号</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr"/>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>com.coloros.smartsidebar:id/roundRectView</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>[1062,600][1080,822]</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr"/>
+      <c r="F590" t="inlineStr"/>
+      <c r="G590" t="inlineStr"/>
+      <c r="H590" t="inlineStr"/>
+      <c r="I590" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/test.xlsx
+++ b/data/test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I590"/>
+  <dimension ref="A1:I832"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13343,6 +13343,5660 @@
       <c r="H590" t="inlineStr"/>
       <c r="I590" t="inlineStr"/>
     </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr"/>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_container</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr"/>
+      <c r="F591" t="inlineStr"/>
+      <c r="G591" t="inlineStr"/>
+      <c r="H591" t="inlineStr"/>
+      <c r="I591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr"/>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr"/>
+      <c r="F592" t="inlineStr"/>
+      <c r="G592" t="inlineStr"/>
+      <c r="H592" t="inlineStr"/>
+      <c r="I592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr"/>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_contents</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr"/>
+      <c r="F593" t="inlineStr"/>
+      <c r="G593" t="inlineStr"/>
+      <c r="H593" t="inlineStr"/>
+      <c r="I593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr"/>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_left_side</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>[69,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr"/>
+      <c r="F594" t="inlineStr"/>
+      <c r="G594" t="inlineStr"/>
+      <c r="H594" t="inlineStr"/>
+      <c r="I594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr"/>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/clock</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>[69,0][181,96]</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="F595" t="inlineStr"/>
+      <c r="G595" t="inlineStr"/>
+      <c r="H595" t="inlineStr"/>
+      <c r="I595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr"/>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr"/>
+      <c r="F596" t="inlineStr"/>
+      <c r="G596" t="inlineStr"/>
+      <c r="H596" t="inlineStr"/>
+      <c r="I596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr"/>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area_inner</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr"/>
+      <c r="F597" t="inlineStr"/>
+      <c r="G597" t="inlineStr"/>
+      <c r="H597" t="inlineStr"/>
+      <c r="I597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr"/>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notificationIcons</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr"/>
+      <c r="F598" t="inlineStr"/>
+      <c r="G598" t="inlineStr"/>
+      <c r="H598" t="inlineStr"/>
+      <c r="I598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr"/>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/cutout_space_view</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>[444,0][636,76]</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr"/>
+      <c r="F599" t="inlineStr"/>
+      <c r="G599" t="inlineStr"/>
+      <c r="H599" t="inlineStr"/>
+      <c r="I599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr"/>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icon_area</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>[636,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr"/>
+      <c r="F600" t="inlineStr"/>
+      <c r="G600" t="inlineStr"/>
+      <c r="H600" t="inlineStr"/>
+      <c r="I600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr"/>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icons</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>[798,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr"/>
+      <c r="F601" t="inlineStr"/>
+      <c r="G601" t="inlineStr"/>
+      <c r="H601" t="inlineStr"/>
+      <c r="I601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr"/>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/statusIcons</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>[798,0][838,96]</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr"/>
+      <c r="F602" t="inlineStr"/>
+      <c r="G602" t="inlineStr"/>
+      <c r="H602" t="inlineStr"/>
+      <c r="I602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr"/>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/signal_cluster</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>[838,0][944,96]</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr"/>
+      <c r="F603" t="inlineStr"/>
+      <c r="G603" t="inlineStr"/>
+      <c r="H603" t="inlineStr"/>
+      <c r="I603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr"/>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_combo</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>[838,30][896,66]</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr"/>
+      <c r="F604" t="inlineStr"/>
+      <c r="G604" t="inlineStr"/>
+      <c r="H604" t="inlineStr"/>
+      <c r="I604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr"/>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_inout</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>[838,30][896,66]</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr"/>
+      <c r="F605" t="inlineStr"/>
+      <c r="G605" t="inlineStr"/>
+      <c r="H605" t="inlineStr"/>
+      <c r="I605" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr"/>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_signal</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>[840,30][896,66]</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr"/>
+      <c r="F606" t="inlineStr"/>
+      <c r="G606" t="inlineStr"/>
+      <c r="H606" t="inlineStr"/>
+      <c r="I606" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr"/>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/no_sims</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>[896,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr"/>
+      <c r="F607" t="inlineStr"/>
+      <c r="G607" t="inlineStr"/>
+      <c r="H607" t="inlineStr"/>
+      <c r="I607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr"/>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>[944,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr"/>
+      <c r="F608" t="inlineStr"/>
+      <c r="G608" t="inlineStr"/>
+      <c r="H608" t="inlineStr"/>
+      <c r="I608" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr"/>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery_content</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr"/>
+      <c r="F609" t="inlineStr"/>
+      <c r="G609" t="inlineStr"/>
+      <c r="H609" t="inlineStr"/>
+      <c r="I609" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr"/>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/stat_battery_view</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr"/>
+      <c r="F610" t="inlineStr"/>
+      <c r="G610" t="inlineStr"/>
+      <c r="H610" t="inlineStr"/>
+      <c r="I610" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr"/>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>com.coloros.smartsidebar:id/roundRectView</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>[1062,600][1080,822]</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr"/>
+      <c r="F611" t="inlineStr"/>
+      <c r="G611" t="inlineStr"/>
+      <c r="H611" t="inlineStr"/>
+      <c r="I611" t="inlineStr"/>
+    </row>
+    <row r="612">
+      <c r="A612" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B612" t="inlineStr"/>
+      <c r="C612" t="inlineStr">
+        <is>
+          <t>android:id/content</t>
+        </is>
+      </c>
+      <c r="D612" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E612" t="inlineStr"/>
+      <c r="F612" t="inlineStr"/>
+      <c r="G612" t="inlineStr"/>
+      <c r="H612" t="inlineStr"/>
+      <c r="I612" t="inlineStr"/>
+    </row>
+    <row r="613">
+      <c r="A613" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B613" t="inlineStr"/>
+      <c r="C613" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/base_layout</t>
+        </is>
+      </c>
+      <c r="D613" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E613" t="inlineStr"/>
+      <c r="F613" t="inlineStr"/>
+      <c r="G613" t="inlineStr"/>
+      <c r="H613" t="inlineStr"/>
+      <c r="I613" t="inlineStr"/>
+    </row>
+    <row r="614">
+      <c r="A614" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B614" t="inlineStr"/>
+      <c r="C614" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title</t>
+        </is>
+      </c>
+      <c r="D614" t="inlineStr">
+        <is>
+          <t>[0,96][1080,240]</t>
+        </is>
+      </c>
+      <c r="E614" t="inlineStr"/>
+      <c r="F614" t="inlineStr"/>
+      <c r="G614" t="inlineStr"/>
+      <c r="H614" t="inlineStr"/>
+      <c r="I614" t="inlineStr"/>
+    </row>
+    <row r="615">
+      <c r="A615" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B615" t="inlineStr"/>
+      <c r="C615" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title_layout</t>
+        </is>
+      </c>
+      <c r="D615" t="inlineStr">
+        <is>
+          <t>[0,96][1080,240]</t>
+        </is>
+      </c>
+      <c r="E615" t="inlineStr"/>
+      <c r="F615" t="inlineStr"/>
+      <c r="G615" t="inlineStr"/>
+      <c r="H615" t="inlineStr"/>
+      <c r="I615" t="inlineStr"/>
+    </row>
+    <row r="616">
+      <c r="A616" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B616" t="inlineStr"/>
+      <c r="C616" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title_left_layout</t>
+        </is>
+      </c>
+      <c r="D616" t="inlineStr">
+        <is>
+          <t>[0,96][129,240]</t>
+        </is>
+      </c>
+      <c r="E616" t="inlineStr"/>
+      <c r="F616" t="inlineStr"/>
+      <c r="G616" t="inlineStr"/>
+      <c r="H616" t="inlineStr"/>
+      <c r="I616" t="inlineStr"/>
+    </row>
+    <row r="617">
+      <c r="A617" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B617" t="inlineStr"/>
+      <c r="C617" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title_left_image</t>
+        </is>
+      </c>
+      <c r="D617" t="inlineStr">
+        <is>
+          <t>[48,139][81,196]</t>
+        </is>
+      </c>
+      <c r="E617" t="inlineStr"/>
+      <c r="F617" t="inlineStr"/>
+      <c r="G617" t="inlineStr"/>
+      <c r="H617" t="inlineStr"/>
+      <c r="I617" t="inlineStr"/>
+    </row>
+    <row r="618">
+      <c r="A618" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B618" t="inlineStr"/>
+      <c r="C618" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/common_title_content</t>
+        </is>
+      </c>
+      <c r="D618" t="inlineStr">
+        <is>
+          <t>[420,96][660,240]</t>
+        </is>
+      </c>
+      <c r="E618" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="F618" t="inlineStr"/>
+      <c r="G618" t="inlineStr"/>
+      <c r="H618" t="inlineStr"/>
+      <c r="I618" t="inlineStr"/>
+    </row>
+    <row r="619">
+      <c r="A619" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B619" t="inlineStr"/>
+      <c r="C619" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/base_content</t>
+        </is>
+      </c>
+      <c r="D619" t="inlineStr">
+        <is>
+          <t>[0,240][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E619" t="inlineStr"/>
+      <c r="F619" t="inlineStr"/>
+      <c r="G619" t="inlineStr"/>
+      <c r="H619" t="inlineStr"/>
+      <c r="I619" t="inlineStr"/>
+    </row>
+    <row r="620">
+      <c r="A620" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B620" t="inlineStr"/>
+      <c r="C620" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_choose</t>
+        </is>
+      </c>
+      <c r="D620" t="inlineStr">
+        <is>
+          <t>[0,240][1080,384]</t>
+        </is>
+      </c>
+      <c r="E620" t="inlineStr"/>
+      <c r="F620" t="inlineStr"/>
+      <c r="G620" t="inlineStr"/>
+      <c r="H620" t="inlineStr"/>
+      <c r="I620" t="inlineStr"/>
+    </row>
+    <row r="621">
+      <c r="A621" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B621" t="inlineStr"/>
+      <c r="C621" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/liveview_choose_title</t>
+        </is>
+      </c>
+      <c r="D621" t="inlineStr">
+        <is>
+          <t>[0,240][1080,384]</t>
+        </is>
+      </c>
+      <c r="E621" t="inlineStr"/>
+      <c r="F621" t="inlineStr"/>
+      <c r="G621" t="inlineStr"/>
+      <c r="H621" t="inlineStr"/>
+      <c r="I621" t="inlineStr"/>
+    </row>
+    <row r="622">
+      <c r="A622" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B622" t="inlineStr"/>
+      <c r="C622" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_share</t>
+        </is>
+      </c>
+      <c r="D622" t="inlineStr">
+        <is>
+          <t>[0,240][540,384]</t>
+        </is>
+      </c>
+      <c r="E622" t="inlineStr">
+        <is>
+          <t>分享给我的设备</t>
+        </is>
+      </c>
+      <c r="F622" t="inlineStr"/>
+      <c r="G622" t="inlineStr"/>
+      <c r="H622" t="inlineStr"/>
+      <c r="I622" t="inlineStr"/>
+    </row>
+    <row r="623">
+      <c r="A623" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B623" t="inlineStr"/>
+      <c r="C623" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_assignment</t>
+        </is>
+      </c>
+      <c r="D623" t="inlineStr">
+        <is>
+          <t>[540,240][1080,384]</t>
+        </is>
+      </c>
+      <c r="E623" t="inlineStr">
+        <is>
+          <t>转让给我的设备</t>
+        </is>
+      </c>
+      <c r="F623" t="inlineStr"/>
+      <c r="G623" t="inlineStr"/>
+      <c r="H623" t="inlineStr"/>
+      <c r="I623" t="inlineStr"/>
+    </row>
+    <row r="624">
+      <c r="A624" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B624" t="inlineStr"/>
+      <c r="C624" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/iv_assignment</t>
+        </is>
+      </c>
+      <c r="D624" t="inlineStr">
+        <is>
+          <t>[1020,255][1065,300]</t>
+        </is>
+      </c>
+      <c r="E624" t="inlineStr"/>
+      <c r="F624" t="inlineStr"/>
+      <c r="G624" t="inlineStr"/>
+      <c r="H624" t="inlineStr"/>
+      <c r="I624" t="inlineStr"/>
+    </row>
+    <row r="625">
+      <c r="A625" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B625" t="inlineStr"/>
+      <c r="C625" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/share_line</t>
+        </is>
+      </c>
+      <c r="D625" t="inlineStr">
+        <is>
+          <t>[210,372][330,384]</t>
+        </is>
+      </c>
+      <c r="E625" t="inlineStr"/>
+      <c r="F625" t="inlineStr"/>
+      <c r="G625" t="inlineStr"/>
+      <c r="H625" t="inlineStr"/>
+      <c r="I625" t="inlineStr"/>
+    </row>
+    <row r="626">
+      <c r="A626" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B626" t="inlineStr"/>
+      <c r="C626" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/view</t>
+        </is>
+      </c>
+      <c r="D626" t="inlineStr">
+        <is>
+          <t>[0,384][1080,414]</t>
+        </is>
+      </c>
+      <c r="E626" t="inlineStr"/>
+      <c r="F626" t="inlineStr"/>
+      <c r="G626" t="inlineStr"/>
+      <c r="H626" t="inlineStr"/>
+      <c r="I626" t="inlineStr"/>
+    </row>
+    <row r="627">
+      <c r="A627" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B627" t="inlineStr"/>
+      <c r="C627" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/content_frame_layout</t>
+        </is>
+      </c>
+      <c r="D627" t="inlineStr">
+        <is>
+          <t>[0,414][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E627" t="inlineStr"/>
+      <c r="F627" t="inlineStr"/>
+      <c r="G627" t="inlineStr"/>
+      <c r="H627" t="inlineStr"/>
+      <c r="I627" t="inlineStr"/>
+    </row>
+    <row r="628">
+      <c r="A628" t="inlineStr">
+        <is>
+          <t>待处理信息</t>
+        </is>
+      </c>
+      <c r="B628" t="inlineStr"/>
+      <c r="C628" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/iv_bg</t>
+        </is>
+      </c>
+      <c r="D628" t="inlineStr">
+        <is>
+          <t>[390,1227][690,1527]</t>
+        </is>
+      </c>
+      <c r="E628" t="inlineStr"/>
+      <c r="F628" t="inlineStr"/>
+      <c r="G628" t="inlineStr"/>
+      <c r="H628" t="inlineStr"/>
+      <c r="I628" t="inlineStr"/>
+    </row>
+    <row r="629">
+      <c r="A629" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B629" t="inlineStr"/>
+      <c r="C629" t="inlineStr">
+        <is>
+          <t>android:id/content</t>
+        </is>
+      </c>
+      <c r="D629" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E629" t="inlineStr"/>
+      <c r="F629" t="inlineStr"/>
+      <c r="G629" t="inlineStr"/>
+      <c r="H629" t="inlineStr"/>
+      <c r="I629" t="inlineStr"/>
+    </row>
+    <row r="630">
+      <c r="A630" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B630" t="inlineStr"/>
+      <c r="C630" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/base_layout</t>
+        </is>
+      </c>
+      <c r="D630" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E630" t="inlineStr"/>
+      <c r="F630" t="inlineStr"/>
+      <c r="G630" t="inlineStr"/>
+      <c r="H630" t="inlineStr"/>
+      <c r="I630" t="inlineStr"/>
+    </row>
+    <row r="631">
+      <c r="A631" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B631" t="inlineStr"/>
+      <c r="C631" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/base_content</t>
+        </is>
+      </c>
+      <c r="D631" t="inlineStr">
+        <is>
+          <t>[0,96][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E631" t="inlineStr"/>
+      <c r="F631" t="inlineStr"/>
+      <c r="G631" t="inlineStr"/>
+      <c r="H631" t="inlineStr"/>
+      <c r="I631" t="inlineStr"/>
+    </row>
+    <row r="632">
+      <c r="A632" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B632" t="inlineStr"/>
+      <c r="C632" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/main_frag_container</t>
+        </is>
+      </c>
+      <c r="D632" t="inlineStr">
+        <is>
+          <t>[0,96][1080,2205]</t>
+        </is>
+      </c>
+      <c r="E632" t="inlineStr"/>
+      <c r="F632" t="inlineStr"/>
+      <c r="G632" t="inlineStr"/>
+      <c r="H632" t="inlineStr"/>
+      <c r="I632" t="inlineStr"/>
+    </row>
+    <row r="633">
+      <c r="A633" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B633" t="inlineStr"/>
+      <c r="C633" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl</t>
+        </is>
+      </c>
+      <c r="D633" t="inlineStr">
+        <is>
+          <t>[0,96][1080,240]</t>
+        </is>
+      </c>
+      <c r="E633" t="inlineStr"/>
+      <c r="F633" t="inlineStr"/>
+      <c r="G633" t="inlineStr"/>
+      <c r="H633" t="inlineStr"/>
+      <c r="I633" t="inlineStr"/>
+    </row>
+    <row r="634">
+      <c r="A634" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B634" t="inlineStr"/>
+      <c r="C634" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/top_tv</t>
+        </is>
+      </c>
+      <c r="D634" t="inlineStr">
+        <is>
+          <t>[45,127][285,208]</t>
+        </is>
+      </c>
+      <c r="E634" t="inlineStr">
+        <is>
+          <t>我的设备</t>
+        </is>
+      </c>
+      <c r="F634" t="inlineStr"/>
+      <c r="G634" t="inlineStr"/>
+      <c r="H634" t="inlineStr"/>
+      <c r="I634" t="inlineStr"/>
+    </row>
+    <row r="635">
+      <c r="A635" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B635" t="inlineStr"/>
+      <c r="C635" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/top_iv_refresh</t>
+        </is>
+      </c>
+      <c r="D635" t="inlineStr">
+        <is>
+          <t>[675,96][765,240]</t>
+        </is>
+      </c>
+      <c r="E635" t="inlineStr"/>
+      <c r="F635" t="inlineStr"/>
+      <c r="G635" t="inlineStr"/>
+      <c r="H635" t="inlineStr"/>
+      <c r="I635" t="inlineStr"/>
+    </row>
+    <row r="636">
+      <c r="A636" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B636" t="inlineStr"/>
+      <c r="C636" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/top_iv_right</t>
+        </is>
+      </c>
+      <c r="D636" t="inlineStr">
+        <is>
+          <t>[810,123][900,213]</t>
+        </is>
+      </c>
+      <c r="E636" t="inlineStr"/>
+      <c r="F636" t="inlineStr"/>
+      <c r="G636" t="inlineStr"/>
+      <c r="H636" t="inlineStr"/>
+      <c r="I636" t="inlineStr"/>
+    </row>
+    <row r="637">
+      <c r="A637" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B637" t="inlineStr"/>
+      <c r="C637" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/top_rl_left</t>
+        </is>
+      </c>
+      <c r="D637" t="inlineStr">
+        <is>
+          <t>[945,96][1035,240]</t>
+        </is>
+      </c>
+      <c r="E637" t="inlineStr"/>
+      <c r="F637" t="inlineStr"/>
+      <c r="G637" t="inlineStr"/>
+      <c r="H637" t="inlineStr"/>
+      <c r="I637" t="inlineStr"/>
+    </row>
+    <row r="638">
+      <c r="A638" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B638" t="inlineStr"/>
+      <c r="C638" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/top_iv_left</t>
+        </is>
+      </c>
+      <c r="D638" t="inlineStr">
+        <is>
+          <t>[945,123][1035,213]</t>
+        </is>
+      </c>
+      <c r="E638" t="inlineStr"/>
+      <c r="F638" t="inlineStr"/>
+      <c r="G638" t="inlineStr"/>
+      <c r="H638" t="inlineStr"/>
+      <c r="I638" t="inlineStr"/>
+    </row>
+    <row r="639">
+      <c r="A639" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B639" t="inlineStr"/>
+      <c r="C639" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/device_refresh_layout</t>
+        </is>
+      </c>
+      <c r="D639" t="inlineStr">
+        <is>
+          <t>[30,270][1050,2205]</t>
+        </is>
+      </c>
+      <c r="E639" t="inlineStr"/>
+      <c r="F639" t="inlineStr"/>
+      <c r="G639" t="inlineStr"/>
+      <c r="H639" t="inlineStr"/>
+      <c r="I639" t="inlineStr"/>
+    </row>
+    <row r="640">
+      <c r="A640" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B640" t="inlineStr"/>
+      <c r="C640" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/device_recycler_view</t>
+        </is>
+      </c>
+      <c r="D640" t="inlineStr">
+        <is>
+          <t>[30,270][1050,2205]</t>
+        </is>
+      </c>
+      <c r="E640" t="inlineStr"/>
+      <c r="F640" t="inlineStr"/>
+      <c r="G640" t="inlineStr"/>
+      <c r="H640" t="inlineStr"/>
+      <c r="I640" t="inlineStr"/>
+    </row>
+    <row r="641">
+      <c r="A641" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B641" t="inlineStr"/>
+      <c r="C641" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_device_titile</t>
+        </is>
+      </c>
+      <c r="D641" t="inlineStr">
+        <is>
+          <t>[30,270][1050,390]</t>
+        </is>
+      </c>
+      <c r="E641" t="inlineStr"/>
+      <c r="F641" t="inlineStr"/>
+      <c r="G641" t="inlineStr"/>
+      <c r="H641" t="inlineStr"/>
+      <c r="I641" t="inlineStr"/>
+    </row>
+    <row r="642">
+      <c r="A642" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B642" t="inlineStr"/>
+      <c r="C642" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/item_device_name</t>
+        </is>
+      </c>
+      <c r="D642" t="inlineStr">
+        <is>
+          <t>[66,297][783,362]</t>
+        </is>
+      </c>
+      <c r="E642" t="inlineStr">
+        <is>
+          <t>000086</t>
+        </is>
+      </c>
+      <c r="F642" t="inlineStr"/>
+      <c r="G642" t="inlineStr"/>
+      <c r="H642" t="inlineStr"/>
+      <c r="I642" t="inlineStr"/>
+    </row>
+    <row r="643">
+      <c r="A643" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B643" t="inlineStr"/>
+      <c r="C643" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll</t>
+        </is>
+      </c>
+      <c r="D643" t="inlineStr">
+        <is>
+          <t>[783,301][1014,358]</t>
+        </is>
+      </c>
+      <c r="E643" t="inlineStr"/>
+      <c r="F643" t="inlineStr"/>
+      <c r="G643" t="inlineStr"/>
+      <c r="H643" t="inlineStr"/>
+      <c r="I643" t="inlineStr"/>
+    </row>
+    <row r="644">
+      <c r="A644" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B644" t="inlineStr"/>
+      <c r="C644" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_main_share</t>
+        </is>
+      </c>
+      <c r="D644" t="inlineStr">
+        <is>
+          <t>[843,301][897,355]</t>
+        </is>
+      </c>
+      <c r="E644" t="inlineStr"/>
+      <c r="F644" t="inlineStr"/>
+      <c r="G644" t="inlineStr"/>
+      <c r="H644" t="inlineStr"/>
+      <c r="I644" t="inlineStr"/>
+    </row>
+    <row r="645">
+      <c r="A645" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B645" t="inlineStr"/>
+      <c r="C645" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/device_set</t>
+        </is>
+      </c>
+      <c r="D645" t="inlineStr">
+        <is>
+          <t>[957,301][1014,358]</t>
+        </is>
+      </c>
+      <c r="E645" t="inlineStr"/>
+      <c r="F645" t="inlineStr"/>
+      <c r="G645" t="inlineStr"/>
+      <c r="H645" t="inlineStr"/>
+      <c r="I645" t="inlineStr"/>
+    </row>
+    <row r="646">
+      <c r="A646" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B646" t="inlineStr"/>
+      <c r="C646" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/item_device_layout</t>
+        </is>
+      </c>
+      <c r="D646" t="inlineStr">
+        <is>
+          <t>[30,390][1050,930]</t>
+        </is>
+      </c>
+      <c r="E646" t="inlineStr"/>
+      <c r="F646" t="inlineStr"/>
+      <c r="G646" t="inlineStr"/>
+      <c r="H646" t="inlineStr"/>
+      <c r="I646" t="inlineStr"/>
+    </row>
+    <row r="647">
+      <c r="A647" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B647" t="inlineStr"/>
+      <c r="C647" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/item_device_snapshot</t>
+        </is>
+      </c>
+      <c r="D647" t="inlineStr">
+        <is>
+          <t>[66,390][1014,930]</t>
+        </is>
+      </c>
+      <c r="E647" t="inlineStr"/>
+      <c r="F647" t="inlineStr"/>
+      <c r="G647" t="inlineStr"/>
+      <c r="H647" t="inlineStr"/>
+      <c r="I647" t="inlineStr"/>
+    </row>
+    <row r="648">
+      <c r="A648" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B648" t="inlineStr"/>
+      <c r="C648" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/item_device_play</t>
+        </is>
+      </c>
+      <c r="D648" t="inlineStr">
+        <is>
+          <t>[481,601][598,718]</t>
+        </is>
+      </c>
+      <c r="E648" t="inlineStr"/>
+      <c r="F648" t="inlineStr"/>
+      <c r="G648" t="inlineStr"/>
+      <c r="H648" t="inlineStr"/>
+      <c r="I648" t="inlineStr"/>
+    </row>
+    <row r="649">
+      <c r="A649" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B649" t="inlineStr"/>
+      <c r="C649" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/item_device_status</t>
+        </is>
+      </c>
+      <c r="D649" t="inlineStr">
+        <is>
+          <t>[90,827][398,900]</t>
+        </is>
+      </c>
+      <c r="E649" t="inlineStr">
+        <is>
+          <t>在线   通道数： 2</t>
+        </is>
+      </c>
+      <c r="F649" t="inlineStr"/>
+      <c r="G649" t="inlineStr"/>
+      <c r="H649" t="inlineStr"/>
+      <c r="I649" t="inlineStr"/>
+    </row>
+    <row r="650">
+      <c r="A650" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B650" t="inlineStr"/>
+      <c r="C650" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/dev_extra_layout</t>
+        </is>
+      </c>
+      <c r="D650" t="inlineStr">
+        <is>
+          <t>[832,816][990,894]</t>
+        </is>
+      </c>
+      <c r="E650" t="inlineStr"/>
+      <c r="F650" t="inlineStr"/>
+      <c r="G650" t="inlineStr"/>
+      <c r="H650" t="inlineStr"/>
+      <c r="I650" t="inlineStr"/>
+    </row>
+    <row r="651">
+      <c r="A651" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B651" t="inlineStr"/>
+      <c r="C651" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_share</t>
+        </is>
+      </c>
+      <c r="D651" t="inlineStr">
+        <is>
+          <t>[904,835][990,894]</t>
+        </is>
+      </c>
+      <c r="E651" t="inlineStr"/>
+      <c r="F651" t="inlineStr"/>
+      <c r="G651" t="inlineStr"/>
+      <c r="H651" t="inlineStr"/>
+      <c r="I651" t="inlineStr"/>
+    </row>
+    <row r="652">
+      <c r="A652" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B652" t="inlineStr"/>
+      <c r="C652" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/iv_share_bg</t>
+        </is>
+      </c>
+      <c r="D652" t="inlineStr">
+        <is>
+          <t>[919,849][949,879]</t>
+        </is>
+      </c>
+      <c r="E652" t="inlineStr"/>
+      <c r="F652" t="inlineStr"/>
+      <c r="G652" t="inlineStr"/>
+      <c r="H652" t="inlineStr"/>
+      <c r="I652" t="inlineStr"/>
+    </row>
+    <row r="653">
+      <c r="A653" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B653" t="inlineStr"/>
+      <c r="C653" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_share_numbers</t>
+        </is>
+      </c>
+      <c r="D653" t="inlineStr">
+        <is>
+          <t>[958,844][975,885]</t>
+        </is>
+      </c>
+      <c r="E653" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F653" t="inlineStr"/>
+      <c r="G653" t="inlineStr"/>
+      <c r="H653" t="inlineStr"/>
+      <c r="I653" t="inlineStr"/>
+    </row>
+    <row r="654">
+      <c r="A654" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B654" t="inlineStr"/>
+      <c r="C654" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_device_set</t>
+        </is>
+      </c>
+      <c r="D654" t="inlineStr">
+        <is>
+          <t>[30,930][1050,1116]</t>
+        </is>
+      </c>
+      <c r="E654" t="inlineStr"/>
+      <c r="F654" t="inlineStr"/>
+      <c r="G654" t="inlineStr"/>
+      <c r="H654" t="inlineStr"/>
+      <c r="I654" t="inlineStr"/>
+    </row>
+    <row r="655">
+      <c r="A655" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B655" t="inlineStr"/>
+      <c r="C655" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_main_message</t>
+        </is>
+      </c>
+      <c r="D655" t="inlineStr">
+        <is>
+          <t>[30,930][285,1116]</t>
+        </is>
+      </c>
+      <c r="E655" t="inlineStr"/>
+      <c r="F655" t="inlineStr"/>
+      <c r="G655" t="inlineStr"/>
+      <c r="H655" t="inlineStr"/>
+      <c r="I655" t="inlineStr"/>
+    </row>
+    <row r="656">
+      <c r="A656" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B656" t="inlineStr"/>
+      <c r="C656" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/iv_msg</t>
+        </is>
+      </c>
+      <c r="D656" t="inlineStr">
+        <is>
+          <t>[130,972][184,1026]</t>
+        </is>
+      </c>
+      <c r="E656" t="inlineStr"/>
+      <c r="F656" t="inlineStr"/>
+      <c r="G656" t="inlineStr"/>
+      <c r="H656" t="inlineStr"/>
+      <c r="I656" t="inlineStr"/>
+    </row>
+    <row r="657">
+      <c r="A657" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B657" t="inlineStr"/>
+      <c r="C657" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_main_cloud_server</t>
+        </is>
+      </c>
+      <c r="D657" t="inlineStr">
+        <is>
+          <t>[285,930][540,1116]</t>
+        </is>
+      </c>
+      <c r="E657" t="inlineStr"/>
+      <c r="F657" t="inlineStr"/>
+      <c r="G657" t="inlineStr"/>
+      <c r="H657" t="inlineStr"/>
+      <c r="I657" t="inlineStr"/>
+    </row>
+    <row r="658">
+      <c r="A658" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B658" t="inlineStr"/>
+      <c r="C658" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/cam_iv_cloud</t>
+        </is>
+      </c>
+      <c r="D658" t="inlineStr">
+        <is>
+          <t>[378,975][447,1026]</t>
+        </is>
+      </c>
+      <c r="E658" t="inlineStr"/>
+      <c r="F658" t="inlineStr"/>
+      <c r="G658" t="inlineStr"/>
+      <c r="H658" t="inlineStr"/>
+      <c r="I658" t="inlineStr"/>
+    </row>
+    <row r="659">
+      <c r="A659" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B659" t="inlineStr"/>
+      <c r="C659" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_playBack</t>
+        </is>
+      </c>
+      <c r="D659" t="inlineStr">
+        <is>
+          <t>[540,930][795,1116]</t>
+        </is>
+      </c>
+      <c r="E659" t="inlineStr"/>
+      <c r="F659" t="inlineStr"/>
+      <c r="G659" t="inlineStr"/>
+      <c r="H659" t="inlineStr"/>
+      <c r="I659" t="inlineStr"/>
+    </row>
+    <row r="660">
+      <c r="A660" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B660" t="inlineStr"/>
+      <c r="C660" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_dev_sets</t>
+        </is>
+      </c>
+      <c r="D660" t="inlineStr">
+        <is>
+          <t>[795,930][1050,1116]</t>
+        </is>
+      </c>
+      <c r="E660" t="inlineStr"/>
+      <c r="F660" t="inlineStr"/>
+      <c r="G660" t="inlineStr"/>
+      <c r="H660" t="inlineStr"/>
+      <c r="I660" t="inlineStr"/>
+    </row>
+    <row r="661">
+      <c r="A661" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B661" t="inlineStr"/>
+      <c r="C661" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_device_titile</t>
+        </is>
+      </c>
+      <c r="D661" t="inlineStr">
+        <is>
+          <t>[30,1152][1050,1272]</t>
+        </is>
+      </c>
+      <c r="E661" t="inlineStr"/>
+      <c r="F661" t="inlineStr"/>
+      <c r="G661" t="inlineStr"/>
+      <c r="H661" t="inlineStr"/>
+      <c r="I661" t="inlineStr"/>
+    </row>
+    <row r="662">
+      <c r="A662" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B662" t="inlineStr"/>
+      <c r="C662" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/item_device_name</t>
+        </is>
+      </c>
+      <c r="D662" t="inlineStr">
+        <is>
+          <t>[66,1179][783,1244]</t>
+        </is>
+      </c>
+      <c r="E662" t="inlineStr">
+        <is>
+          <t>699245</t>
+        </is>
+      </c>
+      <c r="F662" t="inlineStr"/>
+      <c r="G662" t="inlineStr"/>
+      <c r="H662" t="inlineStr"/>
+      <c r="I662" t="inlineStr"/>
+    </row>
+    <row r="663">
+      <c r="A663" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B663" t="inlineStr"/>
+      <c r="C663" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll</t>
+        </is>
+      </c>
+      <c r="D663" t="inlineStr">
+        <is>
+          <t>[783,1183][1014,1240]</t>
+        </is>
+      </c>
+      <c r="E663" t="inlineStr"/>
+      <c r="F663" t="inlineStr"/>
+      <c r="G663" t="inlineStr"/>
+      <c r="H663" t="inlineStr"/>
+      <c r="I663" t="inlineStr"/>
+    </row>
+    <row r="664">
+      <c r="A664" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B664" t="inlineStr"/>
+      <c r="C664" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_main_share</t>
+        </is>
+      </c>
+      <c r="D664" t="inlineStr">
+        <is>
+          <t>[843,1183][897,1237]</t>
+        </is>
+      </c>
+      <c r="E664" t="inlineStr"/>
+      <c r="F664" t="inlineStr"/>
+      <c r="G664" t="inlineStr"/>
+      <c r="H664" t="inlineStr"/>
+      <c r="I664" t="inlineStr"/>
+    </row>
+    <row r="665">
+      <c r="A665" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B665" t="inlineStr"/>
+      <c r="C665" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/device_set</t>
+        </is>
+      </c>
+      <c r="D665" t="inlineStr">
+        <is>
+          <t>[957,1183][1014,1240]</t>
+        </is>
+      </c>
+      <c r="E665" t="inlineStr"/>
+      <c r="F665" t="inlineStr"/>
+      <c r="G665" t="inlineStr"/>
+      <c r="H665" t="inlineStr"/>
+      <c r="I665" t="inlineStr"/>
+    </row>
+    <row r="666">
+      <c r="A666" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B666" t="inlineStr"/>
+      <c r="C666" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/item_device_layout</t>
+        </is>
+      </c>
+      <c r="D666" t="inlineStr">
+        <is>
+          <t>[30,1272][1050,1812]</t>
+        </is>
+      </c>
+      <c r="E666" t="inlineStr"/>
+      <c r="F666" t="inlineStr"/>
+      <c r="G666" t="inlineStr"/>
+      <c r="H666" t="inlineStr"/>
+      <c r="I666" t="inlineStr"/>
+    </row>
+    <row r="667">
+      <c r="A667" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B667" t="inlineStr"/>
+      <c r="C667" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/item_device_snapshot</t>
+        </is>
+      </c>
+      <c r="D667" t="inlineStr">
+        <is>
+          <t>[66,1272][1014,1812]</t>
+        </is>
+      </c>
+      <c r="E667" t="inlineStr"/>
+      <c r="F667" t="inlineStr"/>
+      <c r="G667" t="inlineStr"/>
+      <c r="H667" t="inlineStr"/>
+      <c r="I667" t="inlineStr"/>
+    </row>
+    <row r="668">
+      <c r="A668" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B668" t="inlineStr"/>
+      <c r="C668" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/item_device_play</t>
+        </is>
+      </c>
+      <c r="D668" t="inlineStr">
+        <is>
+          <t>[481,1483][598,1600]</t>
+        </is>
+      </c>
+      <c r="E668" t="inlineStr"/>
+      <c r="F668" t="inlineStr"/>
+      <c r="G668" t="inlineStr"/>
+      <c r="H668" t="inlineStr"/>
+      <c r="I668" t="inlineStr"/>
+    </row>
+    <row r="669">
+      <c r="A669" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B669" t="inlineStr"/>
+      <c r="C669" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/item_device_status</t>
+        </is>
+      </c>
+      <c r="D669" t="inlineStr">
+        <is>
+          <t>[90,1709][398,1782]</t>
+        </is>
+      </c>
+      <c r="E669" t="inlineStr">
+        <is>
+          <t>在线   通道数： 2</t>
+        </is>
+      </c>
+      <c r="F669" t="inlineStr"/>
+      <c r="G669" t="inlineStr"/>
+      <c r="H669" t="inlineStr"/>
+      <c r="I669" t="inlineStr"/>
+    </row>
+    <row r="670">
+      <c r="A670" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B670" t="inlineStr"/>
+      <c r="C670" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/dev_extra_layout</t>
+        </is>
+      </c>
+      <c r="D670" t="inlineStr">
+        <is>
+          <t>[832,1698][990,1776]</t>
+        </is>
+      </c>
+      <c r="E670" t="inlineStr"/>
+      <c r="F670" t="inlineStr"/>
+      <c r="G670" t="inlineStr"/>
+      <c r="H670" t="inlineStr"/>
+      <c r="I670" t="inlineStr"/>
+    </row>
+    <row r="671">
+      <c r="A671" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B671" t="inlineStr"/>
+      <c r="C671" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_share</t>
+        </is>
+      </c>
+      <c r="D671" t="inlineStr">
+        <is>
+          <t>[904,1717][990,1776]</t>
+        </is>
+      </c>
+      <c r="E671" t="inlineStr"/>
+      <c r="F671" t="inlineStr"/>
+      <c r="G671" t="inlineStr"/>
+      <c r="H671" t="inlineStr"/>
+      <c r="I671" t="inlineStr"/>
+    </row>
+    <row r="672">
+      <c r="A672" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B672" t="inlineStr"/>
+      <c r="C672" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/iv_share_bg</t>
+        </is>
+      </c>
+      <c r="D672" t="inlineStr">
+        <is>
+          <t>[919,1731][949,1761]</t>
+        </is>
+      </c>
+      <c r="E672" t="inlineStr"/>
+      <c r="F672" t="inlineStr"/>
+      <c r="G672" t="inlineStr"/>
+      <c r="H672" t="inlineStr"/>
+      <c r="I672" t="inlineStr"/>
+    </row>
+    <row r="673">
+      <c r="A673" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B673" t="inlineStr"/>
+      <c r="C673" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_share_numbers</t>
+        </is>
+      </c>
+      <c r="D673" t="inlineStr">
+        <is>
+          <t>[958,1726][975,1767]</t>
+        </is>
+      </c>
+      <c r="E673" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F673" t="inlineStr"/>
+      <c r="G673" t="inlineStr"/>
+      <c r="H673" t="inlineStr"/>
+      <c r="I673" t="inlineStr"/>
+    </row>
+    <row r="674">
+      <c r="A674" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B674" t="inlineStr"/>
+      <c r="C674" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_device_set</t>
+        </is>
+      </c>
+      <c r="D674" t="inlineStr">
+        <is>
+          <t>[30,1812][1050,1998]</t>
+        </is>
+      </c>
+      <c r="E674" t="inlineStr"/>
+      <c r="F674" t="inlineStr"/>
+      <c r="G674" t="inlineStr"/>
+      <c r="H674" t="inlineStr"/>
+      <c r="I674" t="inlineStr"/>
+    </row>
+    <row r="675">
+      <c r="A675" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr"/>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_main_message</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>[30,1812][285,1998]</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr"/>
+      <c r="F675" t="inlineStr"/>
+      <c r="G675" t="inlineStr"/>
+      <c r="H675" t="inlineStr"/>
+      <c r="I675" t="inlineStr"/>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B676" t="inlineStr"/>
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/iv_msg</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>[130,1854][184,1908]</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr"/>
+      <c r="F676" t="inlineStr"/>
+      <c r="G676" t="inlineStr"/>
+      <c r="H676" t="inlineStr"/>
+      <c r="I676" t="inlineStr"/>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr"/>
+      <c r="C677" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_main_cloud_server</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>[285,1812][540,1998]</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr"/>
+      <c r="F677" t="inlineStr"/>
+      <c r="G677" t="inlineStr"/>
+      <c r="H677" t="inlineStr"/>
+      <c r="I677" t="inlineStr"/>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr"/>
+      <c r="C678" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/cam_iv_cloud</t>
+        </is>
+      </c>
+      <c r="D678" t="inlineStr">
+        <is>
+          <t>[378,1857][447,1908]</t>
+        </is>
+      </c>
+      <c r="E678" t="inlineStr"/>
+      <c r="F678" t="inlineStr"/>
+      <c r="G678" t="inlineStr"/>
+      <c r="H678" t="inlineStr"/>
+      <c r="I678" t="inlineStr"/>
+    </row>
+    <row r="679">
+      <c r="A679" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B679" t="inlineStr"/>
+      <c r="C679" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/iv_cloud_free</t>
+        </is>
+      </c>
+      <c r="D679" t="inlineStr">
+        <is>
+          <t>[429,1836][513,1878]</t>
+        </is>
+      </c>
+      <c r="E679" t="inlineStr"/>
+      <c r="F679" t="inlineStr"/>
+      <c r="G679" t="inlineStr"/>
+      <c r="H679" t="inlineStr"/>
+      <c r="I679" t="inlineStr"/>
+    </row>
+    <row r="680">
+      <c r="A680" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B680" t="inlineStr"/>
+      <c r="C680" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_playBack</t>
+        </is>
+      </c>
+      <c r="D680" t="inlineStr">
+        <is>
+          <t>[540,1812][795,1998]</t>
+        </is>
+      </c>
+      <c r="E680" t="inlineStr"/>
+      <c r="F680" t="inlineStr"/>
+      <c r="G680" t="inlineStr"/>
+      <c r="H680" t="inlineStr"/>
+      <c r="I680" t="inlineStr"/>
+    </row>
+    <row r="681">
+      <c r="A681" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B681" t="inlineStr"/>
+      <c r="C681" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll_dev_sets</t>
+        </is>
+      </c>
+      <c r="D681" t="inlineStr">
+        <is>
+          <t>[795,1812][1050,1998]</t>
+        </is>
+      </c>
+      <c r="E681" t="inlineStr"/>
+      <c r="F681" t="inlineStr"/>
+      <c r="G681" t="inlineStr"/>
+      <c r="H681" t="inlineStr"/>
+      <c r="I681" t="inlineStr"/>
+    </row>
+    <row r="682">
+      <c r="A682" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B682" t="inlineStr"/>
+      <c r="C682" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_device_titile</t>
+        </is>
+      </c>
+      <c r="D682" t="inlineStr">
+        <is>
+          <t>[30,2034][1050,2154]</t>
+        </is>
+      </c>
+      <c r="E682" t="inlineStr"/>
+      <c r="F682" t="inlineStr"/>
+      <c r="G682" t="inlineStr"/>
+      <c r="H682" t="inlineStr"/>
+      <c r="I682" t="inlineStr"/>
+    </row>
+    <row r="683">
+      <c r="A683" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B683" t="inlineStr"/>
+      <c r="C683" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/item_device_name</t>
+        </is>
+      </c>
+      <c r="D683" t="inlineStr">
+        <is>
+          <t>[66,2061][897,2126]</t>
+        </is>
+      </c>
+      <c r="E683" t="inlineStr">
+        <is>
+          <t>432843</t>
+        </is>
+      </c>
+      <c r="F683" t="inlineStr"/>
+      <c r="G683" t="inlineStr"/>
+      <c r="H683" t="inlineStr"/>
+      <c r="I683" t="inlineStr"/>
+    </row>
+    <row r="684">
+      <c r="A684" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B684" t="inlineStr"/>
+      <c r="C684" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/ll</t>
+        </is>
+      </c>
+      <c r="D684" t="inlineStr">
+        <is>
+          <t>[897,2065][1014,2122]</t>
+        </is>
+      </c>
+      <c r="E684" t="inlineStr"/>
+      <c r="F684" t="inlineStr"/>
+      <c r="G684" t="inlineStr"/>
+      <c r="H684" t="inlineStr"/>
+      <c r="I684" t="inlineStr"/>
+    </row>
+    <row r="685">
+      <c r="A685" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B685" t="inlineStr"/>
+      <c r="C685" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/device_set</t>
+        </is>
+      </c>
+      <c r="D685" t="inlineStr">
+        <is>
+          <t>[957,2065][1014,2122]</t>
+        </is>
+      </c>
+      <c r="E685" t="inlineStr"/>
+      <c r="F685" t="inlineStr"/>
+      <c r="G685" t="inlineStr"/>
+      <c r="H685" t="inlineStr"/>
+      <c r="I685" t="inlineStr"/>
+    </row>
+    <row r="686">
+      <c r="A686" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B686" t="inlineStr"/>
+      <c r="C686" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/item_device_layout</t>
+        </is>
+      </c>
+      <c r="D686" t="inlineStr">
+        <is>
+          <t>[30,2154][1050,2205]</t>
+        </is>
+      </c>
+      <c r="E686" t="inlineStr"/>
+      <c r="F686" t="inlineStr"/>
+      <c r="G686" t="inlineStr"/>
+      <c r="H686" t="inlineStr"/>
+      <c r="I686" t="inlineStr"/>
+    </row>
+    <row r="687">
+      <c r="A687" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B687" t="inlineStr"/>
+      <c r="C687" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/item_device_snapshot</t>
+        </is>
+      </c>
+      <c r="D687" t="inlineStr">
+        <is>
+          <t>[66,2154][1014,2205]</t>
+        </is>
+      </c>
+      <c r="E687" t="inlineStr"/>
+      <c r="F687" t="inlineStr"/>
+      <c r="G687" t="inlineStr"/>
+      <c r="H687" t="inlineStr"/>
+      <c r="I687" t="inlineStr"/>
+    </row>
+    <row r="688">
+      <c r="A688" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B688" t="inlineStr"/>
+      <c r="C688" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/dev_offline_layout</t>
+        </is>
+      </c>
+      <c r="D688" t="inlineStr">
+        <is>
+          <t>[66,2154][1014,2205]</t>
+        </is>
+      </c>
+      <c r="E688" t="inlineStr"/>
+      <c r="F688" t="inlineStr"/>
+      <c r="G688" t="inlineStr"/>
+      <c r="H688" t="inlineStr"/>
+      <c r="I688" t="inlineStr"/>
+    </row>
+    <row r="689">
+      <c r="A689" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B689" t="inlineStr"/>
+      <c r="C689" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/main_btm_view</t>
+        </is>
+      </c>
+      <c r="D689" t="inlineStr">
+        <is>
+          <t>[0,2199][1080,2205]</t>
+        </is>
+      </c>
+      <c r="E689" t="inlineStr"/>
+      <c r="F689" t="inlineStr"/>
+      <c r="G689" t="inlineStr"/>
+      <c r="H689" t="inlineStr"/>
+      <c r="I689" t="inlineStr"/>
+    </row>
+    <row r="690">
+      <c r="A690" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B690" t="inlineStr"/>
+      <c r="C690" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/main_btm_layout</t>
+        </is>
+      </c>
+      <c r="D690" t="inlineStr">
+        <is>
+          <t>[0,2205][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E690" t="inlineStr"/>
+      <c r="F690" t="inlineStr"/>
+      <c r="G690" t="inlineStr"/>
+      <c r="H690" t="inlineStr"/>
+      <c r="I690" t="inlineStr"/>
+    </row>
+    <row r="691">
+      <c r="A691" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B691" t="inlineStr"/>
+      <c r="C691" t="inlineStr">
+        <is>
+          <t>com.coloros.smartsidebar:id/roundRectView</t>
+        </is>
+      </c>
+      <c r="D691" t="inlineStr">
+        <is>
+          <t>[1062,600][1080,822]</t>
+        </is>
+      </c>
+      <c r="E691" t="inlineStr"/>
+      <c r="F691" t="inlineStr"/>
+      <c r="G691" t="inlineStr"/>
+      <c r="H691" t="inlineStr"/>
+      <c r="I691" t="inlineStr"/>
+    </row>
+    <row r="692">
+      <c r="A692" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B692" t="inlineStr"/>
+      <c r="C692" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_container</t>
+        </is>
+      </c>
+      <c r="D692" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E692" t="inlineStr"/>
+      <c r="F692" t="inlineStr"/>
+      <c r="G692" t="inlineStr"/>
+      <c r="H692" t="inlineStr"/>
+      <c r="I692" t="inlineStr"/>
+    </row>
+    <row r="693">
+      <c r="A693" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B693" t="inlineStr"/>
+      <c r="C693" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar</t>
+        </is>
+      </c>
+      <c r="D693" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E693" t="inlineStr"/>
+      <c r="F693" t="inlineStr"/>
+      <c r="G693" t="inlineStr"/>
+      <c r="H693" t="inlineStr"/>
+      <c r="I693" t="inlineStr"/>
+    </row>
+    <row r="694">
+      <c r="A694" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B694" t="inlineStr"/>
+      <c r="C694" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_contents</t>
+        </is>
+      </c>
+      <c r="D694" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E694" t="inlineStr"/>
+      <c r="F694" t="inlineStr"/>
+      <c r="G694" t="inlineStr"/>
+      <c r="H694" t="inlineStr"/>
+      <c r="I694" t="inlineStr"/>
+    </row>
+    <row r="695">
+      <c r="A695" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B695" t="inlineStr"/>
+      <c r="C695" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_left_side</t>
+        </is>
+      </c>
+      <c r="D695" t="inlineStr">
+        <is>
+          <t>[69,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E695" t="inlineStr"/>
+      <c r="F695" t="inlineStr"/>
+      <c r="G695" t="inlineStr"/>
+      <c r="H695" t="inlineStr"/>
+      <c r="I695" t="inlineStr"/>
+    </row>
+    <row r="696">
+      <c r="A696" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B696" t="inlineStr"/>
+      <c r="C696" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/clock</t>
+        </is>
+      </c>
+      <c r="D696" t="inlineStr">
+        <is>
+          <t>[69,0][181,96]</t>
+        </is>
+      </c>
+      <c r="E696" t="inlineStr">
+        <is>
+          <t>10:54</t>
+        </is>
+      </c>
+      <c r="F696" t="inlineStr"/>
+      <c r="G696" t="inlineStr"/>
+      <c r="H696" t="inlineStr"/>
+      <c r="I696" t="inlineStr"/>
+    </row>
+    <row r="697">
+      <c r="A697" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B697" t="inlineStr"/>
+      <c r="C697" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area</t>
+        </is>
+      </c>
+      <c r="D697" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E697" t="inlineStr"/>
+      <c r="F697" t="inlineStr"/>
+      <c r="G697" t="inlineStr"/>
+      <c r="H697" t="inlineStr"/>
+      <c r="I697" t="inlineStr"/>
+    </row>
+    <row r="698">
+      <c r="A698" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B698" t="inlineStr"/>
+      <c r="C698" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area_inner</t>
+        </is>
+      </c>
+      <c r="D698" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E698" t="inlineStr"/>
+      <c r="F698" t="inlineStr"/>
+      <c r="G698" t="inlineStr"/>
+      <c r="H698" t="inlineStr"/>
+      <c r="I698" t="inlineStr"/>
+    </row>
+    <row r="699">
+      <c r="A699" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B699" t="inlineStr"/>
+      <c r="C699" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notificationIcons</t>
+        </is>
+      </c>
+      <c r="D699" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E699" t="inlineStr"/>
+      <c r="F699" t="inlineStr"/>
+      <c r="G699" t="inlineStr"/>
+      <c r="H699" t="inlineStr"/>
+      <c r="I699" t="inlineStr"/>
+    </row>
+    <row r="700">
+      <c r="A700" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B700" t="inlineStr"/>
+      <c r="C700" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/cutout_space_view</t>
+        </is>
+      </c>
+      <c r="D700" t="inlineStr">
+        <is>
+          <t>[444,0][636,76]</t>
+        </is>
+      </c>
+      <c r="E700" t="inlineStr"/>
+      <c r="F700" t="inlineStr"/>
+      <c r="G700" t="inlineStr"/>
+      <c r="H700" t="inlineStr"/>
+      <c r="I700" t="inlineStr"/>
+    </row>
+    <row r="701">
+      <c r="A701" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B701" t="inlineStr"/>
+      <c r="C701" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icon_area</t>
+        </is>
+      </c>
+      <c r="D701" t="inlineStr">
+        <is>
+          <t>[636,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E701" t="inlineStr"/>
+      <c r="F701" t="inlineStr"/>
+      <c r="G701" t="inlineStr"/>
+      <c r="H701" t="inlineStr"/>
+      <c r="I701" t="inlineStr"/>
+    </row>
+    <row r="702">
+      <c r="A702" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B702" t="inlineStr"/>
+      <c r="C702" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icons</t>
+        </is>
+      </c>
+      <c r="D702" t="inlineStr">
+        <is>
+          <t>[665,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E702" t="inlineStr"/>
+      <c r="F702" t="inlineStr"/>
+      <c r="G702" t="inlineStr"/>
+      <c r="H702" t="inlineStr"/>
+      <c r="I702" t="inlineStr"/>
+    </row>
+    <row r="703">
+      <c r="A703" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B703" t="inlineStr"/>
+      <c r="C703" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/statusIcons</t>
+        </is>
+      </c>
+      <c r="D703" t="inlineStr">
+        <is>
+          <t>[665,0][705,96]</t>
+        </is>
+      </c>
+      <c r="E703" t="inlineStr"/>
+      <c r="F703" t="inlineStr"/>
+      <c r="G703" t="inlineStr"/>
+      <c r="H703" t="inlineStr"/>
+      <c r="I703" t="inlineStr"/>
+    </row>
+    <row r="704">
+      <c r="A704" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B704" t="inlineStr"/>
+      <c r="C704" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/signal_cluster</t>
+        </is>
+      </c>
+      <c r="D704" t="inlineStr">
+        <is>
+          <t>[705,0][944,96]</t>
+        </is>
+      </c>
+      <c r="E704" t="inlineStr"/>
+      <c r="F704" t="inlineStr"/>
+      <c r="G704" t="inlineStr"/>
+      <c r="H704" t="inlineStr"/>
+      <c r="I704" t="inlineStr"/>
+    </row>
+    <row r="705">
+      <c r="A705" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B705" t="inlineStr"/>
+      <c r="C705" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_combo</t>
+        </is>
+      </c>
+      <c r="D705" t="inlineStr">
+        <is>
+          <t>[705,30][763,66]</t>
+        </is>
+      </c>
+      <c r="E705" t="inlineStr"/>
+      <c r="F705" t="inlineStr"/>
+      <c r="G705" t="inlineStr"/>
+      <c r="H705" t="inlineStr"/>
+      <c r="I705" t="inlineStr"/>
+    </row>
+    <row r="706">
+      <c r="A706" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B706" t="inlineStr"/>
+      <c r="C706" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_inout</t>
+        </is>
+      </c>
+      <c r="D706" t="inlineStr">
+        <is>
+          <t>[705,30][763,66]</t>
+        </is>
+      </c>
+      <c r="E706" t="inlineStr"/>
+      <c r="F706" t="inlineStr"/>
+      <c r="G706" t="inlineStr"/>
+      <c r="H706" t="inlineStr"/>
+      <c r="I706" t="inlineStr"/>
+    </row>
+    <row r="707">
+      <c r="A707" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B707" t="inlineStr"/>
+      <c r="C707" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_signal</t>
+        </is>
+      </c>
+      <c r="D707" t="inlineStr">
+        <is>
+          <t>[707,30][763,66]</t>
+        </is>
+      </c>
+      <c r="E707" t="inlineStr"/>
+      <c r="F707" t="inlineStr"/>
+      <c r="G707" t="inlineStr"/>
+      <c r="H707" t="inlineStr"/>
+      <c r="I707" t="inlineStr"/>
+    </row>
+    <row r="708">
+      <c r="A708" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr"/>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/volte_imag</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>[763,30][820,66]</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr"/>
+      <c r="F708" t="inlineStr"/>
+      <c r="G708" t="inlineStr"/>
+      <c r="H708" t="inlineStr"/>
+      <c r="I708" t="inlineStr"/>
+    </row>
+    <row r="709">
+      <c r="A709" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr"/>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_signal_group</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>[820,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr"/>
+      <c r="F709" t="inlineStr"/>
+      <c r="G709" t="inlineStr"/>
+      <c r="H709" t="inlineStr"/>
+      <c r="I709" t="inlineStr"/>
+    </row>
+    <row r="710">
+      <c r="A710" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr"/>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_combo</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>[820,30][882,66]</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr"/>
+      <c r="F710" t="inlineStr"/>
+      <c r="G710" t="inlineStr"/>
+      <c r="H710" t="inlineStr"/>
+      <c r="I710" t="inlineStr"/>
+    </row>
+    <row r="711">
+      <c r="A711" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr"/>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_type</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>[820,30][882,66]</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr"/>
+      <c r="F711" t="inlineStr"/>
+      <c r="G711" t="inlineStr"/>
+      <c r="H711" t="inlineStr"/>
+      <c r="I711" t="inlineStr"/>
+    </row>
+    <row r="712">
+      <c r="A712" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr"/>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_signal</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>[826,30][882,66]</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr"/>
+      <c r="F712" t="inlineStr"/>
+      <c r="G712" t="inlineStr"/>
+      <c r="H712" t="inlineStr"/>
+      <c r="I712" t="inlineStr"/>
+    </row>
+    <row r="713">
+      <c r="A713" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr"/>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_combo</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>[882,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr"/>
+      <c r="F713" t="inlineStr"/>
+      <c r="G713" t="inlineStr"/>
+      <c r="H713" t="inlineStr"/>
+      <c r="I713" t="inlineStr"/>
+    </row>
+    <row r="714">
+      <c r="A714" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr"/>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_type</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>[882,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr"/>
+      <c r="F714" t="inlineStr"/>
+      <c r="G714" t="inlineStr"/>
+      <c r="H714" t="inlineStr"/>
+      <c r="I714" t="inlineStr"/>
+    </row>
+    <row r="715">
+      <c r="A715" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr"/>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_signal</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>[888,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr"/>
+      <c r="F715" t="inlineStr"/>
+      <c r="G715" t="inlineStr"/>
+      <c r="H715" t="inlineStr"/>
+      <c r="I715" t="inlineStr"/>
+    </row>
+    <row r="716">
+      <c r="A716" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr"/>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>[944,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr"/>
+      <c r="F716" t="inlineStr"/>
+      <c r="G716" t="inlineStr"/>
+      <c r="H716" t="inlineStr"/>
+      <c r="I716" t="inlineStr"/>
+    </row>
+    <row r="717">
+      <c r="A717" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr"/>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery_content</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr"/>
+      <c r="F717" t="inlineStr"/>
+      <c r="G717" t="inlineStr"/>
+      <c r="H717" t="inlineStr"/>
+      <c r="I717" t="inlineStr"/>
+    </row>
+    <row r="718">
+      <c r="A718" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B718" t="inlineStr"/>
+      <c r="C718" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/stat_battery_view</t>
+        </is>
+      </c>
+      <c r="D718" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E718" t="inlineStr"/>
+      <c r="F718" t="inlineStr"/>
+      <c r="G718" t="inlineStr"/>
+      <c r="H718" t="inlineStr"/>
+      <c r="I718" t="inlineStr"/>
+    </row>
+    <row r="719">
+      <c r="A719" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B719" t="inlineStr"/>
+      <c r="C719" t="inlineStr">
+        <is>
+          <t>android:id/content</t>
+        </is>
+      </c>
+      <c r="D719" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E719" t="inlineStr"/>
+      <c r="F719" t="inlineStr"/>
+      <c r="G719" t="inlineStr"/>
+      <c r="H719" t="inlineStr"/>
+      <c r="I719" t="inlineStr"/>
+    </row>
+    <row r="720">
+      <c r="A720" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B720" t="inlineStr"/>
+      <c r="C720" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/base_layout</t>
+        </is>
+      </c>
+      <c r="D720" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E720" t="inlineStr"/>
+      <c r="F720" t="inlineStr"/>
+      <c r="G720" t="inlineStr"/>
+      <c r="H720" t="inlineStr"/>
+      <c r="I720" t="inlineStr"/>
+    </row>
+    <row r="721">
+      <c r="A721" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B721" t="inlineStr"/>
+      <c r="C721" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/base_content</t>
+        </is>
+      </c>
+      <c r="D721" t="inlineStr">
+        <is>
+          <t>[0,96][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E721" t="inlineStr"/>
+      <c r="F721" t="inlineStr"/>
+      <c r="G721" t="inlineStr"/>
+      <c r="H721" t="inlineStr"/>
+      <c r="I721" t="inlineStr"/>
+    </row>
+    <row r="722">
+      <c r="A722" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B722" t="inlineStr"/>
+      <c r="C722" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/fl_portait</t>
+        </is>
+      </c>
+      <c r="D722" t="inlineStr">
+        <is>
+          <t>[0,96][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E722" t="inlineStr"/>
+      <c r="F722" t="inlineStr"/>
+      <c r="G722" t="inlineStr"/>
+      <c r="H722" t="inlineStr"/>
+      <c r="I722" t="inlineStr"/>
+    </row>
+    <row r="723">
+      <c r="A723" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B723" t="inlineStr"/>
+      <c r="C723" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_status</t>
+        </is>
+      </c>
+      <c r="D723" t="inlineStr">
+        <is>
+          <t>[0,96][1080,246]</t>
+        </is>
+      </c>
+      <c r="E723" t="inlineStr"/>
+      <c r="F723" t="inlineStr"/>
+      <c r="G723" t="inlineStr"/>
+      <c r="H723" t="inlineStr"/>
+      <c r="I723" t="inlineStr"/>
+    </row>
+    <row r="724">
+      <c r="A724" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B724" t="inlineStr"/>
+      <c r="C724" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/btn_back</t>
+        </is>
+      </c>
+      <c r="D724" t="inlineStr">
+        <is>
+          <t>[0,106][105,235]</t>
+        </is>
+      </c>
+      <c r="E724" t="inlineStr"/>
+      <c r="F724" t="inlineStr"/>
+      <c r="G724" t="inlineStr"/>
+      <c r="H724" t="inlineStr"/>
+      <c r="I724" t="inlineStr"/>
+    </row>
+    <row r="725">
+      <c r="A725" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B725" t="inlineStr"/>
+      <c r="C725" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_obs</t>
+        </is>
+      </c>
+      <c r="D725" t="inlineStr">
+        <is>
+          <t>[459,134][621,207]</t>
+        </is>
+      </c>
+      <c r="E725" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="F725" t="inlineStr"/>
+      <c r="G725" t="inlineStr"/>
+      <c r="H725" t="inlineStr"/>
+      <c r="I725" t="inlineStr"/>
+    </row>
+    <row r="726">
+      <c r="A726" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B726" t="inlineStr"/>
+      <c r="C726" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_layout</t>
+        </is>
+      </c>
+      <c r="D726" t="inlineStr">
+        <is>
+          <t>[0,246][1080,1378]</t>
+        </is>
+      </c>
+      <c r="E726" t="inlineStr"/>
+      <c r="F726" t="inlineStr"/>
+      <c r="G726" t="inlineStr"/>
+      <c r="H726" t="inlineStr"/>
+      <c r="I726" t="inlineStr"/>
+    </row>
+    <row r="727">
+      <c r="A727" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B727" t="inlineStr"/>
+      <c r="C727" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/liner_control</t>
+        </is>
+      </c>
+      <c r="D727" t="inlineStr">
+        <is>
+          <t>[0,1378][1080,1558]</t>
+        </is>
+      </c>
+      <c r="E727" t="inlineStr"/>
+      <c r="F727" t="inlineStr"/>
+      <c r="G727" t="inlineStr"/>
+      <c r="H727" t="inlineStr"/>
+      <c r="I727" t="inlineStr"/>
+    </row>
+    <row r="728">
+      <c r="A728" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B728" t="inlineStr"/>
+      <c r="C728" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_sound</t>
+        </is>
+      </c>
+      <c r="D728" t="inlineStr">
+        <is>
+          <t>[0,1381][270,1555]</t>
+        </is>
+      </c>
+      <c r="E728" t="inlineStr"/>
+      <c r="F728" t="inlineStr"/>
+      <c r="G728" t="inlineStr"/>
+      <c r="H728" t="inlineStr"/>
+      <c r="I728" t="inlineStr"/>
+    </row>
+    <row r="729">
+      <c r="A729" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B729" t="inlineStr"/>
+      <c r="C729" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_play</t>
+        </is>
+      </c>
+      <c r="D729" t="inlineStr">
+        <is>
+          <t>[270,1378][540,1558]</t>
+        </is>
+      </c>
+      <c r="E729" t="inlineStr"/>
+      <c r="F729" t="inlineStr"/>
+      <c r="G729" t="inlineStr"/>
+      <c r="H729" t="inlineStr"/>
+      <c r="I729" t="inlineStr"/>
+    </row>
+    <row r="730">
+      <c r="A730" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B730" t="inlineStr"/>
+      <c r="C730" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_photo</t>
+        </is>
+      </c>
+      <c r="D730" t="inlineStr">
+        <is>
+          <t>[540,1381][810,1555]</t>
+        </is>
+      </c>
+      <c r="E730" t="inlineStr"/>
+      <c r="F730" t="inlineStr"/>
+      <c r="G730" t="inlineStr"/>
+      <c r="H730" t="inlineStr"/>
+      <c r="I730" t="inlineStr"/>
+    </row>
+    <row r="731">
+      <c r="A731" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B731" t="inlineStr"/>
+      <c r="C731" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_full_screen</t>
+        </is>
+      </c>
+      <c r="D731" t="inlineStr">
+        <is>
+          <t>[810,1378][1080,1558]</t>
+        </is>
+      </c>
+      <c r="E731" t="inlineStr"/>
+      <c r="F731" t="inlineStr"/>
+      <c r="G731" t="inlineStr"/>
+      <c r="H731" t="inlineStr"/>
+      <c r="I731" t="inlineStr"/>
+    </row>
+    <row r="732">
+      <c r="A732" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B732" t="inlineStr"/>
+      <c r="C732" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/liner_time</t>
+        </is>
+      </c>
+      <c r="D732" t="inlineStr">
+        <is>
+          <t>[0,1558][1080,1735]</t>
+        </is>
+      </c>
+      <c r="E732" t="inlineStr"/>
+      <c r="F732" t="inlineStr"/>
+      <c r="G732" t="inlineStr"/>
+      <c r="H732" t="inlineStr"/>
+      <c r="I732" t="inlineStr"/>
+    </row>
+    <row r="733">
+      <c r="A733" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B733" t="inlineStr"/>
+      <c r="C733" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_record</t>
+        </is>
+      </c>
+      <c r="D733" t="inlineStr">
+        <is>
+          <t>[36,1577][174,1715]</t>
+        </is>
+      </c>
+      <c r="E733" t="inlineStr"/>
+      <c r="F733" t="inlineStr"/>
+      <c r="G733" t="inlineStr"/>
+      <c r="H733" t="inlineStr"/>
+      <c r="I733" t="inlineStr"/>
+    </row>
+    <row r="734">
+      <c r="A734" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B734" t="inlineStr"/>
+      <c r="C734" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_pre</t>
+        </is>
+      </c>
+      <c r="D734" t="inlineStr">
+        <is>
+          <t>[174,1565][318,1727]</t>
+        </is>
+      </c>
+      <c r="E734" t="inlineStr"/>
+      <c r="F734" t="inlineStr"/>
+      <c r="G734" t="inlineStr"/>
+      <c r="H734" t="inlineStr"/>
+      <c r="I734" t="inlineStr"/>
+    </row>
+    <row r="735">
+      <c r="A735" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B735" t="inlineStr"/>
+      <c r="C735" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_day</t>
+        </is>
+      </c>
+      <c r="D735" t="inlineStr">
+        <is>
+          <t>[426,1558][666,1735]</t>
+        </is>
+      </c>
+      <c r="E735" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="F735" t="inlineStr"/>
+      <c r="G735" t="inlineStr"/>
+      <c r="H735" t="inlineStr"/>
+      <c r="I735" t="inlineStr"/>
+    </row>
+    <row r="736">
+      <c r="A736" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B736" t="inlineStr"/>
+      <c r="C736" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_next</t>
+        </is>
+      </c>
+      <c r="D736" t="inlineStr">
+        <is>
+          <t>[666,1565][750,1727]</t>
+        </is>
+      </c>
+      <c r="E736" t="inlineStr"/>
+      <c r="F736" t="inlineStr"/>
+      <c r="G736" t="inlineStr"/>
+      <c r="H736" t="inlineStr"/>
+      <c r="I736" t="inlineStr"/>
+    </row>
+    <row r="737">
+      <c r="A737" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B737" t="inlineStr"/>
+      <c r="C737" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_time</t>
+        </is>
+      </c>
+      <c r="D737" t="inlineStr">
+        <is>
+          <t>[0,1906][1080,1963]</t>
+        </is>
+      </c>
+      <c r="E737" t="inlineStr">
+        <is>
+          <t>13:44:59</t>
+        </is>
+      </c>
+      <c r="F737" t="inlineStr"/>
+      <c r="G737" t="inlineStr"/>
+      <c r="H737" t="inlineStr"/>
+      <c r="I737" t="inlineStr"/>
+    </row>
+    <row r="738">
+      <c r="A738" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B738" t="inlineStr"/>
+      <c r="C738" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/time_line_view</t>
+        </is>
+      </c>
+      <c r="D738" t="inlineStr">
+        <is>
+          <t>[0,1978][1080,2170]</t>
+        </is>
+      </c>
+      <c r="E738" t="inlineStr"/>
+      <c r="F738" t="inlineStr"/>
+      <c r="G738" t="inlineStr"/>
+      <c r="H738" t="inlineStr"/>
+      <c r="I738" t="inlineStr"/>
+    </row>
+    <row r="739">
+      <c r="A739" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B739" t="inlineStr"/>
+      <c r="C739" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_monitor_content</t>
+        </is>
+      </c>
+      <c r="D739" t="inlineStr">
+        <is>
+          <t>[0,246][1080,1378]</t>
+        </is>
+      </c>
+      <c r="E739" t="inlineStr"/>
+      <c r="F739" t="inlineStr"/>
+      <c r="G739" t="inlineStr"/>
+      <c r="H739" t="inlineStr"/>
+      <c r="I739" t="inlineStr"/>
+    </row>
+    <row r="740">
+      <c r="A740" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B740" t="inlineStr"/>
+      <c r="C740" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/playback_monitor</t>
+        </is>
+      </c>
+      <c r="D740" t="inlineStr">
+        <is>
+          <t>[0,246][1080,1378]</t>
+        </is>
+      </c>
+      <c r="E740" t="inlineStr"/>
+      <c r="F740" t="inlineStr"/>
+      <c r="G740" t="inlineStr"/>
+      <c r="H740" t="inlineStr"/>
+      <c r="I740" t="inlineStr"/>
+    </row>
+    <row r="741">
+      <c r="A741" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B741" t="inlineStr"/>
+      <c r="C741" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/layout_easy_player</t>
+        </is>
+      </c>
+      <c r="D741" t="inlineStr">
+        <is>
+          <t>[0,246][1080,1378]</t>
+        </is>
+      </c>
+      <c r="E741" t="inlineStr"/>
+      <c r="F741" t="inlineStr"/>
+      <c r="G741" t="inlineStr"/>
+      <c r="H741" t="inlineStr"/>
+      <c r="I741" t="inlineStr"/>
+    </row>
+    <row r="742">
+      <c r="A742" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B742" t="inlineStr"/>
+      <c r="C742" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_first</t>
+        </is>
+      </c>
+      <c r="D742" t="inlineStr">
+        <is>
+          <t>[0,246][1080,812]</t>
+        </is>
+      </c>
+      <c r="E742" t="inlineStr"/>
+      <c r="F742" t="inlineStr"/>
+      <c r="G742" t="inlineStr"/>
+      <c r="H742" t="inlineStr"/>
+      <c r="I742" t="inlineStr"/>
+    </row>
+    <row r="743">
+      <c r="A743" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B743" t="inlineStr"/>
+      <c r="C743" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/monitor_first</t>
+        </is>
+      </c>
+      <c r="D743" t="inlineStr">
+        <is>
+          <t>[0,246][1080,812]</t>
+        </is>
+      </c>
+      <c r="E743" t="inlineStr"/>
+      <c r="F743" t="inlineStr"/>
+      <c r="G743" t="inlineStr"/>
+      <c r="H743" t="inlineStr"/>
+      <c r="I743" t="inlineStr"/>
+    </row>
+    <row r="744">
+      <c r="A744" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B744" t="inlineStr"/>
+      <c r="C744" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_second</t>
+        </is>
+      </c>
+      <c r="D744" t="inlineStr">
+        <is>
+          <t>[0,812][1080,1378]</t>
+        </is>
+      </c>
+      <c r="E744" t="inlineStr"/>
+      <c r="F744" t="inlineStr"/>
+      <c r="G744" t="inlineStr"/>
+      <c r="H744" t="inlineStr"/>
+      <c r="I744" t="inlineStr"/>
+    </row>
+    <row r="745">
+      <c r="A745" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B745" t="inlineStr"/>
+      <c r="C745" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/monitor_second</t>
+        </is>
+      </c>
+      <c r="D745" t="inlineStr">
+        <is>
+          <t>[0,812][1080,1378]</t>
+        </is>
+      </c>
+      <c r="E745" t="inlineStr"/>
+      <c r="F745" t="inlineStr"/>
+      <c r="G745" t="inlineStr"/>
+      <c r="H745" t="inlineStr"/>
+      <c r="I745" t="inlineStr"/>
+    </row>
+    <row r="746">
+      <c r="A746" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B746" t="inlineStr"/>
+      <c r="C746" t="inlineStr">
+        <is>
+          <t>com.coloros.smartsidebar:id/roundRectView</t>
+        </is>
+      </c>
+      <c r="D746" t="inlineStr">
+        <is>
+          <t>[1062,600][1080,822]</t>
+        </is>
+      </c>
+      <c r="E746" t="inlineStr"/>
+      <c r="F746" t="inlineStr"/>
+      <c r="G746" t="inlineStr"/>
+      <c r="H746" t="inlineStr"/>
+      <c r="I746" t="inlineStr"/>
+    </row>
+    <row r="747">
+      <c r="A747" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B747" t="inlineStr"/>
+      <c r="C747" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_container</t>
+        </is>
+      </c>
+      <c r="D747" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E747" t="inlineStr"/>
+      <c r="F747" t="inlineStr"/>
+      <c r="G747" t="inlineStr"/>
+      <c r="H747" t="inlineStr"/>
+      <c r="I747" t="inlineStr"/>
+    </row>
+    <row r="748">
+      <c r="A748" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B748" t="inlineStr"/>
+      <c r="C748" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar</t>
+        </is>
+      </c>
+      <c r="D748" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E748" t="inlineStr"/>
+      <c r="F748" t="inlineStr"/>
+      <c r="G748" t="inlineStr"/>
+      <c r="H748" t="inlineStr"/>
+      <c r="I748" t="inlineStr"/>
+    </row>
+    <row r="749">
+      <c r="A749" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B749" t="inlineStr"/>
+      <c r="C749" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_contents</t>
+        </is>
+      </c>
+      <c r="D749" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E749" t="inlineStr"/>
+      <c r="F749" t="inlineStr"/>
+      <c r="G749" t="inlineStr"/>
+      <c r="H749" t="inlineStr"/>
+      <c r="I749" t="inlineStr"/>
+    </row>
+    <row r="750">
+      <c r="A750" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B750" t="inlineStr"/>
+      <c r="C750" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_left_side</t>
+        </is>
+      </c>
+      <c r="D750" t="inlineStr">
+        <is>
+          <t>[69,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E750" t="inlineStr"/>
+      <c r="F750" t="inlineStr"/>
+      <c r="G750" t="inlineStr"/>
+      <c r="H750" t="inlineStr"/>
+      <c r="I750" t="inlineStr"/>
+    </row>
+    <row r="751">
+      <c r="A751" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B751" t="inlineStr"/>
+      <c r="C751" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/clock</t>
+        </is>
+      </c>
+      <c r="D751" t="inlineStr">
+        <is>
+          <t>[69,0][181,96]</t>
+        </is>
+      </c>
+      <c r="E751" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="F751" t="inlineStr"/>
+      <c r="G751" t="inlineStr"/>
+      <c r="H751" t="inlineStr"/>
+      <c r="I751" t="inlineStr"/>
+    </row>
+    <row r="752">
+      <c r="A752" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B752" t="inlineStr"/>
+      <c r="C752" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area</t>
+        </is>
+      </c>
+      <c r="D752" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E752" t="inlineStr"/>
+      <c r="F752" t="inlineStr"/>
+      <c r="G752" t="inlineStr"/>
+      <c r="H752" t="inlineStr"/>
+      <c r="I752" t="inlineStr"/>
+    </row>
+    <row r="753">
+      <c r="A753" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B753" t="inlineStr"/>
+      <c r="C753" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area_inner</t>
+        </is>
+      </c>
+      <c r="D753" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E753" t="inlineStr"/>
+      <c r="F753" t="inlineStr"/>
+      <c r="G753" t="inlineStr"/>
+      <c r="H753" t="inlineStr"/>
+      <c r="I753" t="inlineStr"/>
+    </row>
+    <row r="754">
+      <c r="A754" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B754" t="inlineStr"/>
+      <c r="C754" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notificationIcons</t>
+        </is>
+      </c>
+      <c r="D754" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E754" t="inlineStr"/>
+      <c r="F754" t="inlineStr"/>
+      <c r="G754" t="inlineStr"/>
+      <c r="H754" t="inlineStr"/>
+      <c r="I754" t="inlineStr"/>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B755" t="inlineStr"/>
+      <c r="C755" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/cutout_space_view</t>
+        </is>
+      </c>
+      <c r="D755" t="inlineStr">
+        <is>
+          <t>[444,0][636,76]</t>
+        </is>
+      </c>
+      <c r="E755" t="inlineStr"/>
+      <c r="F755" t="inlineStr"/>
+      <c r="G755" t="inlineStr"/>
+      <c r="H755" t="inlineStr"/>
+      <c r="I755" t="inlineStr"/>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B756" t="inlineStr"/>
+      <c r="C756" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icon_area</t>
+        </is>
+      </c>
+      <c r="D756" t="inlineStr">
+        <is>
+          <t>[636,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E756" t="inlineStr"/>
+      <c r="F756" t="inlineStr"/>
+      <c r="G756" t="inlineStr"/>
+      <c r="H756" t="inlineStr"/>
+      <c r="I756" t="inlineStr"/>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B757" t="inlineStr"/>
+      <c r="C757" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icons</t>
+        </is>
+      </c>
+      <c r="D757" t="inlineStr">
+        <is>
+          <t>[665,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E757" t="inlineStr"/>
+      <c r="F757" t="inlineStr"/>
+      <c r="G757" t="inlineStr"/>
+      <c r="H757" t="inlineStr"/>
+      <c r="I757" t="inlineStr"/>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B758" t="inlineStr"/>
+      <c r="C758" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/statusIcons</t>
+        </is>
+      </c>
+      <c r="D758" t="inlineStr">
+        <is>
+          <t>[665,0][705,96]</t>
+        </is>
+      </c>
+      <c r="E758" t="inlineStr"/>
+      <c r="F758" t="inlineStr"/>
+      <c r="G758" t="inlineStr"/>
+      <c r="H758" t="inlineStr"/>
+      <c r="I758" t="inlineStr"/>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B759" t="inlineStr"/>
+      <c r="C759" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/signal_cluster</t>
+        </is>
+      </c>
+      <c r="D759" t="inlineStr">
+        <is>
+          <t>[705,0][944,96]</t>
+        </is>
+      </c>
+      <c r="E759" t="inlineStr"/>
+      <c r="F759" t="inlineStr"/>
+      <c r="G759" t="inlineStr"/>
+      <c r="H759" t="inlineStr"/>
+      <c r="I759" t="inlineStr"/>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B760" t="inlineStr"/>
+      <c r="C760" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_combo</t>
+        </is>
+      </c>
+      <c r="D760" t="inlineStr">
+        <is>
+          <t>[705,30][763,66]</t>
+        </is>
+      </c>
+      <c r="E760" t="inlineStr"/>
+      <c r="F760" t="inlineStr"/>
+      <c r="G760" t="inlineStr"/>
+      <c r="H760" t="inlineStr"/>
+      <c r="I760" t="inlineStr"/>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B761" t="inlineStr"/>
+      <c r="C761" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_inout</t>
+        </is>
+      </c>
+      <c r="D761" t="inlineStr">
+        <is>
+          <t>[705,30][763,66]</t>
+        </is>
+      </c>
+      <c r="E761" t="inlineStr"/>
+      <c r="F761" t="inlineStr"/>
+      <c r="G761" t="inlineStr"/>
+      <c r="H761" t="inlineStr"/>
+      <c r="I761" t="inlineStr"/>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B762" t="inlineStr"/>
+      <c r="C762" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_signal</t>
+        </is>
+      </c>
+      <c r="D762" t="inlineStr">
+        <is>
+          <t>[707,30][763,66]</t>
+        </is>
+      </c>
+      <c r="E762" t="inlineStr"/>
+      <c r="F762" t="inlineStr"/>
+      <c r="G762" t="inlineStr"/>
+      <c r="H762" t="inlineStr"/>
+      <c r="I762" t="inlineStr"/>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B763" t="inlineStr"/>
+      <c r="C763" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/volte_imag</t>
+        </is>
+      </c>
+      <c r="D763" t="inlineStr">
+        <is>
+          <t>[763,30][820,66]</t>
+        </is>
+      </c>
+      <c r="E763" t="inlineStr"/>
+      <c r="F763" t="inlineStr"/>
+      <c r="G763" t="inlineStr"/>
+      <c r="H763" t="inlineStr"/>
+      <c r="I763" t="inlineStr"/>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B764" t="inlineStr"/>
+      <c r="C764" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_signal_group</t>
+        </is>
+      </c>
+      <c r="D764" t="inlineStr">
+        <is>
+          <t>[820,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E764" t="inlineStr"/>
+      <c r="F764" t="inlineStr"/>
+      <c r="G764" t="inlineStr"/>
+      <c r="H764" t="inlineStr"/>
+      <c r="I764" t="inlineStr"/>
+    </row>
+    <row r="765">
+      <c r="A765" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B765" t="inlineStr"/>
+      <c r="C765" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_combo</t>
+        </is>
+      </c>
+      <c r="D765" t="inlineStr">
+        <is>
+          <t>[820,30][882,66]</t>
+        </is>
+      </c>
+      <c r="E765" t="inlineStr"/>
+      <c r="F765" t="inlineStr"/>
+      <c r="G765" t="inlineStr"/>
+      <c r="H765" t="inlineStr"/>
+      <c r="I765" t="inlineStr"/>
+    </row>
+    <row r="766">
+      <c r="A766" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B766" t="inlineStr"/>
+      <c r="C766" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_type</t>
+        </is>
+      </c>
+      <c r="D766" t="inlineStr">
+        <is>
+          <t>[820,30][882,66]</t>
+        </is>
+      </c>
+      <c r="E766" t="inlineStr"/>
+      <c r="F766" t="inlineStr"/>
+      <c r="G766" t="inlineStr"/>
+      <c r="H766" t="inlineStr"/>
+      <c r="I766" t="inlineStr"/>
+    </row>
+    <row r="767">
+      <c r="A767" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B767" t="inlineStr"/>
+      <c r="C767" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_signal</t>
+        </is>
+      </c>
+      <c r="D767" t="inlineStr">
+        <is>
+          <t>[826,30][882,66]</t>
+        </is>
+      </c>
+      <c r="E767" t="inlineStr"/>
+      <c r="F767" t="inlineStr"/>
+      <c r="G767" t="inlineStr"/>
+      <c r="H767" t="inlineStr"/>
+      <c r="I767" t="inlineStr"/>
+    </row>
+    <row r="768">
+      <c r="A768" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B768" t="inlineStr"/>
+      <c r="C768" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_combo</t>
+        </is>
+      </c>
+      <c r="D768" t="inlineStr">
+        <is>
+          <t>[882,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E768" t="inlineStr"/>
+      <c r="F768" t="inlineStr"/>
+      <c r="G768" t="inlineStr"/>
+      <c r="H768" t="inlineStr"/>
+      <c r="I768" t="inlineStr"/>
+    </row>
+    <row r="769">
+      <c r="A769" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B769" t="inlineStr"/>
+      <c r="C769" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_type</t>
+        </is>
+      </c>
+      <c r="D769" t="inlineStr">
+        <is>
+          <t>[882,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E769" t="inlineStr"/>
+      <c r="F769" t="inlineStr"/>
+      <c r="G769" t="inlineStr"/>
+      <c r="H769" t="inlineStr"/>
+      <c r="I769" t="inlineStr"/>
+    </row>
+    <row r="770">
+      <c r="A770" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B770" t="inlineStr"/>
+      <c r="C770" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_signal</t>
+        </is>
+      </c>
+      <c r="D770" t="inlineStr">
+        <is>
+          <t>[888,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E770" t="inlineStr"/>
+      <c r="F770" t="inlineStr"/>
+      <c r="G770" t="inlineStr"/>
+      <c r="H770" t="inlineStr"/>
+      <c r="I770" t="inlineStr"/>
+    </row>
+    <row r="771">
+      <c r="A771" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B771" t="inlineStr"/>
+      <c r="C771" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery</t>
+        </is>
+      </c>
+      <c r="D771" t="inlineStr">
+        <is>
+          <t>[944,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E771" t="inlineStr"/>
+      <c r="F771" t="inlineStr"/>
+      <c r="G771" t="inlineStr"/>
+      <c r="H771" t="inlineStr"/>
+      <c r="I771" t="inlineStr"/>
+    </row>
+    <row r="772">
+      <c r="A772" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B772" t="inlineStr"/>
+      <c r="C772" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery_content</t>
+        </is>
+      </c>
+      <c r="D772" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E772" t="inlineStr"/>
+      <c r="F772" t="inlineStr"/>
+      <c r="G772" t="inlineStr"/>
+      <c r="H772" t="inlineStr"/>
+      <c r="I772" t="inlineStr"/>
+    </row>
+    <row r="773">
+      <c r="A773" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="B773" t="inlineStr"/>
+      <c r="C773" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/stat_battery_view</t>
+        </is>
+      </c>
+      <c r="D773" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E773" t="inlineStr"/>
+      <c r="F773" t="inlineStr"/>
+      <c r="G773" t="inlineStr"/>
+      <c r="H773" t="inlineStr"/>
+      <c r="I773" t="inlineStr"/>
+    </row>
+    <row r="774">
+      <c r="A774" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B774" t="inlineStr"/>
+      <c r="C774" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_container</t>
+        </is>
+      </c>
+      <c r="D774" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E774" t="inlineStr"/>
+      <c r="F774" t="inlineStr"/>
+      <c r="G774" t="inlineStr"/>
+      <c r="H774" t="inlineStr"/>
+      <c r="I774" t="inlineStr"/>
+    </row>
+    <row r="775">
+      <c r="A775" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B775" t="inlineStr"/>
+      <c r="C775" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar</t>
+        </is>
+      </c>
+      <c r="D775" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E775" t="inlineStr"/>
+      <c r="F775" t="inlineStr"/>
+      <c r="G775" t="inlineStr"/>
+      <c r="H775" t="inlineStr"/>
+      <c r="I775" t="inlineStr"/>
+    </row>
+    <row r="776">
+      <c r="A776" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B776" t="inlineStr"/>
+      <c r="C776" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_contents</t>
+        </is>
+      </c>
+      <c r="D776" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E776" t="inlineStr"/>
+      <c r="F776" t="inlineStr"/>
+      <c r="G776" t="inlineStr"/>
+      <c r="H776" t="inlineStr"/>
+      <c r="I776" t="inlineStr"/>
+    </row>
+    <row r="777">
+      <c r="A777" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B777" t="inlineStr"/>
+      <c r="C777" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_left_side</t>
+        </is>
+      </c>
+      <c r="D777" t="inlineStr">
+        <is>
+          <t>[69,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E777" t="inlineStr"/>
+      <c r="F777" t="inlineStr"/>
+      <c r="G777" t="inlineStr"/>
+      <c r="H777" t="inlineStr"/>
+      <c r="I777" t="inlineStr"/>
+    </row>
+    <row r="778">
+      <c r="A778" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B778" t="inlineStr"/>
+      <c r="C778" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/clock</t>
+        </is>
+      </c>
+      <c r="D778" t="inlineStr">
+        <is>
+          <t>[69,0][181,96]</t>
+        </is>
+      </c>
+      <c r="E778" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="F778" t="inlineStr"/>
+      <c r="G778" t="inlineStr"/>
+      <c r="H778" t="inlineStr"/>
+      <c r="I778" t="inlineStr"/>
+    </row>
+    <row r="779">
+      <c r="A779" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B779" t="inlineStr"/>
+      <c r="C779" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area</t>
+        </is>
+      </c>
+      <c r="D779" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E779" t="inlineStr"/>
+      <c r="F779" t="inlineStr"/>
+      <c r="G779" t="inlineStr"/>
+      <c r="H779" t="inlineStr"/>
+      <c r="I779" t="inlineStr"/>
+    </row>
+    <row r="780">
+      <c r="A780" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B780" t="inlineStr"/>
+      <c r="C780" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area_inner</t>
+        </is>
+      </c>
+      <c r="D780" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E780" t="inlineStr"/>
+      <c r="F780" t="inlineStr"/>
+      <c r="G780" t="inlineStr"/>
+      <c r="H780" t="inlineStr"/>
+      <c r="I780" t="inlineStr"/>
+    </row>
+    <row r="781">
+      <c r="A781" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B781" t="inlineStr"/>
+      <c r="C781" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notificationIcons</t>
+        </is>
+      </c>
+      <c r="D781" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E781" t="inlineStr"/>
+      <c r="F781" t="inlineStr"/>
+      <c r="G781" t="inlineStr"/>
+      <c r="H781" t="inlineStr"/>
+      <c r="I781" t="inlineStr"/>
+    </row>
+    <row r="782">
+      <c r="A782" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B782" t="inlineStr"/>
+      <c r="C782" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/cutout_space_view</t>
+        </is>
+      </c>
+      <c r="D782" t="inlineStr">
+        <is>
+          <t>[444,0][636,76]</t>
+        </is>
+      </c>
+      <c r="E782" t="inlineStr"/>
+      <c r="F782" t="inlineStr"/>
+      <c r="G782" t="inlineStr"/>
+      <c r="H782" t="inlineStr"/>
+      <c r="I782" t="inlineStr"/>
+    </row>
+    <row r="783">
+      <c r="A783" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B783" t="inlineStr"/>
+      <c r="C783" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icon_area</t>
+        </is>
+      </c>
+      <c r="D783" t="inlineStr">
+        <is>
+          <t>[636,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E783" t="inlineStr"/>
+      <c r="F783" t="inlineStr"/>
+      <c r="G783" t="inlineStr"/>
+      <c r="H783" t="inlineStr"/>
+      <c r="I783" t="inlineStr"/>
+    </row>
+    <row r="784">
+      <c r="A784" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B784" t="inlineStr"/>
+      <c r="C784" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icons</t>
+        </is>
+      </c>
+      <c r="D784" t="inlineStr">
+        <is>
+          <t>[665,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E784" t="inlineStr"/>
+      <c r="F784" t="inlineStr"/>
+      <c r="G784" t="inlineStr"/>
+      <c r="H784" t="inlineStr"/>
+      <c r="I784" t="inlineStr"/>
+    </row>
+    <row r="785">
+      <c r="A785" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B785" t="inlineStr"/>
+      <c r="C785" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/statusIcons</t>
+        </is>
+      </c>
+      <c r="D785" t="inlineStr">
+        <is>
+          <t>[665,0][705,96]</t>
+        </is>
+      </c>
+      <c r="E785" t="inlineStr"/>
+      <c r="F785" t="inlineStr"/>
+      <c r="G785" t="inlineStr"/>
+      <c r="H785" t="inlineStr"/>
+      <c r="I785" t="inlineStr"/>
+    </row>
+    <row r="786">
+      <c r="A786" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B786" t="inlineStr"/>
+      <c r="C786" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/signal_cluster</t>
+        </is>
+      </c>
+      <c r="D786" t="inlineStr">
+        <is>
+          <t>[705,0][944,96]</t>
+        </is>
+      </c>
+      <c r="E786" t="inlineStr"/>
+      <c r="F786" t="inlineStr"/>
+      <c r="G786" t="inlineStr"/>
+      <c r="H786" t="inlineStr"/>
+      <c r="I786" t="inlineStr"/>
+    </row>
+    <row r="787">
+      <c r="A787" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B787" t="inlineStr"/>
+      <c r="C787" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_combo</t>
+        </is>
+      </c>
+      <c r="D787" t="inlineStr">
+        <is>
+          <t>[705,30][763,66]</t>
+        </is>
+      </c>
+      <c r="E787" t="inlineStr"/>
+      <c r="F787" t="inlineStr"/>
+      <c r="G787" t="inlineStr"/>
+      <c r="H787" t="inlineStr"/>
+      <c r="I787" t="inlineStr"/>
+    </row>
+    <row r="788">
+      <c r="A788" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B788" t="inlineStr"/>
+      <c r="C788" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_inout</t>
+        </is>
+      </c>
+      <c r="D788" t="inlineStr">
+        <is>
+          <t>[705,30][763,66]</t>
+        </is>
+      </c>
+      <c r="E788" t="inlineStr"/>
+      <c r="F788" t="inlineStr"/>
+      <c r="G788" t="inlineStr"/>
+      <c r="H788" t="inlineStr"/>
+      <c r="I788" t="inlineStr"/>
+    </row>
+    <row r="789">
+      <c r="A789" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B789" t="inlineStr"/>
+      <c r="C789" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_signal</t>
+        </is>
+      </c>
+      <c r="D789" t="inlineStr">
+        <is>
+          <t>[707,30][763,66]</t>
+        </is>
+      </c>
+      <c r="E789" t="inlineStr"/>
+      <c r="F789" t="inlineStr"/>
+      <c r="G789" t="inlineStr"/>
+      <c r="H789" t="inlineStr"/>
+      <c r="I789" t="inlineStr"/>
+    </row>
+    <row r="790">
+      <c r="A790" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B790" t="inlineStr"/>
+      <c r="C790" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/volte_imag</t>
+        </is>
+      </c>
+      <c r="D790" t="inlineStr">
+        <is>
+          <t>[763,30][820,66]</t>
+        </is>
+      </c>
+      <c r="E790" t="inlineStr"/>
+      <c r="F790" t="inlineStr"/>
+      <c r="G790" t="inlineStr"/>
+      <c r="H790" t="inlineStr"/>
+      <c r="I790" t="inlineStr"/>
+    </row>
+    <row r="791">
+      <c r="A791" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B791" t="inlineStr"/>
+      <c r="C791" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_signal_group</t>
+        </is>
+      </c>
+      <c r="D791" t="inlineStr">
+        <is>
+          <t>[820,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E791" t="inlineStr"/>
+      <c r="F791" t="inlineStr"/>
+      <c r="G791" t="inlineStr"/>
+      <c r="H791" t="inlineStr"/>
+      <c r="I791" t="inlineStr"/>
+    </row>
+    <row r="792">
+      <c r="A792" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B792" t="inlineStr"/>
+      <c r="C792" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_combo</t>
+        </is>
+      </c>
+      <c r="D792" t="inlineStr">
+        <is>
+          <t>[820,30][882,66]</t>
+        </is>
+      </c>
+      <c r="E792" t="inlineStr"/>
+      <c r="F792" t="inlineStr"/>
+      <c r="G792" t="inlineStr"/>
+      <c r="H792" t="inlineStr"/>
+      <c r="I792" t="inlineStr"/>
+    </row>
+    <row r="793">
+      <c r="A793" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B793" t="inlineStr"/>
+      <c r="C793" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_type</t>
+        </is>
+      </c>
+      <c r="D793" t="inlineStr">
+        <is>
+          <t>[820,30][882,66]</t>
+        </is>
+      </c>
+      <c r="E793" t="inlineStr"/>
+      <c r="F793" t="inlineStr"/>
+      <c r="G793" t="inlineStr"/>
+      <c r="H793" t="inlineStr"/>
+      <c r="I793" t="inlineStr"/>
+    </row>
+    <row r="794">
+      <c r="A794" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B794" t="inlineStr"/>
+      <c r="C794" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_signal</t>
+        </is>
+      </c>
+      <c r="D794" t="inlineStr">
+        <is>
+          <t>[826,30][882,66]</t>
+        </is>
+      </c>
+      <c r="E794" t="inlineStr"/>
+      <c r="F794" t="inlineStr"/>
+      <c r="G794" t="inlineStr"/>
+      <c r="H794" t="inlineStr"/>
+      <c r="I794" t="inlineStr"/>
+    </row>
+    <row r="795">
+      <c r="A795" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B795" t="inlineStr"/>
+      <c r="C795" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_combo</t>
+        </is>
+      </c>
+      <c r="D795" t="inlineStr">
+        <is>
+          <t>[882,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E795" t="inlineStr"/>
+      <c r="F795" t="inlineStr"/>
+      <c r="G795" t="inlineStr"/>
+      <c r="H795" t="inlineStr"/>
+      <c r="I795" t="inlineStr"/>
+    </row>
+    <row r="796">
+      <c r="A796" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B796" t="inlineStr"/>
+      <c r="C796" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_type</t>
+        </is>
+      </c>
+      <c r="D796" t="inlineStr">
+        <is>
+          <t>[882,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E796" t="inlineStr"/>
+      <c r="F796" t="inlineStr"/>
+      <c r="G796" t="inlineStr"/>
+      <c r="H796" t="inlineStr"/>
+      <c r="I796" t="inlineStr"/>
+    </row>
+    <row r="797">
+      <c r="A797" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B797" t="inlineStr"/>
+      <c r="C797" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_signal</t>
+        </is>
+      </c>
+      <c r="D797" t="inlineStr">
+        <is>
+          <t>[888,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E797" t="inlineStr"/>
+      <c r="F797" t="inlineStr"/>
+      <c r="G797" t="inlineStr"/>
+      <c r="H797" t="inlineStr"/>
+      <c r="I797" t="inlineStr"/>
+    </row>
+    <row r="798">
+      <c r="A798" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B798" t="inlineStr"/>
+      <c r="C798" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery</t>
+        </is>
+      </c>
+      <c r="D798" t="inlineStr">
+        <is>
+          <t>[944,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E798" t="inlineStr"/>
+      <c r="F798" t="inlineStr"/>
+      <c r="G798" t="inlineStr"/>
+      <c r="H798" t="inlineStr"/>
+      <c r="I798" t="inlineStr"/>
+    </row>
+    <row r="799">
+      <c r="A799" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B799" t="inlineStr"/>
+      <c r="C799" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery_content</t>
+        </is>
+      </c>
+      <c r="D799" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E799" t="inlineStr"/>
+      <c r="F799" t="inlineStr"/>
+      <c r="G799" t="inlineStr"/>
+      <c r="H799" t="inlineStr"/>
+      <c r="I799" t="inlineStr"/>
+    </row>
+    <row r="800">
+      <c r="A800" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B800" t="inlineStr"/>
+      <c r="C800" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/stat_battery_view</t>
+        </is>
+      </c>
+      <c r="D800" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E800" t="inlineStr"/>
+      <c r="F800" t="inlineStr"/>
+      <c r="G800" t="inlineStr"/>
+      <c r="H800" t="inlineStr"/>
+      <c r="I800" t="inlineStr"/>
+    </row>
+    <row r="801">
+      <c r="A801" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B801" t="inlineStr"/>
+      <c r="C801" t="inlineStr">
+        <is>
+          <t>android:id/content</t>
+        </is>
+      </c>
+      <c r="D801" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E801" t="inlineStr"/>
+      <c r="F801" t="inlineStr"/>
+      <c r="G801" t="inlineStr"/>
+      <c r="H801" t="inlineStr"/>
+      <c r="I801" t="inlineStr"/>
+    </row>
+    <row r="802">
+      <c r="A802" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B802" t="inlineStr"/>
+      <c r="C802" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/base_layout</t>
+        </is>
+      </c>
+      <c r="D802" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E802" t="inlineStr"/>
+      <c r="F802" t="inlineStr"/>
+      <c r="G802" t="inlineStr"/>
+      <c r="H802" t="inlineStr"/>
+      <c r="I802" t="inlineStr"/>
+    </row>
+    <row r="803">
+      <c r="A803" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B803" t="inlineStr"/>
+      <c r="C803" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/base_content</t>
+        </is>
+      </c>
+      <c r="D803" t="inlineStr">
+        <is>
+          <t>[0,96][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E803" t="inlineStr"/>
+      <c r="F803" t="inlineStr"/>
+      <c r="G803" t="inlineStr"/>
+      <c r="H803" t="inlineStr"/>
+      <c r="I803" t="inlineStr"/>
+    </row>
+    <row r="804">
+      <c r="A804" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B804" t="inlineStr"/>
+      <c r="C804" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/fl_portait</t>
+        </is>
+      </c>
+      <c r="D804" t="inlineStr">
+        <is>
+          <t>[0,96][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E804" t="inlineStr"/>
+      <c r="F804" t="inlineStr"/>
+      <c r="G804" t="inlineStr"/>
+      <c r="H804" t="inlineStr"/>
+      <c r="I804" t="inlineStr"/>
+    </row>
+    <row r="805">
+      <c r="A805" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B805" t="inlineStr"/>
+      <c r="C805" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_status</t>
+        </is>
+      </c>
+      <c r="D805" t="inlineStr">
+        <is>
+          <t>[0,96][1080,246]</t>
+        </is>
+      </c>
+      <c r="E805" t="inlineStr"/>
+      <c r="F805" t="inlineStr"/>
+      <c r="G805" t="inlineStr"/>
+      <c r="H805" t="inlineStr"/>
+      <c r="I805" t="inlineStr"/>
+    </row>
+    <row r="806">
+      <c r="A806" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B806" t="inlineStr"/>
+      <c r="C806" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/btn_back</t>
+        </is>
+      </c>
+      <c r="D806" t="inlineStr">
+        <is>
+          <t>[0,106][105,235]</t>
+        </is>
+      </c>
+      <c r="E806" t="inlineStr"/>
+      <c r="F806" t="inlineStr"/>
+      <c r="G806" t="inlineStr"/>
+      <c r="H806" t="inlineStr"/>
+      <c r="I806" t="inlineStr"/>
+    </row>
+    <row r="807">
+      <c r="A807" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B807" t="inlineStr"/>
+      <c r="C807" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_title</t>
+        </is>
+      </c>
+      <c r="D807" t="inlineStr">
+        <is>
+          <t>[342,134][504,207]</t>
+        </is>
+      </c>
+      <c r="E807" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="F807" t="inlineStr"/>
+      <c r="G807" t="inlineStr"/>
+      <c r="H807" t="inlineStr"/>
+      <c r="I807" t="inlineStr"/>
+    </row>
+    <row r="808">
+      <c r="A808" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B808" t="inlineStr"/>
+      <c r="C808" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_obs</t>
+        </is>
+      </c>
+      <c r="D808" t="inlineStr">
+        <is>
+          <t>[576,134][738,207]</t>
+        </is>
+      </c>
+      <c r="E808" t="inlineStr">
+        <is>
+          <t>云回放</t>
+        </is>
+      </c>
+      <c r="F808" t="inlineStr"/>
+      <c r="G808" t="inlineStr"/>
+      <c r="H808" t="inlineStr"/>
+      <c r="I808" t="inlineStr"/>
+    </row>
+    <row r="809">
+      <c r="A809" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B809" t="inlineStr"/>
+      <c r="C809" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_layout</t>
+        </is>
+      </c>
+      <c r="D809" t="inlineStr">
+        <is>
+          <t>[0,246][1080,1378]</t>
+        </is>
+      </c>
+      <c r="E809" t="inlineStr"/>
+      <c r="F809" t="inlineStr"/>
+      <c r="G809" t="inlineStr"/>
+      <c r="H809" t="inlineStr"/>
+      <c r="I809" t="inlineStr"/>
+    </row>
+    <row r="810">
+      <c r="A810" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B810" t="inlineStr"/>
+      <c r="C810" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/no_playback_control</t>
+        </is>
+      </c>
+      <c r="D810" t="inlineStr">
+        <is>
+          <t>[439,763][640,861]</t>
+        </is>
+      </c>
+      <c r="E810" t="inlineStr"/>
+      <c r="F810" t="inlineStr"/>
+      <c r="G810" t="inlineStr"/>
+      <c r="H810" t="inlineStr"/>
+      <c r="I810" t="inlineStr"/>
+    </row>
+    <row r="811">
+      <c r="A811" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B811" t="inlineStr"/>
+      <c r="C811" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_data_content</t>
+        </is>
+      </c>
+      <c r="D811" t="inlineStr">
+        <is>
+          <t>[439,763][640,816]</t>
+        </is>
+      </c>
+      <c r="E811" t="inlineStr">
+        <is>
+          <t>请插入TF卡</t>
+        </is>
+      </c>
+      <c r="F811" t="inlineStr"/>
+      <c r="G811" t="inlineStr"/>
+      <c r="H811" t="inlineStr"/>
+      <c r="I811" t="inlineStr"/>
+    </row>
+    <row r="812">
+      <c r="A812" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B812" t="inlineStr"/>
+      <c r="C812" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/liner_control</t>
+        </is>
+      </c>
+      <c r="D812" t="inlineStr">
+        <is>
+          <t>[0,1378][1080,1558]</t>
+        </is>
+      </c>
+      <c r="E812" t="inlineStr"/>
+      <c r="F812" t="inlineStr"/>
+      <c r="G812" t="inlineStr"/>
+      <c r="H812" t="inlineStr"/>
+      <c r="I812" t="inlineStr"/>
+    </row>
+    <row r="813">
+      <c r="A813" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B813" t="inlineStr"/>
+      <c r="C813" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_1x</t>
+        </is>
+      </c>
+      <c r="D813" t="inlineStr">
+        <is>
+          <t>[0,1378][216,1558]</t>
+        </is>
+      </c>
+      <c r="E813" t="inlineStr"/>
+      <c r="F813" t="inlineStr"/>
+      <c r="G813" t="inlineStr"/>
+      <c r="H813" t="inlineStr"/>
+      <c r="I813" t="inlineStr"/>
+    </row>
+    <row r="814">
+      <c r="A814" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B814" t="inlineStr"/>
+      <c r="C814" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_sound</t>
+        </is>
+      </c>
+      <c r="D814" t="inlineStr">
+        <is>
+          <t>[216,1381][432,1555]</t>
+        </is>
+      </c>
+      <c r="E814" t="inlineStr"/>
+      <c r="F814" t="inlineStr"/>
+      <c r="G814" t="inlineStr"/>
+      <c r="H814" t="inlineStr"/>
+      <c r="I814" t="inlineStr"/>
+    </row>
+    <row r="815">
+      <c r="A815" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B815" t="inlineStr"/>
+      <c r="C815" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_play</t>
+        </is>
+      </c>
+      <c r="D815" t="inlineStr">
+        <is>
+          <t>[432,1378][648,1558]</t>
+        </is>
+      </c>
+      <c r="E815" t="inlineStr"/>
+      <c r="F815" t="inlineStr"/>
+      <c r="G815" t="inlineStr"/>
+      <c r="H815" t="inlineStr"/>
+      <c r="I815" t="inlineStr"/>
+    </row>
+    <row r="816">
+      <c r="A816" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B816" t="inlineStr"/>
+      <c r="C816" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_photo</t>
+        </is>
+      </c>
+      <c r="D816" t="inlineStr">
+        <is>
+          <t>[648,1381][864,1555]</t>
+        </is>
+      </c>
+      <c r="E816" t="inlineStr"/>
+      <c r="F816" t="inlineStr"/>
+      <c r="G816" t="inlineStr"/>
+      <c r="H816" t="inlineStr"/>
+      <c r="I816" t="inlineStr"/>
+    </row>
+    <row r="817">
+      <c r="A817" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B817" t="inlineStr"/>
+      <c r="C817" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_full_screen</t>
+        </is>
+      </c>
+      <c r="D817" t="inlineStr">
+        <is>
+          <t>[864,1378][1080,1558]</t>
+        </is>
+      </c>
+      <c r="E817" t="inlineStr"/>
+      <c r="F817" t="inlineStr"/>
+      <c r="G817" t="inlineStr"/>
+      <c r="H817" t="inlineStr"/>
+      <c r="I817" t="inlineStr"/>
+    </row>
+    <row r="818">
+      <c r="A818" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B818" t="inlineStr"/>
+      <c r="C818" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/liner_time</t>
+        </is>
+      </c>
+      <c r="D818" t="inlineStr">
+        <is>
+          <t>[0,1558][1080,1735]</t>
+        </is>
+      </c>
+      <c r="E818" t="inlineStr"/>
+      <c r="F818" t="inlineStr"/>
+      <c r="G818" t="inlineStr"/>
+      <c r="H818" t="inlineStr"/>
+      <c r="I818" t="inlineStr"/>
+    </row>
+    <row r="819">
+      <c r="A819" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B819" t="inlineStr"/>
+      <c r="C819" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_record</t>
+        </is>
+      </c>
+      <c r="D819" t="inlineStr">
+        <is>
+          <t>[36,1577][174,1715]</t>
+        </is>
+      </c>
+      <c r="E819" t="inlineStr"/>
+      <c r="F819" t="inlineStr"/>
+      <c r="G819" t="inlineStr"/>
+      <c r="H819" t="inlineStr"/>
+      <c r="I819" t="inlineStr"/>
+    </row>
+    <row r="820">
+      <c r="A820" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B820" t="inlineStr"/>
+      <c r="C820" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_pre</t>
+        </is>
+      </c>
+      <c r="D820" t="inlineStr">
+        <is>
+          <t>[174,1565][318,1727]</t>
+        </is>
+      </c>
+      <c r="E820" t="inlineStr"/>
+      <c r="F820" t="inlineStr"/>
+      <c r="G820" t="inlineStr"/>
+      <c r="H820" t="inlineStr"/>
+      <c r="I820" t="inlineStr"/>
+    </row>
+    <row r="821">
+      <c r="A821" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B821" t="inlineStr"/>
+      <c r="C821" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_day</t>
+        </is>
+      </c>
+      <c r="D821" t="inlineStr">
+        <is>
+          <t>[426,1558][666,1735]</t>
+        </is>
+      </c>
+      <c r="E821" t="inlineStr">
+        <is>
+          <t>2024-11-12</t>
+        </is>
+      </c>
+      <c r="F821" t="inlineStr"/>
+      <c r="G821" t="inlineStr"/>
+      <c r="H821" t="inlineStr"/>
+      <c r="I821" t="inlineStr"/>
+    </row>
+    <row r="822">
+      <c r="A822" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B822" t="inlineStr"/>
+      <c r="C822" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/img_next</t>
+        </is>
+      </c>
+      <c r="D822" t="inlineStr">
+        <is>
+          <t>[666,1565][750,1727]</t>
+        </is>
+      </c>
+      <c r="E822" t="inlineStr"/>
+      <c r="F822" t="inlineStr"/>
+      <c r="G822" t="inlineStr"/>
+      <c r="H822" t="inlineStr"/>
+      <c r="I822" t="inlineStr"/>
+    </row>
+    <row r="823">
+      <c r="A823" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B823" t="inlineStr"/>
+      <c r="C823" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/tv_time</t>
+        </is>
+      </c>
+      <c r="D823" t="inlineStr">
+        <is>
+          <t>[0,1906][1080,1963]</t>
+        </is>
+      </c>
+      <c r="E823" t="inlineStr"/>
+      <c r="F823" t="inlineStr"/>
+      <c r="G823" t="inlineStr"/>
+      <c r="H823" t="inlineStr"/>
+      <c r="I823" t="inlineStr"/>
+    </row>
+    <row r="824">
+      <c r="A824" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B824" t="inlineStr"/>
+      <c r="C824" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/time_line_view</t>
+        </is>
+      </c>
+      <c r="D824" t="inlineStr">
+        <is>
+          <t>[0,1978][1080,2170]</t>
+        </is>
+      </c>
+      <c r="E824" t="inlineStr"/>
+      <c r="F824" t="inlineStr"/>
+      <c r="G824" t="inlineStr"/>
+      <c r="H824" t="inlineStr"/>
+      <c r="I824" t="inlineStr"/>
+    </row>
+    <row r="825">
+      <c r="A825" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B825" t="inlineStr"/>
+      <c r="C825" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_monitor_content</t>
+        </is>
+      </c>
+      <c r="D825" t="inlineStr">
+        <is>
+          <t>[0,246][1080,1378]</t>
+        </is>
+      </c>
+      <c r="E825" t="inlineStr"/>
+      <c r="F825" t="inlineStr"/>
+      <c r="G825" t="inlineStr"/>
+      <c r="H825" t="inlineStr"/>
+      <c r="I825" t="inlineStr"/>
+    </row>
+    <row r="826">
+      <c r="A826" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B826" t="inlineStr"/>
+      <c r="C826" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/playback_monitor</t>
+        </is>
+      </c>
+      <c r="D826" t="inlineStr">
+        <is>
+          <t>[0,246][1080,1378]</t>
+        </is>
+      </c>
+      <c r="E826" t="inlineStr"/>
+      <c r="F826" t="inlineStr"/>
+      <c r="G826" t="inlineStr"/>
+      <c r="H826" t="inlineStr"/>
+      <c r="I826" t="inlineStr"/>
+    </row>
+    <row r="827">
+      <c r="A827" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B827" t="inlineStr"/>
+      <c r="C827" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/layout_easy_player</t>
+        </is>
+      </c>
+      <c r="D827" t="inlineStr">
+        <is>
+          <t>[0,246][1080,1378]</t>
+        </is>
+      </c>
+      <c r="E827" t="inlineStr"/>
+      <c r="F827" t="inlineStr"/>
+      <c r="G827" t="inlineStr"/>
+      <c r="H827" t="inlineStr"/>
+      <c r="I827" t="inlineStr"/>
+    </row>
+    <row r="828">
+      <c r="A828" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B828" t="inlineStr"/>
+      <c r="C828" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_first</t>
+        </is>
+      </c>
+      <c r="D828" t="inlineStr">
+        <is>
+          <t>[0,246][1080,812]</t>
+        </is>
+      </c>
+      <c r="E828" t="inlineStr"/>
+      <c r="F828" t="inlineStr"/>
+      <c r="G828" t="inlineStr"/>
+      <c r="H828" t="inlineStr"/>
+      <c r="I828" t="inlineStr"/>
+    </row>
+    <row r="829">
+      <c r="A829" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B829" t="inlineStr"/>
+      <c r="C829" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/monitor_first</t>
+        </is>
+      </c>
+      <c r="D829" t="inlineStr">
+        <is>
+          <t>[0,246][1080,812]</t>
+        </is>
+      </c>
+      <c r="E829" t="inlineStr"/>
+      <c r="F829" t="inlineStr"/>
+      <c r="G829" t="inlineStr"/>
+      <c r="H829" t="inlineStr"/>
+      <c r="I829" t="inlineStr"/>
+    </row>
+    <row r="830">
+      <c r="A830" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B830" t="inlineStr"/>
+      <c r="C830" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/rl_second</t>
+        </is>
+      </c>
+      <c r="D830" t="inlineStr">
+        <is>
+          <t>[0,812][1080,1378]</t>
+        </is>
+      </c>
+      <c r="E830" t="inlineStr"/>
+      <c r="F830" t="inlineStr"/>
+      <c r="G830" t="inlineStr"/>
+      <c r="H830" t="inlineStr"/>
+      <c r="I830" t="inlineStr"/>
+    </row>
+    <row r="831">
+      <c r="A831" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B831" t="inlineStr"/>
+      <c r="C831" t="inlineStr">
+        <is>
+          <t>com.zwcode.p6slite:id/monitor_second</t>
+        </is>
+      </c>
+      <c r="D831" t="inlineStr">
+        <is>
+          <t>[0,812][1080,1378]</t>
+        </is>
+      </c>
+      <c r="E831" t="inlineStr"/>
+      <c r="F831" t="inlineStr"/>
+      <c r="G831" t="inlineStr"/>
+      <c r="H831" t="inlineStr"/>
+      <c r="I831" t="inlineStr"/>
+    </row>
+    <row r="832">
+      <c r="A832" t="inlineStr">
+        <is>
+          <t>卡回放</t>
+        </is>
+      </c>
+      <c r="B832" t="inlineStr"/>
+      <c r="C832" t="inlineStr">
+        <is>
+          <t>com.coloros.smartsidebar:id/roundRectView</t>
+        </is>
+      </c>
+      <c r="D832" t="inlineStr">
+        <is>
+          <t>[1062,600][1080,822]</t>
+        </is>
+      </c>
+      <c r="E832" t="inlineStr"/>
+      <c r="F832" t="inlineStr"/>
+      <c r="G832" t="inlineStr"/>
+      <c r="H832" t="inlineStr"/>
+      <c r="I832" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/test.xlsx
+++ b/data/test.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I390"/>
+  <dimension ref="A1:I611"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9349,6 +9349,5357 @@
       <c r="H390" t="inlineStr"/>
       <c r="I390" t="inlineStr"/>
     </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr"/>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/action_bar_root</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr"/>
+      <c r="H391" t="inlineStr"/>
+      <c r="I391" t="inlineStr"/>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr"/>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>android:id/content</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr"/>
+      <c r="H392" t="inlineStr"/>
+      <c r="I392" t="inlineStr"/>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr"/>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/fl_content</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2165]</t>
+        </is>
+      </c>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr"/>
+      <c r="H393" t="inlineStr"/>
+      <c r="I393" t="inlineStr"/>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr"/>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/tv_title</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>[60,154][300,235]</t>
+        </is>
+      </c>
+      <c r="E394" t="inlineStr">
+        <is>
+          <t>我的设备</t>
+        </is>
+      </c>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr"/>
+      <c r="H394" t="inlineStr"/>
+      <c r="I394" t="inlineStr"/>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr"/>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/iv_refresh</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>[813,135][930,255]</t>
+        </is>
+      </c>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr"/>
+      <c r="H395" t="inlineStr"/>
+      <c r="I395" t="inlineStr"/>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr"/>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/iv_add_device</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>[930,135][1050,255]</t>
+        </is>
+      </c>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr"/>
+      <c r="H396" t="inlineStr"/>
+      <c r="I396" t="inlineStr"/>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr"/>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/srl</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>[0,270][1080,2165]</t>
+        </is>
+      </c>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr"/>
+      <c r="H397" t="inlineStr"/>
+      <c r="I397" t="inlineStr"/>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr"/>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/rv</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>[0,270][1080,1071]</t>
+        </is>
+      </c>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr"/>
+      <c r="H398" t="inlineStr"/>
+      <c r="I398" t="inlineStr"/>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr"/>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/tv_device_name</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>[72,330][633,391]</t>
+        </is>
+      </c>
+      <c r="E399" t="inlineStr">
+        <is>
+          <t>000086</t>
+        </is>
+      </c>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr"/>
+      <c r="H399" t="inlineStr"/>
+      <c r="I399" t="inlineStr"/>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr"/>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/tv_device_state</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>[72,391][227,444]</t>
+        </is>
+      </c>
+      <c r="E400" t="inlineStr">
+        <is>
+          <t>在线:2</t>
+        </is>
+      </c>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr"/>
+      <c r="H400" t="inlineStr"/>
+      <c r="I400" t="inlineStr"/>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr"/>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/ll_tab</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>[669,330][1008,426]</t>
+        </is>
+      </c>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr"/>
+      <c r="H401" t="inlineStr"/>
+      <c r="I401" t="inlineStr"/>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr"/>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/iv_cloud</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>[684,345][759,411]</t>
+        </is>
+      </c>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr"/>
+      <c r="H402" t="inlineStr"/>
+      <c r="I402" t="inlineStr"/>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr"/>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/iv_push</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>[804,330][891,426]</t>
+        </is>
+      </c>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr"/>
+      <c r="H403" t="inlineStr"/>
+      <c r="I403" t="inlineStr"/>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr"/>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/iv_more</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>[921,333][1008,423]</t>
+        </is>
+      </c>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr"/>
+      <c r="H404" t="inlineStr"/>
+      <c r="I404" t="inlineStr"/>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr"/>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/iv_camera_img</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>[36,480][1044,1047]</t>
+        </is>
+      </c>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr"/>
+      <c r="H405" t="inlineStr"/>
+      <c r="I405" t="inlineStr"/>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr"/>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/iv_online_img</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>[471,695][609,833]</t>
+        </is>
+      </c>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr"/>
+      <c r="H406" t="inlineStr"/>
+      <c r="I406" t="inlineStr"/>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr"/>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/tab_bottom</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>[0,2165][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr"/>
+      <c r="H407" t="inlineStr"/>
+      <c r="I407" t="inlineStr"/>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr"/>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/tab_home</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>[0,2165][360,2340]</t>
+        </is>
+      </c>
+      <c r="E408" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr"/>
+      <c r="H408" t="inlineStr"/>
+      <c r="I408" t="inlineStr"/>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr"/>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/tab_msg</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>[360,2165][720,2340]</t>
+        </is>
+      </c>
+      <c r="E409" t="inlineStr">
+        <is>
+          <t>消息</t>
+        </is>
+      </c>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr"/>
+      <c r="H409" t="inlineStr"/>
+      <c r="I409" t="inlineStr"/>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr"/>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>com.xrs.guangchun:id/tab_my</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>[720,2165][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E410" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr"/>
+      <c r="H410" t="inlineStr"/>
+      <c r="I410" t="inlineStr"/>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr"/>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_container</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr"/>
+      <c r="H411" t="inlineStr"/>
+      <c r="I411" t="inlineStr"/>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr"/>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr"/>
+      <c r="H412" t="inlineStr"/>
+      <c r="I412" t="inlineStr"/>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr"/>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_contents</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr"/>
+      <c r="H413" t="inlineStr"/>
+      <c r="I413" t="inlineStr"/>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr"/>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_left_side</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>[69,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr"/>
+      <c r="H414" t="inlineStr"/>
+      <c r="I414" t="inlineStr"/>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr"/>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/clock</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>[69,0][181,96]</t>
+        </is>
+      </c>
+      <c r="E415" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr"/>
+      <c r="H415" t="inlineStr"/>
+      <c r="I415" t="inlineStr"/>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr"/>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr"/>
+      <c r="H416" t="inlineStr"/>
+      <c r="I416" t="inlineStr"/>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr"/>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area_inner</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr"/>
+      <c r="H417" t="inlineStr"/>
+      <c r="I417" t="inlineStr"/>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr"/>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notificationIcons</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr"/>
+      <c r="H418" t="inlineStr"/>
+      <c r="I418" t="inlineStr"/>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr"/>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/cutout_space_view</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>[444,0][636,76]</t>
+        </is>
+      </c>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr"/>
+      <c r="H419" t="inlineStr"/>
+      <c r="I419" t="inlineStr"/>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr"/>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icon_area</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>[636,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr"/>
+      <c r="H420" t="inlineStr"/>
+      <c r="I420" t="inlineStr"/>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr"/>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icons</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>[736,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr"/>
+      <c r="H421" t="inlineStr"/>
+      <c r="I421" t="inlineStr"/>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr"/>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/statusIcons</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>[736,0][776,96]</t>
+        </is>
+      </c>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr"/>
+      <c r="H422" t="inlineStr"/>
+      <c r="I422" t="inlineStr"/>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr"/>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/signal_cluster</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>[776,0][944,96]</t>
+        </is>
+      </c>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr"/>
+      <c r="H423" t="inlineStr"/>
+      <c r="I423" t="inlineStr"/>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr"/>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_combo</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>[776,30][834,66]</t>
+        </is>
+      </c>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr"/>
+      <c r="H424" t="inlineStr"/>
+      <c r="I424" t="inlineStr"/>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr"/>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_inout</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>[776,30][834,66]</t>
+        </is>
+      </c>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr"/>
+      <c r="H425" t="inlineStr"/>
+      <c r="I425" t="inlineStr"/>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr"/>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/wifi_signal</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>[778,30][834,66]</t>
+        </is>
+      </c>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr"/>
+      <c r="H426" t="inlineStr"/>
+      <c r="I426" t="inlineStr"/>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr"/>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/volte_imag</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>[834,30][882,66]</t>
+        </is>
+      </c>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr"/>
+      <c r="H427" t="inlineStr"/>
+      <c r="I427" t="inlineStr"/>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr"/>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_signal_group</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>[882,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr"/>
+      <c r="H428" t="inlineStr"/>
+      <c r="I428" t="inlineStr"/>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr"/>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_combo</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>[882,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr"/>
+      <c r="H429" t="inlineStr"/>
+      <c r="I429" t="inlineStr"/>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr"/>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_type</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>[882,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr"/>
+      <c r="H430" t="inlineStr"/>
+      <c r="I430" t="inlineStr"/>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr"/>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_signal</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>[888,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr"/>
+      <c r="H431" t="inlineStr"/>
+      <c r="I431" t="inlineStr"/>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr"/>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>[944,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr"/>
+      <c r="H432" t="inlineStr"/>
+      <c r="I432" t="inlineStr"/>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr"/>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery_content</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr"/>
+      <c r="H433" t="inlineStr"/>
+      <c r="I433" t="inlineStr"/>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr"/>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/stat_battery_view</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr"/>
+      <c r="H434" t="inlineStr"/>
+      <c r="I434" t="inlineStr"/>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr"/>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>com.coloros.smartsidebar:id/roundRectView</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>[1062,600][1080,822]</t>
+        </is>
+      </c>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr"/>
+      <c r="H435" t="inlineStr"/>
+      <c r="I435" t="inlineStr"/>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr"/>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_container</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr"/>
+      <c r="H436" t="inlineStr"/>
+      <c r="I436" t="inlineStr"/>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr"/>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr"/>
+      <c r="H437" t="inlineStr"/>
+      <c r="I437" t="inlineStr"/>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr"/>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_contents</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>[0,0][1080,96]</t>
+        </is>
+      </c>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr"/>
+      <c r="H438" t="inlineStr"/>
+      <c r="I438" t="inlineStr"/>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr"/>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/status_bar_left_side</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>[69,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr"/>
+      <c r="H439" t="inlineStr"/>
+      <c r="I439" t="inlineStr"/>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr"/>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/clock</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>[69,0][181,96]</t>
+        </is>
+      </c>
+      <c r="E440" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr"/>
+      <c r="H440" t="inlineStr"/>
+      <c r="I440" t="inlineStr"/>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr"/>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr"/>
+      <c r="H441" t="inlineStr"/>
+      <c r="I441" t="inlineStr"/>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr"/>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notification_icon_area_inner</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr"/>
+      <c r="H442" t="inlineStr"/>
+      <c r="I442" t="inlineStr"/>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr"/>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/notificationIcons</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>[181,0][444,96]</t>
+        </is>
+      </c>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr"/>
+      <c r="H443" t="inlineStr"/>
+      <c r="I443" t="inlineStr"/>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr"/>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/cutout_space_view</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>[444,0][636,76]</t>
+        </is>
+      </c>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr"/>
+      <c r="H444" t="inlineStr"/>
+      <c r="I444" t="inlineStr"/>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr"/>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icon_area</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>[636,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E445" t="inlineStr"/>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr"/>
+      <c r="H445" t="inlineStr"/>
+      <c r="I445" t="inlineStr"/>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr"/>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/system_icons</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>[785,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E446" t="inlineStr"/>
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" t="inlineStr"/>
+      <c r="H446" t="inlineStr"/>
+      <c r="I446" t="inlineStr"/>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr"/>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/statusIcons</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>[785,0][825,96]</t>
+        </is>
+      </c>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="inlineStr"/>
+      <c r="H447" t="inlineStr"/>
+      <c r="I447" t="inlineStr"/>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr"/>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/signal_cluster</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>[825,0][944,96]</t>
+        </is>
+      </c>
+      <c r="E448" t="inlineStr"/>
+      <c r="F448" t="inlineStr"/>
+      <c r="G448" t="inlineStr"/>
+      <c r="H448" t="inlineStr"/>
+      <c r="I448" t="inlineStr"/>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr"/>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/volte_imag</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>[825,30][873,66]</t>
+        </is>
+      </c>
+      <c r="E449" t="inlineStr"/>
+      <c r="F449" t="inlineStr"/>
+      <c r="G449" t="inlineStr"/>
+      <c r="H449" t="inlineStr"/>
+      <c r="I449" t="inlineStr"/>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr"/>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_signal_group</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>[873,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E450" t="inlineStr"/>
+      <c r="F450" t="inlineStr"/>
+      <c r="G450" t="inlineStr"/>
+      <c r="H450" t="inlineStr"/>
+      <c r="I450" t="inlineStr"/>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr"/>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_combo</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>[873,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E451" t="inlineStr"/>
+      <c r="F451" t="inlineStr"/>
+      <c r="G451" t="inlineStr"/>
+      <c r="H451" t="inlineStr"/>
+      <c r="I451" t="inlineStr"/>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr"/>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/data_inout</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>[873,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E452" t="inlineStr"/>
+      <c r="F452" t="inlineStr"/>
+      <c r="G452" t="inlineStr"/>
+      <c r="H452" t="inlineStr"/>
+      <c r="I452" t="inlineStr"/>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr"/>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_type</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>[882,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E453" t="inlineStr"/>
+      <c r="F453" t="inlineStr"/>
+      <c r="G453" t="inlineStr"/>
+      <c r="H453" t="inlineStr"/>
+      <c r="I453" t="inlineStr"/>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr"/>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/mobile_signal</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>[888,30][944,66]</t>
+        </is>
+      </c>
+      <c r="E454" t="inlineStr"/>
+      <c r="F454" t="inlineStr"/>
+      <c r="G454" t="inlineStr"/>
+      <c r="H454" t="inlineStr"/>
+      <c r="I454" t="inlineStr"/>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr"/>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>[944,0][1011,96]</t>
+        </is>
+      </c>
+      <c r="E455" t="inlineStr"/>
+      <c r="F455" t="inlineStr"/>
+      <c r="G455" t="inlineStr"/>
+      <c r="H455" t="inlineStr"/>
+      <c r="I455" t="inlineStr"/>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr"/>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/battery_content</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E456" t="inlineStr"/>
+      <c r="F456" t="inlineStr"/>
+      <c r="G456" t="inlineStr"/>
+      <c r="H456" t="inlineStr"/>
+      <c r="I456" t="inlineStr"/>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr"/>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>com.android.systemui:id/stat_battery_view</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>[949,30][1011,66]</t>
+        </is>
+      </c>
+      <c r="E457" t="inlineStr"/>
+      <c r="F457" t="inlineStr"/>
+      <c r="G457" t="inlineStr"/>
+      <c r="H457" t="inlineStr"/>
+      <c r="I457" t="inlineStr"/>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr"/>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>com.coloros.smartsidebar:id/roundRectView</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>[1062,600][1080,822]</t>
+        </is>
+      </c>
+      <c r="E458" t="inlineStr"/>
+      <c r="F458" t="inlineStr"/>
+      <c r="G458" t="inlineStr"/>
+      <c r="H458" t="inlineStr"/>
+      <c r="I458" t="inlineStr"/>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr"/>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/action_bar_root</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E459" t="inlineStr"/>
+      <c r="F459" t="inlineStr"/>
+      <c r="G459" t="inlineStr"/>
+      <c r="H459" t="inlineStr"/>
+      <c r="I459" t="inlineStr"/>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr"/>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>android:id/content</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E460" t="inlineStr"/>
+      <c r="F460" t="inlineStr"/>
+      <c r="G460" t="inlineStr"/>
+      <c r="H460" t="inlineStr"/>
+      <c r="I460" t="inlineStr"/>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr"/>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_app_container</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E461" t="inlineStr"/>
+      <c r="F461" t="inlineStr"/>
+      <c r="G461" t="inlineStr"/>
+      <c r="H461" t="inlineStr"/>
+      <c r="I461" t="inlineStr"/>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr"/>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_im_tab_popup</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>[0,0][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E462" t="inlineStr"/>
+      <c r="F462" t="inlineStr"/>
+      <c r="G462" t="inlineStr"/>
+      <c r="H462" t="inlineStr"/>
+      <c r="I462" t="inlineStr"/>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr"/>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/status_bar_placeholder2</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>[0,0][1080,132]</t>
+        </is>
+      </c>
+      <c r="E463" t="inlineStr"/>
+      <c r="F463" t="inlineStr"/>
+      <c r="G463" t="inlineStr"/>
+      <c r="H463" t="inlineStr"/>
+      <c r="I463" t="inlineStr"/>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr"/>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/hidden_home_content</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>[0,96][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E464" t="inlineStr"/>
+      <c r="F464" t="inlineStr"/>
+      <c r="G464" t="inlineStr"/>
+      <c r="H464" t="inlineStr"/>
+      <c r="I464" t="inlineStr"/>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr"/>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_content_container</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>[0,96][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E465" t="inlineStr"/>
+      <c r="F465" t="inlineStr"/>
+      <c r="G465" t="inlineStr"/>
+      <c r="H465" t="inlineStr"/>
+      <c r="I465" t="inlineStr"/>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr"/>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_app_container_header_skin</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>[0,96][1080,492]</t>
+        </is>
+      </c>
+      <c r="E466" t="inlineStr"/>
+      <c r="F466" t="inlineStr"/>
+      <c r="G466" t="inlineStr"/>
+      <c r="H466" t="inlineStr"/>
+      <c r="I466" t="inlineStr"/>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr"/>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/skin_parent</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>[0,96][1080,492]</t>
+        </is>
+      </c>
+      <c r="E467" t="inlineStr"/>
+      <c r="F467" t="inlineStr"/>
+      <c r="G467" t="inlineStr"/>
+      <c r="H467" t="inlineStr"/>
+      <c r="I467" t="inlineStr"/>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr"/>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/skin_custom_container</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>[0,96][1080,492]</t>
+        </is>
+      </c>
+      <c r="E468" t="inlineStr"/>
+      <c r="F468" t="inlineStr"/>
+      <c r="G468" t="inlineStr"/>
+      <c r="H468" t="inlineStr"/>
+      <c r="I468" t="inlineStr"/>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr"/>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_app_container_header</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>[0,96][1080,240]</t>
+        </is>
+      </c>
+      <c r="E469" t="inlineStr"/>
+      <c r="F469" t="inlineStr"/>
+      <c r="G469" t="inlineStr"/>
+      <c r="H469" t="inlineStr"/>
+      <c r="I469" t="inlineStr"/>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr"/>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/fl_avatar</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>[0,102][177,234]</t>
+        </is>
+      </c>
+      <c r="E470" t="inlineStr"/>
+      <c r="F470" t="inlineStr"/>
+      <c r="G470" t="inlineStr"/>
+      <c r="H470" t="inlineStr"/>
+      <c r="I470" t="inlineStr"/>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr"/>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/fl_my_avatar</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>[12,114][165,222]</t>
+        </is>
+      </c>
+      <c r="E471" t="inlineStr"/>
+      <c r="F471" t="inlineStr"/>
+      <c r="G471" t="inlineStr"/>
+      <c r="H471" t="inlineStr"/>
+      <c r="I471" t="inlineStr"/>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr"/>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/my_avatar</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>[57,114][165,222]</t>
+        </is>
+      </c>
+      <c r="E472" t="inlineStr"/>
+      <c r="F472" t="inlineStr"/>
+      <c r="G472" t="inlineStr"/>
+      <c r="H472" t="inlineStr"/>
+      <c r="I472" t="inlineStr"/>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr"/>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tv_device_icon</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>[132,189][177,234]</t>
+        </is>
+      </c>
+      <c r="E473" t="inlineStr">
+        <is>
+          <t></t>
+        </is>
+      </c>
+      <c r="F473" t="inlineStr"/>
+      <c r="G473" t="inlineStr"/>
+      <c r="H473" t="inlineStr"/>
+      <c r="I473" t="inlineStr"/>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr"/>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/header_content</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>[177,96][672,240]</t>
+        </is>
+      </c>
+      <c r="E474" t="inlineStr"/>
+      <c r="F474" t="inlineStr"/>
+      <c r="G474" t="inlineStr"/>
+      <c r="H474" t="inlineStr"/>
+      <c r="I474" t="inlineStr"/>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr"/>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/layout_logo</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>[177,114][672,222]</t>
+        </is>
+      </c>
+      <c r="E475" t="inlineStr"/>
+      <c r="F475" t="inlineStr"/>
+      <c r="G475" t="inlineStr"/>
+      <c r="H475" t="inlineStr"/>
+      <c r="I475" t="inlineStr"/>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr"/>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/org_title_v2</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>[213,114][618,222]</t>
+        </is>
+      </c>
+      <c r="E476" t="inlineStr">
+        <is>
+          <t>深圳市芯睿视科技有限公司武汉分公司</t>
+        </is>
+      </c>
+      <c r="F476" t="inlineStr"/>
+      <c r="G476" t="inlineStr"/>
+      <c r="H476" t="inlineStr"/>
+      <c r="I476" t="inlineStr"/>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr"/>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/dt_org_switch</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>[636,150][672,186]</t>
+        </is>
+      </c>
+      <c r="E477" t="inlineStr">
+        <is>
+          <t></t>
+        </is>
+      </c>
+      <c r="F477" t="inlineStr"/>
+      <c r="G477" t="inlineStr"/>
+      <c r="H477" t="inlineStr"/>
+      <c r="I477" t="inlineStr"/>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr"/>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/toolbar_menus_container</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>[672,96][936,240]</t>
+        </is>
+      </c>
+      <c r="E478" t="inlineStr"/>
+      <c r="F478" t="inlineStr"/>
+      <c r="G478" t="inlineStr"/>
+      <c r="H478" t="inlineStr"/>
+      <c r="I478" t="inlineStr"/>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr"/>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_action_bar_button_icon</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>[705,135][771,201]</t>
+        </is>
+      </c>
+      <c r="E479" t="inlineStr"/>
+      <c r="F479" t="inlineStr"/>
+      <c r="G479" t="inlineStr"/>
+      <c r="H479" t="inlineStr"/>
+      <c r="I479" t="inlineStr"/>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr"/>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_action_bar_button_icon</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>[837,135][903,201]</t>
+        </is>
+      </c>
+      <c r="E480" t="inlineStr"/>
+      <c r="F480" t="inlineStr"/>
+      <c r="G480" t="inlineStr"/>
+      <c r="H480" t="inlineStr"/>
+      <c r="I480" t="inlineStr"/>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr"/>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/menu_more</t>
+        </is>
+      </c>
+      <c r="D481" t="inlineStr">
+        <is>
+          <t>[936,96][1068,240]</t>
+        </is>
+      </c>
+      <c r="E481" t="inlineStr"/>
+      <c r="F481" t="inlineStr"/>
+      <c r="G481" t="inlineStr"/>
+      <c r="H481" t="inlineStr"/>
+      <c r="I481" t="inlineStr"/>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr"/>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_action_bar_button_icon</t>
+        </is>
+      </c>
+      <c r="D482" t="inlineStr">
+        <is>
+          <t>[969,135][1035,201]</t>
+        </is>
+      </c>
+      <c r="E482" t="inlineStr"/>
+      <c r="F482" t="inlineStr"/>
+      <c r="G482" t="inlineStr"/>
+      <c r="H482" t="inlineStr"/>
+      <c r="I482" t="inlineStr"/>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr"/>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_content</t>
+        </is>
+      </c>
+      <c r="D483" t="inlineStr">
+        <is>
+          <t>[0,240][1080,2160]</t>
+        </is>
+      </c>
+      <c r="E483" t="inlineStr"/>
+      <c r="F483" t="inlineStr"/>
+      <c r="G483" t="inlineStr"/>
+      <c r="H483" t="inlineStr"/>
+      <c r="I483" t="inlineStr"/>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr"/>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/nested_frame_ly_id</t>
+        </is>
+      </c>
+      <c r="D484" t="inlineStr">
+        <is>
+          <t>[0,240][1080,2160]</t>
+        </is>
+      </c>
+      <c r="E484" t="inlineStr"/>
+      <c r="F484" t="inlineStr"/>
+      <c r="G484" t="inlineStr"/>
+      <c r="H484" t="inlineStr"/>
+      <c r="I484" t="inlineStr"/>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr"/>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/header_panel_id</t>
+        </is>
+      </c>
+      <c r="D485" t="inlineStr">
+        <is>
+          <t>[0,240][1080,645]</t>
+        </is>
+      </c>
+      <c r="E485" t="inlineStr"/>
+      <c r="F485" t="inlineStr"/>
+      <c r="G485" t="inlineStr"/>
+      <c r="H485" t="inlineStr"/>
+      <c r="I485" t="inlineStr"/>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr"/>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/container</t>
+        </is>
+      </c>
+      <c r="D486" t="inlineStr">
+        <is>
+          <t>[0,240][1080,372]</t>
+        </is>
+      </c>
+      <c r="E486" t="inlineStr"/>
+      <c r="F486" t="inlineStr"/>
+      <c r="G486" t="inlineStr"/>
+      <c r="H486" t="inlineStr"/>
+      <c r="I486" t="inlineStr"/>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr"/>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/search_btn</t>
+        </is>
+      </c>
+      <c r="D487" t="inlineStr">
+        <is>
+          <t>[48,264][1032,372]</t>
+        </is>
+      </c>
+      <c r="E487" t="inlineStr"/>
+      <c r="F487" t="inlineStr"/>
+      <c r="G487" t="inlineStr"/>
+      <c r="H487" t="inlineStr"/>
+      <c r="I487" t="inlineStr"/>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr"/>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/if_search</t>
+        </is>
+      </c>
+      <c r="D488" t="inlineStr">
+        <is>
+          <t>[90,297][162,345]</t>
+        </is>
+      </c>
+      <c r="E488" t="inlineStr">
+        <is>
+          <t></t>
+        </is>
+      </c>
+      <c r="F488" t="inlineStr"/>
+      <c r="G488" t="inlineStr"/>
+      <c r="H488" t="inlineStr"/>
+      <c r="I488" t="inlineStr"/>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr"/>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/ts</t>
+        </is>
+      </c>
+      <c r="D489" t="inlineStr">
+        <is>
+          <t>[162,285][258,350]</t>
+        </is>
+      </c>
+      <c r="E489" t="inlineStr"/>
+      <c r="F489" t="inlineStr"/>
+      <c r="G489" t="inlineStr"/>
+      <c r="H489" t="inlineStr"/>
+      <c r="I489" t="inlineStr"/>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr"/>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/container</t>
+        </is>
+      </c>
+      <c r="D490" t="inlineStr">
+        <is>
+          <t>[0,372][1080,504]</t>
+        </is>
+      </c>
+      <c r="E490" t="inlineStr"/>
+      <c r="F490" t="inlineStr"/>
+      <c r="G490" t="inlineStr"/>
+      <c r="H490" t="inlineStr"/>
+      <c r="I490" t="inlineStr"/>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr"/>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/container</t>
+        </is>
+      </c>
+      <c r="D491" t="inlineStr">
+        <is>
+          <t>[0,372][1080,504]</t>
+        </is>
+      </c>
+      <c r="E491" t="inlineStr"/>
+      <c r="F491" t="inlineStr"/>
+      <c r="G491" t="inlineStr"/>
+      <c r="H491" t="inlineStr"/>
+      <c r="I491" t="inlineStr"/>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr"/>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_container</t>
+        </is>
+      </c>
+      <c r="D492" t="inlineStr">
+        <is>
+          <t>[0,372][1080,504]</t>
+        </is>
+      </c>
+      <c r="E492" t="inlineStr"/>
+      <c r="F492" t="inlineStr"/>
+      <c r="G492" t="inlineStr"/>
+      <c r="H492" t="inlineStr"/>
+      <c r="I492" t="inlineStr"/>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr"/>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/im_ding_kit_item_txt</t>
+        </is>
+      </c>
+      <c r="D493" t="inlineStr">
+        <is>
+          <t>[62,412][152,465]</t>
+        </is>
+      </c>
+      <c r="E493" t="inlineStr">
+        <is>
+          <t>日历</t>
+        </is>
+      </c>
+      <c r="F493" t="inlineStr"/>
+      <c r="G493" t="inlineStr"/>
+      <c r="H493" t="inlineStr"/>
+      <c r="I493" t="inlineStr"/>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr"/>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/im_ding_kit_item_txt</t>
+        </is>
+      </c>
+      <c r="D494" t="inlineStr">
+        <is>
+          <t>[251,412][341,465]</t>
+        </is>
+      </c>
+      <c r="E494" t="inlineStr">
+        <is>
+          <t>待办</t>
+        </is>
+      </c>
+      <c r="F494" t="inlineStr"/>
+      <c r="G494" t="inlineStr"/>
+      <c r="H494" t="inlineStr"/>
+      <c r="I494" t="inlineStr"/>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr"/>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/im_ding_kit_item_red_dot</t>
+        </is>
+      </c>
+      <c r="D495" t="inlineStr">
+        <is>
+          <t>[341,411][395,465]</t>
+        </is>
+      </c>
+      <c r="E495" t="inlineStr"/>
+      <c r="F495" t="inlineStr"/>
+      <c r="G495" t="inlineStr"/>
+      <c r="H495" t="inlineStr"/>
+      <c r="I495" t="inlineStr"/>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr"/>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/im_ding_kit_item_txt</t>
+        </is>
+      </c>
+      <c r="D496" t="inlineStr">
+        <is>
+          <t>[460,412][564,465]</t>
+        </is>
+      </c>
+      <c r="E496" t="inlineStr">
+        <is>
+          <t>DING</t>
+        </is>
+      </c>
+      <c r="F496" t="inlineStr"/>
+      <c r="G496" t="inlineStr"/>
+      <c r="H496" t="inlineStr"/>
+      <c r="I496" t="inlineStr"/>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr"/>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/im_ding_kit_item_red_dot</t>
+        </is>
+      </c>
+      <c r="D497" t="inlineStr">
+        <is>
+          <t>[564,411][618,465]</t>
+        </is>
+      </c>
+      <c r="E497" t="inlineStr"/>
+      <c r="F497" t="inlineStr"/>
+      <c r="G497" t="inlineStr"/>
+      <c r="H497" t="inlineStr"/>
+      <c r="I497" t="inlineStr"/>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr"/>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/im_ding_kit_item_txt</t>
+        </is>
+      </c>
+      <c r="D498" t="inlineStr">
+        <is>
+          <t>[695,412][785,465]</t>
+        </is>
+      </c>
+      <c r="E498" t="inlineStr">
+        <is>
+          <t>打卡</t>
+        </is>
+      </c>
+      <c r="F498" t="inlineStr"/>
+      <c r="G498" t="inlineStr"/>
+      <c r="H498" t="inlineStr"/>
+      <c r="I498" t="inlineStr"/>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr"/>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/im_ding_kit_item_red_dot</t>
+        </is>
+      </c>
+      <c r="D499" t="inlineStr">
+        <is>
+          <t>[785,423][815,453]</t>
+        </is>
+      </c>
+      <c r="E499" t="inlineStr"/>
+      <c r="F499" t="inlineStr"/>
+      <c r="G499" t="inlineStr"/>
+      <c r="H499" t="inlineStr"/>
+      <c r="I499" t="inlineStr"/>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr"/>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/im_ding_kit_item_txt</t>
+        </is>
+      </c>
+      <c r="D500" t="inlineStr">
+        <is>
+          <t>[903,412][993,465]</t>
+        </is>
+      </c>
+      <c r="E500" t="inlineStr">
+        <is>
+          <t>更多</t>
+        </is>
+      </c>
+      <c r="F500" t="inlineStr"/>
+      <c r="G500" t="inlineStr"/>
+      <c r="H500" t="inlineStr"/>
+      <c r="I500" t="inlineStr"/>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr"/>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/im_ding_kit_item_more</t>
+        </is>
+      </c>
+      <c r="D501" t="inlineStr">
+        <is>
+          <t>[993,420][1041,456]</t>
+        </is>
+      </c>
+      <c r="E501" t="inlineStr">
+        <is>
+          <t></t>
+        </is>
+      </c>
+      <c r="F501" t="inlineStr"/>
+      <c r="G501" t="inlineStr"/>
+      <c r="H501" t="inlineStr"/>
+      <c r="I501" t="inlineStr"/>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr"/>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/container</t>
+        </is>
+      </c>
+      <c r="D502" t="inlineStr">
+        <is>
+          <t>[0,504][1080,624]</t>
+        </is>
+      </c>
+      <c r="E502" t="inlineStr"/>
+      <c r="F502" t="inlineStr"/>
+      <c r="G502" t="inlineStr"/>
+      <c r="H502" t="inlineStr"/>
+      <c r="I502" t="inlineStr"/>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr"/>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tv_title</t>
+        </is>
+      </c>
+      <c r="D503" t="inlineStr">
+        <is>
+          <t>[132,540][807,593]</t>
+        </is>
+      </c>
+      <c r="E503" t="inlineStr">
+        <is>
+          <t>收不到消息通知？点这里检测一下</t>
+        </is>
+      </c>
+      <c r="F503" t="inlineStr"/>
+      <c r="G503" t="inlineStr"/>
+      <c r="H503" t="inlineStr"/>
+      <c r="I503" t="inlineStr"/>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr"/>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tv_icon</t>
+        </is>
+      </c>
+      <c r="D504" t="inlineStr">
+        <is>
+          <t>[48,534][108,594]</t>
+        </is>
+      </c>
+      <c r="E504" t="inlineStr">
+        <is>
+          <t></t>
+        </is>
+      </c>
+      <c r="F504" t="inlineStr"/>
+      <c r="G504" t="inlineStr"/>
+      <c r="H504" t="inlineStr"/>
+      <c r="I504" t="inlineStr"/>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr"/>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/layout_close</t>
+        </is>
+      </c>
+      <c r="D505" t="inlineStr">
+        <is>
+          <t>[948,504][1068,624]</t>
+        </is>
+      </c>
+      <c r="E505" t="inlineStr"/>
+      <c r="F505" t="inlineStr"/>
+      <c r="G505" t="inlineStr"/>
+      <c r="H505" t="inlineStr"/>
+      <c r="I505" t="inlineStr"/>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr"/>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_panel_id</t>
+        </is>
+      </c>
+      <c r="D506" t="inlineStr">
+        <is>
+          <t>[0,645][1080,777]</t>
+        </is>
+      </c>
+      <c r="E506" t="inlineStr"/>
+      <c r="F506" t="inlineStr"/>
+      <c r="G506" t="inlineStr"/>
+      <c r="H506" t="inlineStr"/>
+      <c r="I506" t="inlineStr"/>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr"/>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/recycler_tab_layout_id</t>
+        </is>
+      </c>
+      <c r="D507" t="inlineStr">
+        <is>
+          <t>[0,645][924,777]</t>
+        </is>
+      </c>
+      <c r="E507" t="inlineStr"/>
+      <c r="F507" t="inlineStr"/>
+      <c r="G507" t="inlineStr"/>
+      <c r="H507" t="inlineStr"/>
+      <c r="I507" t="inlineStr"/>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr"/>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_name</t>
+        </is>
+      </c>
+      <c r="D508" t="inlineStr">
+        <is>
+          <t>[84,669][156,753]</t>
+        </is>
+      </c>
+      <c r="E508" t="inlineStr">
+        <is>
+          <t>全部</t>
+        </is>
+      </c>
+      <c r="F508" t="inlineStr"/>
+      <c r="G508" t="inlineStr"/>
+      <c r="H508" t="inlineStr"/>
+      <c r="I508" t="inlineStr"/>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr"/>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_unread</t>
+        </is>
+      </c>
+      <c r="D509" t="inlineStr">
+        <is>
+          <t>[162,669][204,753]</t>
+        </is>
+      </c>
+      <c r="E509" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F509" t="inlineStr"/>
+      <c r="G509" t="inlineStr"/>
+      <c r="H509" t="inlineStr"/>
+      <c r="I509" t="inlineStr"/>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr"/>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_name</t>
+        </is>
+      </c>
+      <c r="D510" t="inlineStr">
+        <is>
+          <t>[306,669][378,753]</t>
+        </is>
+      </c>
+      <c r="E510" t="inlineStr">
+        <is>
+          <t>未读</t>
+        </is>
+      </c>
+      <c r="F510" t="inlineStr"/>
+      <c r="G510" t="inlineStr"/>
+      <c r="H510" t="inlineStr"/>
+      <c r="I510" t="inlineStr"/>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr"/>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_unread</t>
+        </is>
+      </c>
+      <c r="D511" t="inlineStr">
+        <is>
+          <t>[384,669][424,753]</t>
+        </is>
+      </c>
+      <c r="E511" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F511" t="inlineStr"/>
+      <c r="G511" t="inlineStr"/>
+      <c r="H511" t="inlineStr"/>
+      <c r="I511" t="inlineStr"/>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr"/>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_name</t>
+        </is>
+      </c>
+      <c r="D512" t="inlineStr">
+        <is>
+          <t>[532,669][600,753]</t>
+        </is>
+      </c>
+      <c r="E512" t="inlineStr">
+        <is>
+          <t>@我</t>
+        </is>
+      </c>
+      <c r="F512" t="inlineStr"/>
+      <c r="G512" t="inlineStr"/>
+      <c r="H512" t="inlineStr"/>
+      <c r="I512" t="inlineStr"/>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr"/>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_unread</t>
+        </is>
+      </c>
+      <c r="D513" t="inlineStr">
+        <is>
+          <t>[606,669][626,753]</t>
+        </is>
+      </c>
+      <c r="E513" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F513" t="inlineStr"/>
+      <c r="G513" t="inlineStr"/>
+      <c r="H513" t="inlineStr"/>
+      <c r="I513" t="inlineStr"/>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr"/>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_name</t>
+        </is>
+      </c>
+      <c r="D514" t="inlineStr">
+        <is>
+          <t>[734,669][806,753]</t>
+        </is>
+      </c>
+      <c r="E514" t="inlineStr">
+        <is>
+          <t>单聊</t>
+        </is>
+      </c>
+      <c r="F514" t="inlineStr"/>
+      <c r="G514" t="inlineStr"/>
+      <c r="H514" t="inlineStr"/>
+      <c r="I514" t="inlineStr"/>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr"/>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_name</t>
+        </is>
+      </c>
+      <c r="D515" t="inlineStr">
+        <is>
+          <t>[920,669][924,753]</t>
+        </is>
+      </c>
+      <c r="E515" t="inlineStr">
+        <is>
+          <t>群聊</t>
+        </is>
+      </c>
+      <c r="F515" t="inlineStr"/>
+      <c r="G515" t="inlineStr"/>
+      <c r="H515" t="inlineStr"/>
+      <c r="I515" t="inlineStr"/>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr"/>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_edge_id</t>
+        </is>
+      </c>
+      <c r="D516" t="inlineStr">
+        <is>
+          <t>[888,645][924,777]</t>
+        </is>
+      </c>
+      <c r="E516" t="inlineStr"/>
+      <c r="F516" t="inlineStr"/>
+      <c r="G516" t="inlineStr"/>
+      <c r="H516" t="inlineStr"/>
+      <c r="I516" t="inlineStr"/>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr"/>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/btn_more</t>
+        </is>
+      </c>
+      <c r="D517" t="inlineStr">
+        <is>
+          <t>[924,645][1080,777]</t>
+        </is>
+      </c>
+      <c r="E517" t="inlineStr">
+        <is>
+          <t></t>
+        </is>
+      </c>
+      <c r="F517" t="inlineStr"/>
+      <c r="G517" t="inlineStr"/>
+      <c r="H517" t="inlineStr"/>
+      <c r="I517" t="inlineStr"/>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr"/>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/view_pager_id</t>
+        </is>
+      </c>
+      <c r="D518" t="inlineStr">
+        <is>
+          <t>[0,777][1080,2160]</t>
+        </is>
+      </c>
+      <c r="E518" t="inlineStr"/>
+      <c r="F518" t="inlineStr"/>
+      <c r="G518" t="inlineStr"/>
+      <c r="H518" t="inlineStr"/>
+      <c r="I518" t="inlineStr"/>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr"/>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_item</t>
+        </is>
+      </c>
+      <c r="D519" t="inlineStr">
+        <is>
+          <t>[0,777][1080,963]</t>
+        </is>
+      </c>
+      <c r="E519" t="inlineStr"/>
+      <c r="F519" t="inlineStr"/>
+      <c r="G519" t="inlineStr"/>
+      <c r="H519" t="inlineStr"/>
+      <c r="I519" t="inlineStr"/>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr"/>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_icon</t>
+        </is>
+      </c>
+      <c r="D520" t="inlineStr">
+        <is>
+          <t>[48,804][180,936]</t>
+        </is>
+      </c>
+      <c r="E520" t="inlineStr"/>
+      <c r="F520" t="inlineStr"/>
+      <c r="G520" t="inlineStr"/>
+      <c r="H520" t="inlineStr"/>
+      <c r="I520" t="inlineStr"/>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr"/>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/layout_session_title</t>
+        </is>
+      </c>
+      <c r="D521" t="inlineStr">
+        <is>
+          <t>[216,807][901,872]</t>
+        </is>
+      </c>
+      <c r="E521" t="inlineStr"/>
+      <c r="F521" t="inlineStr"/>
+      <c r="G521" t="inlineStr"/>
+      <c r="H521" t="inlineStr"/>
+      <c r="I521" t="inlineStr"/>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr"/>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_title</t>
+        </is>
+      </c>
+      <c r="D522" t="inlineStr">
+        <is>
+          <t>[216,807][692,872]</t>
+        </is>
+      </c>
+      <c r="E522" t="inlineStr">
+        <is>
+          <t>芯睿视武汉R&amp;D全员群</t>
+        </is>
+      </c>
+      <c r="F522" t="inlineStr"/>
+      <c r="G522" t="inlineStr"/>
+      <c r="H522" t="inlineStr"/>
+      <c r="I522" t="inlineStr"/>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr"/>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/group_tag_layout</t>
+        </is>
+      </c>
+      <c r="D523" t="inlineStr">
+        <is>
+          <t>[698,807][781,872]</t>
+        </is>
+      </c>
+      <c r="E523" t="inlineStr"/>
+      <c r="F523" t="inlineStr"/>
+      <c r="G523" t="inlineStr"/>
+      <c r="H523" t="inlineStr"/>
+      <c r="I523" t="inlineStr"/>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr"/>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_top</t>
+        </is>
+      </c>
+      <c r="D524" t="inlineStr">
+        <is>
+          <t>[1044,789][1068,813]</t>
+        </is>
+      </c>
+      <c r="E524" t="inlineStr">
+        <is>
+          <t></t>
+        </is>
+      </c>
+      <c r="F524" t="inlineStr"/>
+      <c r="G524" t="inlineStr"/>
+      <c r="H524" t="inlineStr"/>
+      <c r="I524" t="inlineStr"/>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr"/>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_gmt</t>
+        </is>
+      </c>
+      <c r="D525" t="inlineStr">
+        <is>
+          <t>[943,815][1032,864]</t>
+        </is>
+      </c>
+      <c r="E525" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="F525" t="inlineStr"/>
+      <c r="G525" t="inlineStr"/>
+      <c r="H525" t="inlineStr"/>
+      <c r="I525" t="inlineStr"/>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr"/>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_content_tv</t>
+        </is>
+      </c>
+      <c r="D526" t="inlineStr">
+        <is>
+          <t>[216,878][954,931]</t>
+        </is>
+      </c>
+      <c r="E526" t="inlineStr">
+        <is>
+          <t>万佳蕾: [表情]</t>
+        </is>
+      </c>
+      <c r="F526" t="inlineStr"/>
+      <c r="G526" t="inlineStr"/>
+      <c r="H526" t="inlineStr"/>
+      <c r="I526" t="inlineStr"/>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr"/>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_unread</t>
+        </is>
+      </c>
+      <c r="D527" t="inlineStr">
+        <is>
+          <t>[978,878][1032,932]</t>
+        </is>
+      </c>
+      <c r="E527" t="inlineStr"/>
+      <c r="F527" t="inlineStr"/>
+      <c r="G527" t="inlineStr"/>
+      <c r="H527" t="inlineStr"/>
+      <c r="I527" t="inlineStr"/>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr"/>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_item</t>
+        </is>
+      </c>
+      <c r="D528" t="inlineStr">
+        <is>
+          <t>[0,963][1080,1149]</t>
+        </is>
+      </c>
+      <c r="E528" t="inlineStr"/>
+      <c r="F528" t="inlineStr"/>
+      <c r="G528" t="inlineStr"/>
+      <c r="H528" t="inlineStr"/>
+      <c r="I528" t="inlineStr"/>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr"/>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_icon</t>
+        </is>
+      </c>
+      <c r="D529" t="inlineStr">
+        <is>
+          <t>[48,990][180,1122]</t>
+        </is>
+      </c>
+      <c r="E529" t="inlineStr"/>
+      <c r="F529" t="inlineStr"/>
+      <c r="G529" t="inlineStr"/>
+      <c r="H529" t="inlineStr"/>
+      <c r="I529" t="inlineStr"/>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr"/>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/layout_session_title</t>
+        </is>
+      </c>
+      <c r="D530" t="inlineStr">
+        <is>
+          <t>[216,993][901,1058]</t>
+        </is>
+      </c>
+      <c r="E530" t="inlineStr"/>
+      <c r="F530" t="inlineStr"/>
+      <c r="G530" t="inlineStr"/>
+      <c r="H530" t="inlineStr"/>
+      <c r="I530" t="inlineStr"/>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr"/>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_title</t>
+        </is>
+      </c>
+      <c r="D531" t="inlineStr">
+        <is>
+          <t>[216,993][566,1058]</t>
+        </is>
+      </c>
+      <c r="E531" t="inlineStr">
+        <is>
+          <t>P6SWMS V1.0.0</t>
+        </is>
+      </c>
+      <c r="F531" t="inlineStr"/>
+      <c r="G531" t="inlineStr"/>
+      <c r="H531" t="inlineStr"/>
+      <c r="I531" t="inlineStr"/>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr"/>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/group_tag_layout</t>
+        </is>
+      </c>
+      <c r="D532" t="inlineStr">
+        <is>
+          <t>[572,993][655,1058]</t>
+        </is>
+      </c>
+      <c r="E532" t="inlineStr"/>
+      <c r="F532" t="inlineStr"/>
+      <c r="G532" t="inlineStr"/>
+      <c r="H532" t="inlineStr"/>
+      <c r="I532" t="inlineStr"/>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr"/>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_top</t>
+        </is>
+      </c>
+      <c r="D533" t="inlineStr">
+        <is>
+          <t>[1044,975][1068,999]</t>
+        </is>
+      </c>
+      <c r="E533" t="inlineStr">
+        <is>
+          <t></t>
+        </is>
+      </c>
+      <c r="F533" t="inlineStr"/>
+      <c r="G533" t="inlineStr"/>
+      <c r="H533" t="inlineStr"/>
+      <c r="I533" t="inlineStr"/>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr"/>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_gmt</t>
+        </is>
+      </c>
+      <c r="D534" t="inlineStr">
+        <is>
+          <t>[943,1001][1032,1050]</t>
+        </is>
+      </c>
+      <c r="E534" t="inlineStr">
+        <is>
+          <t>17:07</t>
+        </is>
+      </c>
+      <c r="F534" t="inlineStr"/>
+      <c r="G534" t="inlineStr"/>
+      <c r="H534" t="inlineStr"/>
+      <c r="I534" t="inlineStr"/>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr"/>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_content_tv</t>
+        </is>
+      </c>
+      <c r="D535" t="inlineStr">
+        <is>
+          <t>[216,1064][1032,1117]</t>
+        </is>
+      </c>
+      <c r="E535" t="inlineStr">
+        <is>
+          <t xml:space="preserve">IOTGFF-242909-ELGHP@张万乐 </t>
+        </is>
+      </c>
+      <c r="F535" t="inlineStr"/>
+      <c r="G535" t="inlineStr"/>
+      <c r="H535" t="inlineStr"/>
+      <c r="I535" t="inlineStr"/>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr"/>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_item</t>
+        </is>
+      </c>
+      <c r="D536" t="inlineStr">
+        <is>
+          <t>[0,1149][1080,1335]</t>
+        </is>
+      </c>
+      <c r="E536" t="inlineStr"/>
+      <c r="F536" t="inlineStr"/>
+      <c r="G536" t="inlineStr"/>
+      <c r="H536" t="inlineStr"/>
+      <c r="I536" t="inlineStr"/>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr"/>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_icon</t>
+        </is>
+      </c>
+      <c r="D537" t="inlineStr">
+        <is>
+          <t>[48,1176][180,1308]</t>
+        </is>
+      </c>
+      <c r="E537" t="inlineStr"/>
+      <c r="F537" t="inlineStr"/>
+      <c r="G537" t="inlineStr"/>
+      <c r="H537" t="inlineStr"/>
+      <c r="I537" t="inlineStr"/>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr"/>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/layout_session_title</t>
+        </is>
+      </c>
+      <c r="D538" t="inlineStr">
+        <is>
+          <t>[216,1179][901,1244]</t>
+        </is>
+      </c>
+      <c r="E538" t="inlineStr"/>
+      <c r="F538" t="inlineStr"/>
+      <c r="G538" t="inlineStr"/>
+      <c r="H538" t="inlineStr"/>
+      <c r="I538" t="inlineStr"/>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr"/>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_title</t>
+        </is>
+      </c>
+      <c r="D539" t="inlineStr">
+        <is>
+          <t>[216,1179][577,1244]</t>
+        </is>
+      </c>
+      <c r="E539" t="inlineStr">
+        <is>
+          <t>平台&amp;APP测试组</t>
+        </is>
+      </c>
+      <c r="F539" t="inlineStr"/>
+      <c r="G539" t="inlineStr"/>
+      <c r="H539" t="inlineStr"/>
+      <c r="I539" t="inlineStr"/>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr"/>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/group_tag_layout</t>
+        </is>
+      </c>
+      <c r="D540" t="inlineStr">
+        <is>
+          <t>[583,1179][755,1244]</t>
+        </is>
+      </c>
+      <c r="E540" t="inlineStr"/>
+      <c r="F540" t="inlineStr"/>
+      <c r="G540" t="inlineStr"/>
+      <c r="H540" t="inlineStr"/>
+      <c r="I540" t="inlineStr"/>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr"/>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_top</t>
+        </is>
+      </c>
+      <c r="D541" t="inlineStr">
+        <is>
+          <t>[1044,1161][1068,1185]</t>
+        </is>
+      </c>
+      <c r="E541" t="inlineStr">
+        <is>
+          <t></t>
+        </is>
+      </c>
+      <c r="F541" t="inlineStr"/>
+      <c r="G541" t="inlineStr"/>
+      <c r="H541" t="inlineStr"/>
+      <c r="I541" t="inlineStr"/>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr"/>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_gmt</t>
+        </is>
+      </c>
+      <c r="D542" t="inlineStr">
+        <is>
+          <t>[943,1187][1032,1236]</t>
+        </is>
+      </c>
+      <c r="E542" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
+      <c r="F542" t="inlineStr"/>
+      <c r="G542" t="inlineStr"/>
+      <c r="H542" t="inlineStr"/>
+      <c r="I542" t="inlineStr"/>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr"/>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_content_tv</t>
+        </is>
+      </c>
+      <c r="D543" t="inlineStr">
+        <is>
+          <t>[216,1250][1032,1303]</t>
+        </is>
+      </c>
+      <c r="E543" t="inlineStr">
+        <is>
+          <t>[特别关注] 刘芳: @所有人 目前手上项目进展情况统计</t>
+        </is>
+      </c>
+      <c r="F543" t="inlineStr"/>
+      <c r="G543" t="inlineStr"/>
+      <c r="H543" t="inlineStr"/>
+      <c r="I543" t="inlineStr"/>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr"/>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_item</t>
+        </is>
+      </c>
+      <c r="D544" t="inlineStr">
+        <is>
+          <t>[0,1335][1080,1521]</t>
+        </is>
+      </c>
+      <c r="E544" t="inlineStr"/>
+      <c r="F544" t="inlineStr"/>
+      <c r="G544" t="inlineStr"/>
+      <c r="H544" t="inlineStr"/>
+      <c r="I544" t="inlineStr"/>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr"/>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_icon</t>
+        </is>
+      </c>
+      <c r="D545" t="inlineStr">
+        <is>
+          <t>[48,1362][180,1494]</t>
+        </is>
+      </c>
+      <c r="E545" t="inlineStr"/>
+      <c r="F545" t="inlineStr"/>
+      <c r="G545" t="inlineStr"/>
+      <c r="H545" t="inlineStr"/>
+      <c r="I545" t="inlineStr"/>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr"/>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/layout_session_title</t>
+        </is>
+      </c>
+      <c r="D546" t="inlineStr">
+        <is>
+          <t>[216,1365][901,1430]</t>
+        </is>
+      </c>
+      <c r="E546" t="inlineStr"/>
+      <c r="F546" t="inlineStr"/>
+      <c r="G546" t="inlineStr"/>
+      <c r="H546" t="inlineStr"/>
+      <c r="I546" t="inlineStr"/>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr"/>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_title</t>
+        </is>
+      </c>
+      <c r="D547" t="inlineStr">
+        <is>
+          <t>[216,1365][717,1430]</t>
+        </is>
+      </c>
+      <c r="E547" t="inlineStr">
+        <is>
+          <t>EasyVMS v4.6.0（P6SC2400098）</t>
+        </is>
+      </c>
+      <c r="F547" t="inlineStr"/>
+      <c r="G547" t="inlineStr"/>
+      <c r="H547" t="inlineStr"/>
+      <c r="I547" t="inlineStr"/>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr"/>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/group_tag_layout</t>
+        </is>
+      </c>
+      <c r="D548" t="inlineStr">
+        <is>
+          <t>[723,1365][895,1430]</t>
+        </is>
+      </c>
+      <c r="E548" t="inlineStr"/>
+      <c r="F548" t="inlineStr"/>
+      <c r="G548" t="inlineStr"/>
+      <c r="H548" t="inlineStr"/>
+      <c r="I548" t="inlineStr"/>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr"/>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_top</t>
+        </is>
+      </c>
+      <c r="D549" t="inlineStr">
+        <is>
+          <t>[1044,1347][1068,1371]</t>
+        </is>
+      </c>
+      <c r="E549" t="inlineStr">
+        <is>
+          <t></t>
+        </is>
+      </c>
+      <c r="F549" t="inlineStr"/>
+      <c r="G549" t="inlineStr"/>
+      <c r="H549" t="inlineStr"/>
+      <c r="I549" t="inlineStr"/>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr"/>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_gmt</t>
+        </is>
+      </c>
+      <c r="D550" t="inlineStr">
+        <is>
+          <t>[943,1373][1032,1422]</t>
+        </is>
+      </c>
+      <c r="E550" t="inlineStr">
+        <is>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="F550" t="inlineStr"/>
+      <c r="G550" t="inlineStr"/>
+      <c r="H550" t="inlineStr"/>
+      <c r="I550" t="inlineStr"/>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr"/>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_content_tv</t>
+        </is>
+      </c>
+      <c r="D551" t="inlineStr">
+        <is>
+          <t>[216,1436][1032,1489]</t>
+        </is>
+      </c>
+      <c r="E551" t="inlineStr">
+        <is>
+          <t xml:space="preserve">陈劲伟: @钱欢欢 </t>
+        </is>
+      </c>
+      <c r="F551" t="inlineStr"/>
+      <c r="G551" t="inlineStr"/>
+      <c r="H551" t="inlineStr"/>
+      <c r="I551" t="inlineStr"/>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr"/>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_item</t>
+        </is>
+      </c>
+      <c r="D552" t="inlineStr">
+        <is>
+          <t>[0,1521][1080,1707]</t>
+        </is>
+      </c>
+      <c r="E552" t="inlineStr"/>
+      <c r="F552" t="inlineStr"/>
+      <c r="G552" t="inlineStr"/>
+      <c r="H552" t="inlineStr"/>
+      <c r="I552" t="inlineStr"/>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr"/>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_icon</t>
+        </is>
+      </c>
+      <c r="D553" t="inlineStr">
+        <is>
+          <t>[48,1548][180,1680]</t>
+        </is>
+      </c>
+      <c r="E553" t="inlineStr"/>
+      <c r="F553" t="inlineStr"/>
+      <c r="G553" t="inlineStr"/>
+      <c r="H553" t="inlineStr"/>
+      <c r="I553" t="inlineStr"/>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr"/>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/layout_session_title</t>
+        </is>
+      </c>
+      <c r="D554" t="inlineStr">
+        <is>
+          <t>[216,1551][901,1616]</t>
+        </is>
+      </c>
+      <c r="E554" t="inlineStr"/>
+      <c r="F554" t="inlineStr"/>
+      <c r="G554" t="inlineStr"/>
+      <c r="H554" t="inlineStr"/>
+      <c r="I554" t="inlineStr"/>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr"/>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_title</t>
+        </is>
+      </c>
+      <c r="D555" t="inlineStr">
+        <is>
+          <t>[216,1551][456,1616]</t>
+        </is>
+      </c>
+      <c r="E555" t="inlineStr">
+        <is>
+          <t>我（陈熙）</t>
+        </is>
+      </c>
+      <c r="F555" t="inlineStr"/>
+      <c r="G555" t="inlineStr"/>
+      <c r="H555" t="inlineStr"/>
+      <c r="I555" t="inlineStr"/>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr"/>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_top</t>
+        </is>
+      </c>
+      <c r="D556" t="inlineStr">
+        <is>
+          <t>[1044,1533][1068,1557]</t>
+        </is>
+      </c>
+      <c r="E556" t="inlineStr">
+        <is>
+          <t></t>
+        </is>
+      </c>
+      <c r="F556" t="inlineStr"/>
+      <c r="G556" t="inlineStr"/>
+      <c r="H556" t="inlineStr"/>
+      <c r="I556" t="inlineStr"/>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr"/>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_gmt</t>
+        </is>
+      </c>
+      <c r="D557" t="inlineStr">
+        <is>
+          <t>[943,1559][1032,1608]</t>
+        </is>
+      </c>
+      <c r="E557" t="inlineStr">
+        <is>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="F557" t="inlineStr"/>
+      <c r="G557" t="inlineStr"/>
+      <c r="H557" t="inlineStr"/>
+      <c r="I557" t="inlineStr"/>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr"/>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_content_tv</t>
+        </is>
+      </c>
+      <c r="D558" t="inlineStr">
+        <is>
+          <t>[216,1622][1032,1675]</t>
+        </is>
+      </c>
+      <c r="E558" t="inlineStr">
+        <is>
+          <t>[图片]</t>
+        </is>
+      </c>
+      <c r="F558" t="inlineStr"/>
+      <c r="G558" t="inlineStr"/>
+      <c r="H558" t="inlineStr"/>
+      <c r="I558" t="inlineStr"/>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr"/>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_item</t>
+        </is>
+      </c>
+      <c r="D559" t="inlineStr">
+        <is>
+          <t>[0,1707][1080,1893]</t>
+        </is>
+      </c>
+      <c r="E559" t="inlineStr"/>
+      <c r="F559" t="inlineStr"/>
+      <c r="G559" t="inlineStr"/>
+      <c r="H559" t="inlineStr"/>
+      <c r="I559" t="inlineStr"/>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr"/>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_icon</t>
+        </is>
+      </c>
+      <c r="D560" t="inlineStr">
+        <is>
+          <t>[48,1734][180,1866]</t>
+        </is>
+      </c>
+      <c r="E560" t="inlineStr"/>
+      <c r="F560" t="inlineStr"/>
+      <c r="G560" t="inlineStr"/>
+      <c r="H560" t="inlineStr"/>
+      <c r="I560" t="inlineStr"/>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr"/>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/layout_session_title</t>
+        </is>
+      </c>
+      <c r="D561" t="inlineStr">
+        <is>
+          <t>[216,1737][901,1802]</t>
+        </is>
+      </c>
+      <c r="E561" t="inlineStr"/>
+      <c r="F561" t="inlineStr"/>
+      <c r="G561" t="inlineStr"/>
+      <c r="H561" t="inlineStr"/>
+      <c r="I561" t="inlineStr"/>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr"/>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_title</t>
+        </is>
+      </c>
+      <c r="D562" t="inlineStr">
+        <is>
+          <t>[216,1737][889,1802]</t>
+        </is>
+      </c>
+      <c r="E562" t="inlineStr">
+        <is>
+          <t>工作通知:深圳市芯睿视科技有限公司武汉分公司</t>
+        </is>
+      </c>
+      <c r="F562" t="inlineStr"/>
+      <c r="G562" t="inlineStr"/>
+      <c r="H562" t="inlineStr"/>
+      <c r="I562" t="inlineStr"/>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr"/>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_top</t>
+        </is>
+      </c>
+      <c r="D563" t="inlineStr">
+        <is>
+          <t>[1044,1719][1068,1743]</t>
+        </is>
+      </c>
+      <c r="E563" t="inlineStr">
+        <is>
+          <t></t>
+        </is>
+      </c>
+      <c r="F563" t="inlineStr"/>
+      <c r="G563" t="inlineStr"/>
+      <c r="H563" t="inlineStr"/>
+      <c r="I563" t="inlineStr"/>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr"/>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_gmt</t>
+        </is>
+      </c>
+      <c r="D564" t="inlineStr">
+        <is>
+          <t>[943,1745][1032,1794]</t>
+        </is>
+      </c>
+      <c r="E564" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="F564" t="inlineStr"/>
+      <c r="G564" t="inlineStr"/>
+      <c r="H564" t="inlineStr"/>
+      <c r="I564" t="inlineStr"/>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr"/>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_content_tv</t>
+        </is>
+      </c>
+      <c r="D565" t="inlineStr">
+        <is>
+          <t>[216,1808][1032,1861]</t>
+        </is>
+      </c>
+      <c r="E565" t="inlineStr">
+        <is>
+          <t>智能填表: 员工午餐订购（2月）的副本-2</t>
+        </is>
+      </c>
+      <c r="F565" t="inlineStr"/>
+      <c r="G565" t="inlineStr"/>
+      <c r="H565" t="inlineStr"/>
+      <c r="I565" t="inlineStr"/>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr"/>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_item</t>
+        </is>
+      </c>
+      <c r="D566" t="inlineStr">
+        <is>
+          <t>[0,1893][1080,2079]</t>
+        </is>
+      </c>
+      <c r="E566" t="inlineStr"/>
+      <c r="F566" t="inlineStr"/>
+      <c r="G566" t="inlineStr"/>
+      <c r="H566" t="inlineStr"/>
+      <c r="I566" t="inlineStr"/>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr"/>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_icon</t>
+        </is>
+      </c>
+      <c r="D567" t="inlineStr">
+        <is>
+          <t>[48,1920][180,2052]</t>
+        </is>
+      </c>
+      <c r="E567" t="inlineStr"/>
+      <c r="F567" t="inlineStr"/>
+      <c r="G567" t="inlineStr"/>
+      <c r="H567" t="inlineStr"/>
+      <c r="I567" t="inlineStr"/>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr"/>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/layout_session_title</t>
+        </is>
+      </c>
+      <c r="D568" t="inlineStr">
+        <is>
+          <t>[216,1923][901,1988]</t>
+        </is>
+      </c>
+      <c r="E568" t="inlineStr"/>
+      <c r="F568" t="inlineStr"/>
+      <c r="G568" t="inlineStr"/>
+      <c r="H568" t="inlineStr"/>
+      <c r="I568" t="inlineStr"/>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr"/>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_title</t>
+        </is>
+      </c>
+      <c r="D569" t="inlineStr">
+        <is>
+          <t>[216,1923][569,1988]</t>
+        </is>
+      </c>
+      <c r="E569" t="inlineStr">
+        <is>
+          <t>P6SOPS v3.1.0()</t>
+        </is>
+      </c>
+      <c r="F569" t="inlineStr"/>
+      <c r="G569" t="inlineStr"/>
+      <c r="H569" t="inlineStr"/>
+      <c r="I569" t="inlineStr"/>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr"/>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/group_tag_layout</t>
+        </is>
+      </c>
+      <c r="D570" t="inlineStr">
+        <is>
+          <t>[575,1923][658,1988]</t>
+        </is>
+      </c>
+      <c r="E570" t="inlineStr"/>
+      <c r="F570" t="inlineStr"/>
+      <c r="G570" t="inlineStr"/>
+      <c r="H570" t="inlineStr"/>
+      <c r="I570" t="inlineStr"/>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr"/>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_top</t>
+        </is>
+      </c>
+      <c r="D571" t="inlineStr">
+        <is>
+          <t>[1044,1905][1068,1929]</t>
+        </is>
+      </c>
+      <c r="E571" t="inlineStr">
+        <is>
+          <t></t>
+        </is>
+      </c>
+      <c r="F571" t="inlineStr"/>
+      <c r="G571" t="inlineStr"/>
+      <c r="H571" t="inlineStr"/>
+      <c r="I571" t="inlineStr"/>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr"/>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_gmt</t>
+        </is>
+      </c>
+      <c r="D572" t="inlineStr">
+        <is>
+          <t>[943,1931][1032,1980]</t>
+        </is>
+      </c>
+      <c r="E572" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="F572" t="inlineStr"/>
+      <c r="G572" t="inlineStr"/>
+      <c r="H572" t="inlineStr"/>
+      <c r="I572" t="inlineStr"/>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr"/>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_content_tv</t>
+        </is>
+      </c>
+      <c r="D573" t="inlineStr">
+        <is>
+          <t>[216,1994][1032,2047]</t>
+        </is>
+      </c>
+      <c r="E573" t="inlineStr">
+        <is>
+          <t xml:space="preserve">程晓东: @张亮 </t>
+        </is>
+      </c>
+      <c r="F573" t="inlineStr"/>
+      <c r="G573" t="inlineStr"/>
+      <c r="H573" t="inlineStr"/>
+      <c r="I573" t="inlineStr"/>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr"/>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_item</t>
+        </is>
+      </c>
+      <c r="D574" t="inlineStr">
+        <is>
+          <t>[0,2079][1080,2160]</t>
+        </is>
+      </c>
+      <c r="E574" t="inlineStr"/>
+      <c r="F574" t="inlineStr"/>
+      <c r="G574" t="inlineStr"/>
+      <c r="H574" t="inlineStr"/>
+      <c r="I574" t="inlineStr"/>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr"/>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_icon</t>
+        </is>
+      </c>
+      <c r="D575" t="inlineStr">
+        <is>
+          <t>[48,2106][180,2160]</t>
+        </is>
+      </c>
+      <c r="E575" t="inlineStr"/>
+      <c r="F575" t="inlineStr"/>
+      <c r="G575" t="inlineStr"/>
+      <c r="H575" t="inlineStr"/>
+      <c r="I575" t="inlineStr"/>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr"/>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/layout_session_title</t>
+        </is>
+      </c>
+      <c r="D576" t="inlineStr">
+        <is>
+          <t>[216,2109][918,2160]</t>
+        </is>
+      </c>
+      <c r="E576" t="inlineStr"/>
+      <c r="F576" t="inlineStr"/>
+      <c r="G576" t="inlineStr"/>
+      <c r="H576" t="inlineStr"/>
+      <c r="I576" t="inlineStr"/>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr"/>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_title</t>
+        </is>
+      </c>
+      <c r="D577" t="inlineStr">
+        <is>
+          <t>[216,2109][823,2160]</t>
+        </is>
+      </c>
+      <c r="E577" t="inlineStr">
+        <is>
+          <t>EasySeries客户端软件问题反馈群</t>
+        </is>
+      </c>
+      <c r="F577" t="inlineStr"/>
+      <c r="G577" t="inlineStr"/>
+      <c r="H577" t="inlineStr"/>
+      <c r="I577" t="inlineStr"/>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr"/>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/group_tag_layout</t>
+        </is>
+      </c>
+      <c r="D578" t="inlineStr">
+        <is>
+          <t>[829,2109][912,2160]</t>
+        </is>
+      </c>
+      <c r="E578" t="inlineStr"/>
+      <c r="F578" t="inlineStr"/>
+      <c r="G578" t="inlineStr"/>
+      <c r="H578" t="inlineStr"/>
+      <c r="I578" t="inlineStr"/>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr"/>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_top</t>
+        </is>
+      </c>
+      <c r="D579" t="inlineStr">
+        <is>
+          <t>[1044,2091][1068,2115]</t>
+        </is>
+      </c>
+      <c r="E579" t="inlineStr">
+        <is>
+          <t></t>
+        </is>
+      </c>
+      <c r="F579" t="inlineStr"/>
+      <c r="G579" t="inlineStr"/>
+      <c r="H579" t="inlineStr"/>
+      <c r="I579" t="inlineStr"/>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr"/>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/session_gmt</t>
+        </is>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>[960,2117][1032,2160]</t>
+        </is>
+      </c>
+      <c r="E580" t="inlineStr">
+        <is>
+          <t>昨天</t>
+        </is>
+      </c>
+      <c r="F580" t="inlineStr"/>
+      <c r="G580" t="inlineStr"/>
+      <c r="H580" t="inlineStr"/>
+      <c r="I580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr"/>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/view_tab_placeholder</t>
+        </is>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>[0,2160][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E581" t="inlineStr"/>
+      <c r="F581" t="inlineStr"/>
+      <c r="G581" t="inlineStr"/>
+      <c r="H581" t="inlineStr"/>
+      <c r="I581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr"/>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/root_container</t>
+        </is>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>[0,2160][1080,2340]</t>
+        </is>
+      </c>
+      <c r="E582" t="inlineStr"/>
+      <c r="F582" t="inlineStr"/>
+      <c r="G582" t="inlineStr"/>
+      <c r="H582" t="inlineStr"/>
+      <c r="I582" t="inlineStr"/>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr"/>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/divider</t>
+        </is>
+      </c>
+      <c r="D583" t="inlineStr">
+        <is>
+          <t>[0,2160][1080,2161]</t>
+        </is>
+      </c>
+      <c r="E583" t="inlineStr"/>
+      <c r="F583" t="inlineStr"/>
+      <c r="G583" t="inlineStr"/>
+      <c r="H583" t="inlineStr"/>
+      <c r="I583" t="inlineStr"/>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr"/>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/tab_container</t>
+        </is>
+      </c>
+      <c r="D584" t="inlineStr">
+        <is>
+          <t>[0,2161][1080,2325]</t>
+        </is>
+      </c>
+      <c r="E584" t="inlineStr"/>
+      <c r="F584" t="inlineStr"/>
+      <c r="G584" t="inlineStr"/>
+      <c r="H584" t="inlineStr"/>
+      <c r="I584" t="inlineStr"/>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr"/>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_app_item</t>
+        </is>
+      </c>
+      <c r="D585" t="inlineStr">
+        <is>
+          <t>[0,2161][226,2325]</t>
+        </is>
+      </c>
+      <c r="E585" t="inlineStr"/>
+      <c r="F585" t="inlineStr"/>
+      <c r="G585" t="inlineStr"/>
+      <c r="H585" t="inlineStr"/>
+      <c r="I585" t="inlineStr"/>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr"/>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_icon_group</t>
+        </is>
+      </c>
+      <c r="D586" t="inlineStr">
+        <is>
+          <t>[60,2191][165,2296]</t>
+        </is>
+      </c>
+      <c r="E586" t="inlineStr"/>
+      <c r="F586" t="inlineStr"/>
+      <c r="G586" t="inlineStr"/>
+      <c r="H586" t="inlineStr"/>
+      <c r="I586" t="inlineStr"/>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr"/>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/lottie_switch</t>
+        </is>
+      </c>
+      <c r="D587" t="inlineStr">
+        <is>
+          <t>[76,2191][148,2263]</t>
+        </is>
+      </c>
+      <c r="E587" t="inlineStr"/>
+      <c r="F587" t="inlineStr"/>
+      <c r="G587" t="inlineStr"/>
+      <c r="H587" t="inlineStr"/>
+      <c r="I587" t="inlineStr"/>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr"/>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_red_dot_text</t>
+        </is>
+      </c>
+      <c r="D588" t="inlineStr">
+        <is>
+          <t>[120,2176][184,2230]</t>
+        </is>
+      </c>
+      <c r="E588" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="F588" t="inlineStr"/>
+      <c r="G588" t="inlineStr"/>
+      <c r="H588" t="inlineStr"/>
+      <c r="I588" t="inlineStr"/>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr"/>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/fl_bottom_text</t>
+        </is>
+      </c>
+      <c r="D589" t="inlineStr">
+        <is>
+          <t>[83,2269][143,2325]</t>
+        </is>
+      </c>
+      <c r="E589" t="inlineStr"/>
+      <c r="F589" t="inlineStr"/>
+      <c r="G589" t="inlineStr"/>
+      <c r="H589" t="inlineStr"/>
+      <c r="I589" t="inlineStr"/>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr"/>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_text_highlight</t>
+        </is>
+      </c>
+      <c r="D590" t="inlineStr">
+        <is>
+          <t>[83,2269][143,2310]</t>
+        </is>
+      </c>
+      <c r="E590" t="inlineStr">
+        <is>
+          <t>消息</t>
+        </is>
+      </c>
+      <c r="F590" t="inlineStr"/>
+      <c r="G590" t="inlineStr"/>
+      <c r="H590" t="inlineStr"/>
+      <c r="I590" t="inlineStr"/>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr"/>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_app_item</t>
+        </is>
+      </c>
+      <c r="D591" t="inlineStr">
+        <is>
+          <t>[226,2161][442,2325]</t>
+        </is>
+      </c>
+      <c r="E591" t="inlineStr"/>
+      <c r="F591" t="inlineStr"/>
+      <c r="G591" t="inlineStr"/>
+      <c r="H591" t="inlineStr"/>
+      <c r="I591" t="inlineStr"/>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr"/>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_icon_group</t>
+        </is>
+      </c>
+      <c r="D592" t="inlineStr">
+        <is>
+          <t>[281,2191][386,2296]</t>
+        </is>
+      </c>
+      <c r="E592" t="inlineStr"/>
+      <c r="F592" t="inlineStr"/>
+      <c r="G592" t="inlineStr"/>
+      <c r="H592" t="inlineStr"/>
+      <c r="I592" t="inlineStr"/>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr"/>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_icon</t>
+        </is>
+      </c>
+      <c r="D593" t="inlineStr">
+        <is>
+          <t>[297,2191][369,2263]</t>
+        </is>
+      </c>
+      <c r="E593" t="inlineStr"/>
+      <c r="F593" t="inlineStr"/>
+      <c r="G593" t="inlineStr"/>
+      <c r="H593" t="inlineStr"/>
+      <c r="I593" t="inlineStr"/>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr"/>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_red_dot_text</t>
+        </is>
+      </c>
+      <c r="D594" t="inlineStr">
+        <is>
+          <t>[341,2176][395,2230]</t>
+        </is>
+      </c>
+      <c r="E594" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="F594" t="inlineStr"/>
+      <c r="G594" t="inlineStr"/>
+      <c r="H594" t="inlineStr"/>
+      <c r="I594" t="inlineStr"/>
+    </row>
+    <row r="595">
+      <c r="A595" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B595" t="inlineStr"/>
+      <c r="C595" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/fl_bottom_text</t>
+        </is>
+      </c>
+      <c r="D595" t="inlineStr">
+        <is>
+          <t>[304,2269][364,2325]</t>
+        </is>
+      </c>
+      <c r="E595" t="inlineStr"/>
+      <c r="F595" t="inlineStr"/>
+      <c r="G595" t="inlineStr"/>
+      <c r="H595" t="inlineStr"/>
+      <c r="I595" t="inlineStr"/>
+    </row>
+    <row r="596">
+      <c r="A596" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B596" t="inlineStr"/>
+      <c r="C596" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_text</t>
+        </is>
+      </c>
+      <c r="D596" t="inlineStr">
+        <is>
+          <t>[304,2269][364,2310]</t>
+        </is>
+      </c>
+      <c r="E596" t="inlineStr">
+        <is>
+          <t>协作</t>
+        </is>
+      </c>
+      <c r="F596" t="inlineStr"/>
+      <c r="G596" t="inlineStr"/>
+      <c r="H596" t="inlineStr"/>
+      <c r="I596" t="inlineStr"/>
+    </row>
+    <row r="597">
+      <c r="A597" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B597" t="inlineStr"/>
+      <c r="C597" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_app_item</t>
+        </is>
+      </c>
+      <c r="D597" t="inlineStr">
+        <is>
+          <t>[442,2161][664,2325]</t>
+        </is>
+      </c>
+      <c r="E597" t="inlineStr"/>
+      <c r="F597" t="inlineStr"/>
+      <c r="G597" t="inlineStr"/>
+      <c r="H597" t="inlineStr"/>
+      <c r="I597" t="inlineStr"/>
+    </row>
+    <row r="598">
+      <c r="A598" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B598" t="inlineStr"/>
+      <c r="C598" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_icon_group</t>
+        </is>
+      </c>
+      <c r="D598" t="inlineStr">
+        <is>
+          <t>[500,2191][605,2296]</t>
+        </is>
+      </c>
+      <c r="E598" t="inlineStr"/>
+      <c r="F598" t="inlineStr"/>
+      <c r="G598" t="inlineStr"/>
+      <c r="H598" t="inlineStr"/>
+      <c r="I598" t="inlineStr"/>
+    </row>
+    <row r="599">
+      <c r="A599" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B599" t="inlineStr"/>
+      <c r="C599" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_icon</t>
+        </is>
+      </c>
+      <c r="D599" t="inlineStr">
+        <is>
+          <t>[516,2191][588,2263]</t>
+        </is>
+      </c>
+      <c r="E599" t="inlineStr"/>
+      <c r="F599" t="inlineStr"/>
+      <c r="G599" t="inlineStr"/>
+      <c r="H599" t="inlineStr"/>
+      <c r="I599" t="inlineStr"/>
+    </row>
+    <row r="600">
+      <c r="A600" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B600" t="inlineStr"/>
+      <c r="C600" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/fl_bottom_text</t>
+        </is>
+      </c>
+      <c r="D600" t="inlineStr">
+        <is>
+          <t>[508,2269][598,2325]</t>
+        </is>
+      </c>
+      <c r="E600" t="inlineStr"/>
+      <c r="F600" t="inlineStr"/>
+      <c r="G600" t="inlineStr"/>
+      <c r="H600" t="inlineStr"/>
+      <c r="I600" t="inlineStr"/>
+    </row>
+    <row r="601">
+      <c r="A601" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B601" t="inlineStr"/>
+      <c r="C601" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_text</t>
+        </is>
+      </c>
+      <c r="D601" t="inlineStr">
+        <is>
+          <t>[508,2269][598,2310]</t>
+        </is>
+      </c>
+      <c r="E601" t="inlineStr">
+        <is>
+          <t>工作台</t>
+        </is>
+      </c>
+      <c r="F601" t="inlineStr"/>
+      <c r="G601" t="inlineStr"/>
+      <c r="H601" t="inlineStr"/>
+      <c r="I601" t="inlineStr"/>
+    </row>
+    <row r="602">
+      <c r="A602" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B602" t="inlineStr"/>
+      <c r="C602" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_app_item</t>
+        </is>
+      </c>
+      <c r="D602" t="inlineStr">
+        <is>
+          <t>[664,2161][872,2325]</t>
+        </is>
+      </c>
+      <c r="E602" t="inlineStr"/>
+      <c r="F602" t="inlineStr"/>
+      <c r="G602" t="inlineStr"/>
+      <c r="H602" t="inlineStr"/>
+      <c r="I602" t="inlineStr"/>
+    </row>
+    <row r="603">
+      <c r="A603" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B603" t="inlineStr"/>
+      <c r="C603" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_icon_group</t>
+        </is>
+      </c>
+      <c r="D603" t="inlineStr">
+        <is>
+          <t>[715,2191][820,2296]</t>
+        </is>
+      </c>
+      <c r="E603" t="inlineStr"/>
+      <c r="F603" t="inlineStr"/>
+      <c r="G603" t="inlineStr"/>
+      <c r="H603" t="inlineStr"/>
+      <c r="I603" t="inlineStr"/>
+    </row>
+    <row r="604">
+      <c r="A604" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B604" t="inlineStr"/>
+      <c r="C604" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_icon</t>
+        </is>
+      </c>
+      <c r="D604" t="inlineStr">
+        <is>
+          <t>[731,2191][803,2263]</t>
+        </is>
+      </c>
+      <c r="E604" t="inlineStr"/>
+      <c r="F604" t="inlineStr"/>
+      <c r="G604" t="inlineStr"/>
+      <c r="H604" t="inlineStr"/>
+      <c r="I604" t="inlineStr"/>
+    </row>
+    <row r="605">
+      <c r="A605" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B605" t="inlineStr"/>
+      <c r="C605" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/fl_bottom_text</t>
+        </is>
+      </c>
+      <c r="D605" t="inlineStr">
+        <is>
+          <t>[723,2269][813,2325]</t>
+        </is>
+      </c>
+      <c r="E605" t="inlineStr"/>
+      <c r="F605" t="inlineStr"/>
+      <c r="G605" t="inlineStr"/>
+      <c r="H605" t="inlineStr"/>
+      <c r="I605" t="inlineStr"/>
+    </row>
+    <row r="606">
+      <c r="A606" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B606" t="inlineStr"/>
+      <c r="C606" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_text</t>
+        </is>
+      </c>
+      <c r="D606" t="inlineStr">
+        <is>
+          <t>[723,2269][813,2310]</t>
+        </is>
+      </c>
+      <c r="E606" t="inlineStr">
+        <is>
+          <t>通讯录</t>
+        </is>
+      </c>
+      <c r="F606" t="inlineStr"/>
+      <c r="G606" t="inlineStr"/>
+      <c r="H606" t="inlineStr"/>
+      <c r="I606" t="inlineStr"/>
+    </row>
+    <row r="607">
+      <c r="A607" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B607" t="inlineStr"/>
+      <c r="C607" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_app_item</t>
+        </is>
+      </c>
+      <c r="D607" t="inlineStr">
+        <is>
+          <t>[872,2161][1080,2325]</t>
+        </is>
+      </c>
+      <c r="E607" t="inlineStr"/>
+      <c r="F607" t="inlineStr"/>
+      <c r="G607" t="inlineStr"/>
+      <c r="H607" t="inlineStr"/>
+      <c r="I607" t="inlineStr"/>
+    </row>
+    <row r="608">
+      <c r="A608" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B608" t="inlineStr"/>
+      <c r="C608" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_icon_group</t>
+        </is>
+      </c>
+      <c r="D608" t="inlineStr">
+        <is>
+          <t>[923,2191][1028,2296]</t>
+        </is>
+      </c>
+      <c r="E608" t="inlineStr"/>
+      <c r="F608" t="inlineStr"/>
+      <c r="G608" t="inlineStr"/>
+      <c r="H608" t="inlineStr"/>
+      <c r="I608" t="inlineStr"/>
+    </row>
+    <row r="609">
+      <c r="A609" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B609" t="inlineStr"/>
+      <c r="C609" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_icon</t>
+        </is>
+      </c>
+      <c r="D609" t="inlineStr">
+        <is>
+          <t>[939,2191][1011,2263]</t>
+        </is>
+      </c>
+      <c r="E609" t="inlineStr"/>
+      <c r="F609" t="inlineStr"/>
+      <c r="G609" t="inlineStr"/>
+      <c r="H609" t="inlineStr"/>
+      <c r="I609" t="inlineStr"/>
+    </row>
+    <row r="610">
+      <c r="A610" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B610" t="inlineStr"/>
+      <c r="C610" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/fl_bottom_text</t>
+        </is>
+      </c>
+      <c r="D610" t="inlineStr">
+        <is>
+          <t>[946,2269][1006,2325]</t>
+        </is>
+      </c>
+      <c r="E610" t="inlineStr"/>
+      <c r="F610" t="inlineStr"/>
+      <c r="G610" t="inlineStr"/>
+      <c r="H610" t="inlineStr"/>
+      <c r="I610" t="inlineStr"/>
+    </row>
+    <row r="611">
+      <c r="A611" t="inlineStr">
+        <is>
+          <t>首页</t>
+        </is>
+      </c>
+      <c r="B611" t="inlineStr"/>
+      <c r="C611" t="inlineStr">
+        <is>
+          <t>com.alibaba.android.rimet:id/home_bottom_tab_text</t>
+        </is>
+      </c>
+      <c r="D611" t="inlineStr">
+        <is>
+          <t>[946,2269][1006,2310]</t>
+        </is>
+      </c>
+      <c r="E611" t="inlineStr">
+        <is>
+          <t>我的</t>
+        </is>
+      </c>
+      <c r="F611" t="inlineStr"/>
+      <c r="G611" t="inlineStr"/>
+      <c r="H611" t="inlineStr"/>
+      <c r="I611" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
